--- a/public/templates/!FORMAT CV LPK MSS NEW.xlsx
+++ b/public/templates/!FORMAT CV LPK MSS NEW.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="4" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="278">
   <si>
     <r>
       <t xml:space="preserve">Reference </t>
@@ -53,7 +53,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Mincho"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">• Address </t>
     </r>
     <r>
@@ -297,6 +303,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">• Number of Family </t>
     </r>
     <r>
@@ -347,6 +359,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Care of elderly </t>
     </r>
     <r>
@@ -427,6 +445,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Care of disabled  </t>
     </r>
     <r>
@@ -483,6 +507,38 @@
   </si>
   <si>
     <t>Gardening 園丁工作</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Car Washing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>車</t>
+    </r>
   </si>
   <si>
     <t>Car Washing 洗 車</t>
@@ -2353,6 +2409,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -2362,12 +2424,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -2575,6 +2631,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="4" tint="0.399975585192419"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="SimSun"/>
@@ -2589,12 +2651,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="4" tint="0.399975585192419"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3612,7 +3668,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="391">
+  <cellXfs count="387">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4439,16 +4495,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4501,203 +4557,191 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4716,16 +4760,16 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4734,7 +4778,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6448,14 +6492,14 @@
       <c r="U24" s="308" t="s">
         <v>15</v>
       </c>
-      <c r="V24" s="309"/>
-      <c r="W24" s="309"/>
-      <c r="X24" s="309"/>
-      <c r="Y24" s="309"/>
-      <c r="Z24" s="309"/>
-      <c r="AA24" s="309"/>
-      <c r="AB24" s="309"/>
-      <c r="AC24" s="309"/>
+      <c r="V24" s="304"/>
+      <c r="W24" s="304"/>
+      <c r="X24" s="304"/>
+      <c r="Y24" s="304"/>
+      <c r="Z24" s="304"/>
+      <c r="AA24" s="304"/>
+      <c r="AB24" s="304"/>
+      <c r="AC24" s="304"/>
       <c r="AD24" s="290"/>
       <c r="AE24" s="290"/>
       <c r="AF24" s="290"/>
@@ -6521,17 +6565,17 @@
       <c r="AQ25" s="291"/>
     </row>
     <row r="26" spans="1:43">
-      <c r="A26" s="310" t="s">
+      <c r="A26" s="309" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="311"/>
-      <c r="C26" s="311"/>
-      <c r="D26" s="311"/>
-      <c r="E26" s="311"/>
-      <c r="F26" s="311"/>
-      <c r="G26" s="311"/>
-      <c r="H26" s="311"/>
-      <c r="I26" s="311"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="310"/>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="310"/>
+      <c r="G26" s="310"/>
+      <c r="H26" s="310"/>
+      <c r="I26" s="310"/>
       <c r="J26" s="302" t="s">
         <v>15</v>
       </c>
@@ -6570,17 +6614,17 @@
       <c r="AQ26" s="291"/>
     </row>
     <row r="27" spans="1:43">
-      <c r="A27" s="310" t="s">
+      <c r="A27" s="309" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="311"/>
-      <c r="C27" s="311"/>
-      <c r="D27" s="311"/>
-      <c r="E27" s="311"/>
-      <c r="F27" s="311"/>
-      <c r="G27" s="311"/>
-      <c r="H27" s="311"/>
-      <c r="I27" s="311"/>
+      <c r="B27" s="310"/>
+      <c r="C27" s="310"/>
+      <c r="D27" s="310"/>
+      <c r="E27" s="310"/>
+      <c r="F27" s="310"/>
+      <c r="G27" s="310"/>
+      <c r="H27" s="310"/>
+      <c r="I27" s="310"/>
       <c r="J27" s="302" t="s">
         <v>15</v>
       </c>
@@ -6619,17 +6663,17 @@
       <c r="AQ27" s="291"/>
     </row>
     <row r="28" spans="1:43">
-      <c r="A28" s="310" t="s">
+      <c r="A28" s="309" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="311"/>
-      <c r="C28" s="311"/>
-      <c r="D28" s="311"/>
-      <c r="E28" s="311"/>
-      <c r="F28" s="311"/>
-      <c r="G28" s="311"/>
-      <c r="H28" s="311"/>
-      <c r="I28" s="311"/>
+      <c r="B28" s="310"/>
+      <c r="C28" s="310"/>
+      <c r="D28" s="310"/>
+      <c r="E28" s="310"/>
+      <c r="F28" s="310"/>
+      <c r="G28" s="310"/>
+      <c r="H28" s="310"/>
+      <c r="I28" s="310"/>
       <c r="J28" s="302" t="s">
         <v>15</v>
       </c>
@@ -6670,17 +6714,17 @@
       <c r="AQ28" s="291"/>
     </row>
     <row r="29" ht="12" customHeight="1" spans="1:43">
-      <c r="A29" s="310" t="s">
+      <c r="A29" s="309" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="311"/>
-      <c r="C29" s="311"/>
-      <c r="D29" s="311"/>
-      <c r="E29" s="311"/>
-      <c r="F29" s="311"/>
-      <c r="G29" s="311"/>
-      <c r="H29" s="311"/>
-      <c r="I29" s="311"/>
+      <c r="B29" s="310"/>
+      <c r="C29" s="310"/>
+      <c r="D29" s="310"/>
+      <c r="E29" s="310"/>
+      <c r="F29" s="310"/>
+      <c r="G29" s="310"/>
+      <c r="H29" s="310"/>
+      <c r="I29" s="310"/>
       <c r="J29" s="302" t="s">
         <v>15</v>
       </c>
@@ -6721,1936 +6765,1936 @@
       <c r="AQ29" s="291"/>
     </row>
     <row r="30" ht="12" customHeight="1" spans="1:43">
-      <c r="A30" s="312" t="s">
+      <c r="A30" s="311" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="313"/>
-      <c r="C30" s="313"/>
-      <c r="D30" s="313"/>
-      <c r="E30" s="313"/>
-      <c r="F30" s="313"/>
-      <c r="G30" s="313"/>
-      <c r="H30" s="313"/>
-      <c r="I30" s="313"/>
-      <c r="J30" s="314" t="s">
+      <c r="B30" s="312"/>
+      <c r="C30" s="312"/>
+      <c r="D30" s="312"/>
+      <c r="E30" s="312"/>
+      <c r="F30" s="312"/>
+      <c r="G30" s="312"/>
+      <c r="H30" s="312"/>
+      <c r="I30" s="312"/>
+      <c r="J30" s="313" t="s">
         <v>15</v>
       </c>
-      <c r="K30" s="315"/>
-      <c r="L30" s="315"/>
-      <c r="M30" s="315"/>
-      <c r="N30" s="315"/>
-      <c r="O30" s="315"/>
-      <c r="P30" s="315"/>
-      <c r="Q30" s="315"/>
-      <c r="R30" s="315"/>
-      <c r="S30" s="315"/>
-      <c r="T30" s="315"/>
-      <c r="U30" s="315"/>
-      <c r="V30" s="315"/>
-      <c r="W30" s="315"/>
-      <c r="X30" s="315"/>
-      <c r="Y30" s="315"/>
-      <c r="Z30" s="315"/>
-      <c r="AA30" s="315"/>
-      <c r="AB30" s="315"/>
-      <c r="AC30" s="315"/>
-      <c r="AD30" s="316"/>
-      <c r="AE30" s="316"/>
-      <c r="AF30" s="316"/>
-      <c r="AG30" s="316"/>
-      <c r="AH30" s="316"/>
-      <c r="AI30" s="316"/>
-      <c r="AJ30" s="316"/>
-      <c r="AK30" s="316"/>
-      <c r="AL30" s="316"/>
-      <c r="AM30" s="316"/>
-      <c r="AN30" s="316"/>
-      <c r="AO30" s="316"/>
-      <c r="AP30" s="316"/>
-      <c r="AQ30" s="317"/>
+      <c r="K30" s="314"/>
+      <c r="L30" s="314"/>
+      <c r="M30" s="314"/>
+      <c r="N30" s="314"/>
+      <c r="O30" s="314"/>
+      <c r="P30" s="314"/>
+      <c r="Q30" s="314"/>
+      <c r="R30" s="314"/>
+      <c r="S30" s="314"/>
+      <c r="T30" s="314"/>
+      <c r="U30" s="314"/>
+      <c r="V30" s="314"/>
+      <c r="W30" s="314"/>
+      <c r="X30" s="314"/>
+      <c r="Y30" s="314"/>
+      <c r="Z30" s="314"/>
+      <c r="AA30" s="314"/>
+      <c r="AB30" s="314"/>
+      <c r="AC30" s="314"/>
+      <c r="AD30" s="315"/>
+      <c r="AE30" s="315"/>
+      <c r="AF30" s="315"/>
+      <c r="AG30" s="315"/>
+      <c r="AH30" s="315"/>
+      <c r="AI30" s="315"/>
+      <c r="AJ30" s="315"/>
+      <c r="AK30" s="315"/>
+      <c r="AL30" s="315"/>
+      <c r="AM30" s="315"/>
+      <c r="AN30" s="315"/>
+      <c r="AO30" s="315"/>
+      <c r="AP30" s="315"/>
+      <c r="AQ30" s="316"/>
     </row>
     <row r="31" ht="12" customHeight="1" spans="1:43">
-      <c r="A31" s="318"/>
-      <c r="B31" s="318"/>
-      <c r="C31" s="318"/>
-      <c r="D31" s="318"/>
-      <c r="E31" s="318"/>
-      <c r="F31" s="318"/>
-      <c r="G31" s="318"/>
-      <c r="H31" s="318"/>
-      <c r="I31" s="318"/>
-      <c r="J31" s="318"/>
-      <c r="K31" s="318"/>
-      <c r="L31" s="318"/>
-      <c r="M31" s="318"/>
-      <c r="N31" s="318"/>
-      <c r="O31" s="318"/>
-      <c r="P31" s="318"/>
-      <c r="Q31" s="318"/>
-      <c r="R31" s="318"/>
-      <c r="S31" s="318"/>
-      <c r="T31" s="318"/>
-      <c r="U31" s="318"/>
-      <c r="V31" s="318"/>
-      <c r="W31" s="318"/>
-      <c r="X31" s="318"/>
-      <c r="Y31" s="318"/>
-      <c r="Z31" s="318"/>
-      <c r="AA31" s="318"/>
-      <c r="AB31" s="318"/>
-      <c r="AC31" s="318"/>
-      <c r="AD31" s="318"/>
-      <c r="AE31" s="318"/>
-      <c r="AF31" s="318"/>
-      <c r="AG31" s="318"/>
-      <c r="AH31" s="318"/>
-      <c r="AI31" s="318"/>
-      <c r="AJ31" s="318"/>
-      <c r="AK31" s="318"/>
-      <c r="AL31" s="318"/>
-      <c r="AM31" s="318"/>
-      <c r="AN31" s="318"/>
-      <c r="AO31" s="318"/>
-      <c r="AP31" s="318"/>
-      <c r="AQ31" s="318"/>
+      <c r="A31" s="317"/>
+      <c r="B31" s="317"/>
+      <c r="C31" s="317"/>
+      <c r="D31" s="317"/>
+      <c r="E31" s="317"/>
+      <c r="F31" s="317"/>
+      <c r="G31" s="317"/>
+      <c r="H31" s="317"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="317"/>
+      <c r="K31" s="317"/>
+      <c r="L31" s="317"/>
+      <c r="M31" s="317"/>
+      <c r="N31" s="317"/>
+      <c r="O31" s="317"/>
+      <c r="P31" s="317"/>
+      <c r="Q31" s="317"/>
+      <c r="R31" s="317"/>
+      <c r="S31" s="317"/>
+      <c r="T31" s="317"/>
+      <c r="U31" s="317"/>
+      <c r="V31" s="317"/>
+      <c r="W31" s="317"/>
+      <c r="X31" s="317"/>
+      <c r="Y31" s="317"/>
+      <c r="Z31" s="317"/>
+      <c r="AA31" s="317"/>
+      <c r="AB31" s="317"/>
+      <c r="AC31" s="317"/>
+      <c r="AD31" s="317"/>
+      <c r="AE31" s="317"/>
+      <c r="AF31" s="317"/>
+      <c r="AG31" s="317"/>
+      <c r="AH31" s="317"/>
+      <c r="AI31" s="317"/>
+      <c r="AJ31" s="317"/>
+      <c r="AK31" s="317"/>
+      <c r="AL31" s="317"/>
+      <c r="AM31" s="317"/>
+      <c r="AN31" s="317"/>
+      <c r="AO31" s="317"/>
+      <c r="AP31" s="317"/>
+      <c r="AQ31" s="317"/>
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:43">
-      <c r="A32" s="319" t="s">
+      <c r="A32" s="318" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="320"/>
-      <c r="C32" s="320"/>
-      <c r="D32" s="320"/>
-      <c r="E32" s="320"/>
-      <c r="F32" s="320"/>
-      <c r="G32" s="320"/>
-      <c r="H32" s="320"/>
-      <c r="I32" s="320"/>
-      <c r="J32" s="320"/>
-      <c r="K32" s="320"/>
-      <c r="L32" s="320"/>
-      <c r="M32" s="320"/>
-      <c r="N32" s="320"/>
-      <c r="O32" s="320"/>
-      <c r="P32" s="320"/>
-      <c r="Q32" s="320"/>
-      <c r="R32" s="320"/>
-      <c r="S32" s="320"/>
-      <c r="T32" s="320"/>
-      <c r="U32" s="320"/>
-      <c r="V32" s="320"/>
-      <c r="W32" s="320"/>
-      <c r="X32" s="320"/>
-      <c r="Y32" s="320"/>
-      <c r="Z32" s="320"/>
-      <c r="AA32" s="320"/>
-      <c r="AB32" s="320"/>
-      <c r="AC32" s="320"/>
-      <c r="AD32" s="320"/>
-      <c r="AE32" s="320"/>
-      <c r="AF32" s="320"/>
-      <c r="AG32" s="320"/>
-      <c r="AH32" s="320"/>
-      <c r="AI32" s="320"/>
-      <c r="AJ32" s="320"/>
-      <c r="AK32" s="320"/>
-      <c r="AL32" s="320"/>
-      <c r="AM32" s="320"/>
-      <c r="AN32" s="320"/>
-      <c r="AO32" s="320"/>
-      <c r="AP32" s="320"/>
-      <c r="AQ32" s="321"/>
+      <c r="B32" s="319"/>
+      <c r="C32" s="319"/>
+      <c r="D32" s="319"/>
+      <c r="E32" s="319"/>
+      <c r="F32" s="319"/>
+      <c r="G32" s="319"/>
+      <c r="H32" s="319"/>
+      <c r="I32" s="319"/>
+      <c r="J32" s="319"/>
+      <c r="K32" s="319"/>
+      <c r="L32" s="319"/>
+      <c r="M32" s="319"/>
+      <c r="N32" s="319"/>
+      <c r="O32" s="319"/>
+      <c r="P32" s="319"/>
+      <c r="Q32" s="319"/>
+      <c r="R32" s="319"/>
+      <c r="S32" s="319"/>
+      <c r="T32" s="319"/>
+      <c r="U32" s="319"/>
+      <c r="V32" s="319"/>
+      <c r="W32" s="319"/>
+      <c r="X32" s="319"/>
+      <c r="Y32" s="319"/>
+      <c r="Z32" s="319"/>
+      <c r="AA32" s="319"/>
+      <c r="AB32" s="319"/>
+      <c r="AC32" s="319"/>
+      <c r="AD32" s="319"/>
+      <c r="AE32" s="319"/>
+      <c r="AF32" s="319"/>
+      <c r="AG32" s="319"/>
+      <c r="AH32" s="319"/>
+      <c r="AI32" s="319"/>
+      <c r="AJ32" s="319"/>
+      <c r="AK32" s="319"/>
+      <c r="AL32" s="319"/>
+      <c r="AM32" s="319"/>
+      <c r="AN32" s="319"/>
+      <c r="AO32" s="319"/>
+      <c r="AP32" s="319"/>
+      <c r="AQ32" s="320"/>
     </row>
     <row r="33" ht="12" customHeight="1" spans="1:43">
-      <c r="A33" s="322"/>
-      <c r="B33" s="323"/>
-      <c r="C33" s="323"/>
-      <c r="D33" s="323"/>
-      <c r="E33" s="323"/>
-      <c r="F33" s="323"/>
-      <c r="G33" s="323"/>
-      <c r="H33" s="323"/>
-      <c r="I33" s="323"/>
-      <c r="J33" s="323"/>
-      <c r="K33" s="323"/>
-      <c r="L33" s="323"/>
-      <c r="M33" s="323"/>
-      <c r="N33" s="323"/>
-      <c r="O33" s="323"/>
-      <c r="P33" s="323"/>
-      <c r="Q33" s="323"/>
-      <c r="R33" s="323"/>
-      <c r="S33" s="323"/>
-      <c r="T33" s="323"/>
-      <c r="U33" s="323"/>
-      <c r="V33" s="323"/>
-      <c r="W33" s="323"/>
-      <c r="X33" s="323"/>
-      <c r="Y33" s="323"/>
-      <c r="Z33" s="323"/>
-      <c r="AA33" s="323"/>
-      <c r="AB33" s="323"/>
-      <c r="AC33" s="323"/>
-      <c r="AD33" s="323"/>
-      <c r="AE33" s="323"/>
-      <c r="AF33" s="323"/>
-      <c r="AG33" s="323"/>
-      <c r="AH33" s="323"/>
-      <c r="AI33" s="323"/>
-      <c r="AJ33" s="323"/>
-      <c r="AK33" s="323"/>
-      <c r="AL33" s="323"/>
-      <c r="AM33" s="323"/>
-      <c r="AN33" s="323"/>
-      <c r="AO33" s="323"/>
-      <c r="AP33" s="323"/>
-      <c r="AQ33" s="324"/>
+      <c r="A33" s="321"/>
+      <c r="B33" s="322"/>
+      <c r="C33" s="322"/>
+      <c r="D33" s="322"/>
+      <c r="E33" s="322"/>
+      <c r="F33" s="322"/>
+      <c r="G33" s="322"/>
+      <c r="H33" s="322"/>
+      <c r="I33" s="322"/>
+      <c r="J33" s="322"/>
+      <c r="K33" s="322"/>
+      <c r="L33" s="322"/>
+      <c r="M33" s="322"/>
+      <c r="N33" s="322"/>
+      <c r="O33" s="322"/>
+      <c r="P33" s="322"/>
+      <c r="Q33" s="322"/>
+      <c r="R33" s="322"/>
+      <c r="S33" s="322"/>
+      <c r="T33" s="322"/>
+      <c r="U33" s="322"/>
+      <c r="V33" s="322"/>
+      <c r="W33" s="322"/>
+      <c r="X33" s="322"/>
+      <c r="Y33" s="322"/>
+      <c r="Z33" s="322"/>
+      <c r="AA33" s="322"/>
+      <c r="AB33" s="322"/>
+      <c r="AC33" s="322"/>
+      <c r="AD33" s="322"/>
+      <c r="AE33" s="322"/>
+      <c r="AF33" s="322"/>
+      <c r="AG33" s="322"/>
+      <c r="AH33" s="322"/>
+      <c r="AI33" s="322"/>
+      <c r="AJ33" s="322"/>
+      <c r="AK33" s="322"/>
+      <c r="AL33" s="322"/>
+      <c r="AM33" s="322"/>
+      <c r="AN33" s="322"/>
+      <c r="AO33" s="322"/>
+      <c r="AP33" s="322"/>
+      <c r="AQ33" s="323"/>
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:43">
-      <c r="A34" s="325" t="s">
+      <c r="A34" s="324" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="326"/>
-      <c r="C34" s="326"/>
-      <c r="D34" s="326"/>
-      <c r="E34" s="326"/>
-      <c r="F34" s="326"/>
-      <c r="G34" s="326"/>
-      <c r="H34" s="326"/>
-      <c r="I34" s="326"/>
-      <c r="J34" s="327" t="s">
+      <c r="B34" s="325"/>
+      <c r="C34" s="325"/>
+      <c r="D34" s="325"/>
+      <c r="E34" s="325"/>
+      <c r="F34" s="325"/>
+      <c r="G34" s="325"/>
+      <c r="H34" s="325"/>
+      <c r="I34" s="325"/>
+      <c r="J34" s="326" t="s">
         <v>15</v>
       </c>
-      <c r="K34" s="328"/>
-      <c r="L34" s="328"/>
-      <c r="M34" s="328"/>
-      <c r="N34" s="328"/>
-      <c r="O34" s="328"/>
-      <c r="P34" s="328"/>
-      <c r="Q34" s="328"/>
-      <c r="R34" s="328"/>
-      <c r="S34" s="328"/>
-      <c r="T34" s="328"/>
-      <c r="U34" s="328"/>
-      <c r="V34" s="328"/>
-      <c r="W34" s="329" t="s">
+      <c r="K34" s="327"/>
+      <c r="L34" s="327"/>
+      <c r="M34" s="327"/>
+      <c r="N34" s="327"/>
+      <c r="O34" s="327"/>
+      <c r="P34" s="327"/>
+      <c r="Q34" s="327"/>
+      <c r="R34" s="327"/>
+      <c r="S34" s="327"/>
+      <c r="T34" s="327"/>
+      <c r="U34" s="327"/>
+      <c r="V34" s="327"/>
+      <c r="W34" s="324" t="s">
         <v>32</v>
       </c>
-      <c r="X34" s="330"/>
-      <c r="Y34" s="330"/>
-      <c r="Z34" s="330"/>
-      <c r="AA34" s="330"/>
-      <c r="AB34" s="330"/>
-      <c r="AC34" s="330"/>
-      <c r="AD34" s="330"/>
-      <c r="AE34" s="330"/>
-      <c r="AF34" s="327" t="s">
+      <c r="X34" s="325"/>
+      <c r="Y34" s="325"/>
+      <c r="Z34" s="325"/>
+      <c r="AA34" s="325"/>
+      <c r="AB34" s="325"/>
+      <c r="AC34" s="325"/>
+      <c r="AD34" s="325"/>
+      <c r="AE34" s="325"/>
+      <c r="AF34" s="326" t="s">
         <v>15</v>
       </c>
-      <c r="AG34" s="330"/>
-      <c r="AH34" s="330"/>
-      <c r="AI34" s="330"/>
-      <c r="AJ34" s="330"/>
-      <c r="AK34" s="330"/>
-      <c r="AL34" s="330"/>
-      <c r="AM34" s="330"/>
-      <c r="AN34" s="330"/>
-      <c r="AO34" s="330"/>
-      <c r="AP34" s="330"/>
-      <c r="AQ34" s="331"/>
+      <c r="AG34" s="325"/>
+      <c r="AH34" s="325"/>
+      <c r="AI34" s="325"/>
+      <c r="AJ34" s="325"/>
+      <c r="AK34" s="325"/>
+      <c r="AL34" s="325"/>
+      <c r="AM34" s="325"/>
+      <c r="AN34" s="325"/>
+      <c r="AO34" s="325"/>
+      <c r="AP34" s="325"/>
+      <c r="AQ34" s="328"/>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:43">
-      <c r="A35" s="332" t="s">
+      <c r="A35" s="329" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="333"/>
-      <c r="C35" s="333"/>
-      <c r="D35" s="333"/>
-      <c r="E35" s="333"/>
-      <c r="F35" s="333"/>
-      <c r="G35" s="333"/>
-      <c r="H35" s="333"/>
-      <c r="I35" s="333"/>
-      <c r="J35" s="334" t="s">
+      <c r="B35" s="330"/>
+      <c r="C35" s="330"/>
+      <c r="D35" s="330"/>
+      <c r="E35" s="330"/>
+      <c r="F35" s="330"/>
+      <c r="G35" s="330"/>
+      <c r="H35" s="330"/>
+      <c r="I35" s="330"/>
+      <c r="J35" s="331" t="s">
         <v>15</v>
       </c>
-      <c r="K35" s="333"/>
-      <c r="L35" s="333"/>
-      <c r="M35" s="333"/>
-      <c r="N35" s="333"/>
-      <c r="O35" s="333"/>
-      <c r="P35" s="333"/>
-      <c r="Q35" s="333"/>
-      <c r="R35" s="333"/>
-      <c r="S35" s="333"/>
-      <c r="T35" s="333"/>
-      <c r="U35" s="333"/>
-      <c r="V35" s="333"/>
-      <c r="W35" s="335" t="s">
+      <c r="K35" s="330"/>
+      <c r="L35" s="330"/>
+      <c r="M35" s="330"/>
+      <c r="N35" s="330"/>
+      <c r="O35" s="330"/>
+      <c r="P35" s="330"/>
+      <c r="Q35" s="330"/>
+      <c r="R35" s="330"/>
+      <c r="S35" s="330"/>
+      <c r="T35" s="330"/>
+      <c r="U35" s="330"/>
+      <c r="V35" s="330"/>
+      <c r="W35" s="329" t="s">
         <v>34</v>
       </c>
-      <c r="X35" s="336"/>
-      <c r="Y35" s="336"/>
-      <c r="Z35" s="336"/>
-      <c r="AA35" s="336"/>
-      <c r="AB35" s="336"/>
-      <c r="AC35" s="336"/>
-      <c r="AD35" s="336"/>
-      <c r="AE35" s="336"/>
-      <c r="AF35" s="334" t="s">
+      <c r="X35" s="330"/>
+      <c r="Y35" s="330"/>
+      <c r="Z35" s="330"/>
+      <c r="AA35" s="330"/>
+      <c r="AB35" s="330"/>
+      <c r="AC35" s="330"/>
+      <c r="AD35" s="330"/>
+      <c r="AE35" s="330"/>
+      <c r="AF35" s="331" t="s">
         <v>15</v>
       </c>
-      <c r="AG35" s="333"/>
-      <c r="AH35" s="333"/>
-      <c r="AI35" s="336" t="s">
+      <c r="AG35" s="330"/>
+      <c r="AH35" s="330"/>
+      <c r="AI35" s="332" t="s">
         <v>35</v>
       </c>
-      <c r="AJ35" s="336"/>
-      <c r="AK35" s="336"/>
-      <c r="AL35" s="336"/>
-      <c r="AM35" s="336"/>
-      <c r="AN35" s="336"/>
-      <c r="AO35" s="336"/>
-      <c r="AP35" s="336"/>
-      <c r="AQ35" s="337"/>
+      <c r="AJ35" s="332"/>
+      <c r="AK35" s="332"/>
+      <c r="AL35" s="332"/>
+      <c r="AM35" s="332"/>
+      <c r="AN35" s="332"/>
+      <c r="AO35" s="332"/>
+      <c r="AP35" s="332"/>
+      <c r="AQ35" s="333"/>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:43">
-      <c r="A36" s="338" t="s">
+      <c r="A36" s="334" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="339"/>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
-      <c r="G36" s="339"/>
-      <c r="H36" s="339"/>
-      <c r="I36" s="339"/>
+      <c r="B36" s="335"/>
+      <c r="C36" s="335"/>
+      <c r="D36" s="335"/>
+      <c r="E36" s="335"/>
+      <c r="F36" s="335"/>
+      <c r="G36" s="335"/>
+      <c r="H36" s="335"/>
+      <c r="I36" s="335"/>
       <c r="J36" s="305" t="s">
         <v>15</v>
       </c>
-      <c r="K36" s="311"/>
-      <c r="L36" s="311"/>
-      <c r="M36" s="311"/>
-      <c r="N36" s="311"/>
-      <c r="O36" s="311"/>
-      <c r="P36" s="311"/>
-      <c r="Q36" s="311"/>
-      <c r="R36" s="311"/>
-      <c r="S36" s="311"/>
-      <c r="T36" s="311"/>
-      <c r="U36" s="311"/>
-      <c r="V36" s="311"/>
-      <c r="W36" s="340" t="s">
+      <c r="K36" s="310"/>
+      <c r="L36" s="310"/>
+      <c r="M36" s="310"/>
+      <c r="N36" s="310"/>
+      <c r="O36" s="310"/>
+      <c r="P36" s="310"/>
+      <c r="Q36" s="310"/>
+      <c r="R36" s="310"/>
+      <c r="S36" s="310"/>
+      <c r="T36" s="310"/>
+      <c r="U36" s="310"/>
+      <c r="V36" s="310"/>
+      <c r="W36" s="336" t="s">
         <v>37</v>
       </c>
-      <c r="X36" s="341"/>
-      <c r="Y36" s="341"/>
-      <c r="Z36" s="341"/>
-      <c r="AA36" s="341"/>
-      <c r="AB36" s="341"/>
-      <c r="AC36" s="341"/>
-      <c r="AD36" s="341"/>
-      <c r="AE36" s="341"/>
-      <c r="AF36" s="342" t="s">
+      <c r="X36" s="337"/>
+      <c r="Y36" s="337"/>
+      <c r="Z36" s="337"/>
+      <c r="AA36" s="337"/>
+      <c r="AB36" s="337"/>
+      <c r="AC36" s="337"/>
+      <c r="AD36" s="337"/>
+      <c r="AE36" s="337"/>
+      <c r="AF36" s="338" t="s">
         <v>15</v>
       </c>
-      <c r="AG36" s="311"/>
-      <c r="AH36" s="311"/>
-      <c r="AI36" s="311"/>
-      <c r="AJ36" s="311"/>
-      <c r="AK36" s="311"/>
-      <c r="AL36" s="311"/>
-      <c r="AM36" s="311"/>
-      <c r="AN36" s="311"/>
-      <c r="AO36" s="311"/>
-      <c r="AP36" s="311"/>
-      <c r="AQ36" s="343"/>
+      <c r="AG36" s="310"/>
+      <c r="AH36" s="310"/>
+      <c r="AI36" s="310"/>
+      <c r="AJ36" s="310"/>
+      <c r="AK36" s="310"/>
+      <c r="AL36" s="310"/>
+      <c r="AM36" s="310"/>
+      <c r="AN36" s="310"/>
+      <c r="AO36" s="310"/>
+      <c r="AP36" s="310"/>
+      <c r="AQ36" s="339"/>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:43">
-      <c r="A37" s="340" t="s">
+      <c r="A37" s="336" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="341"/>
-      <c r="C37" s="341"/>
-      <c r="D37" s="341"/>
-      <c r="E37" s="341"/>
-      <c r="F37" s="341"/>
-      <c r="G37" s="341"/>
-      <c r="H37" s="341"/>
-      <c r="I37" s="341"/>
+      <c r="B37" s="337"/>
+      <c r="C37" s="337"/>
+      <c r="D37" s="337"/>
+      <c r="E37" s="337"/>
+      <c r="F37" s="337"/>
+      <c r="G37" s="337"/>
+      <c r="H37" s="337"/>
+      <c r="I37" s="337"/>
       <c r="J37" s="305" t="s">
         <v>15</v>
       </c>
-      <c r="K37" s="311"/>
-      <c r="L37" s="311"/>
-      <c r="M37" s="311"/>
-      <c r="N37" s="311"/>
-      <c r="O37" s="311"/>
-      <c r="P37" s="311"/>
-      <c r="Q37" s="311"/>
-      <c r="R37" s="311"/>
-      <c r="S37" s="311"/>
-      <c r="T37" s="311"/>
-      <c r="U37" s="311"/>
-      <c r="V37" s="311"/>
-      <c r="W37" s="340" t="s">
+      <c r="K37" s="310"/>
+      <c r="L37" s="310"/>
+      <c r="M37" s="310"/>
+      <c r="N37" s="310"/>
+      <c r="O37" s="310"/>
+      <c r="P37" s="310"/>
+      <c r="Q37" s="310"/>
+      <c r="R37" s="310"/>
+      <c r="S37" s="310"/>
+      <c r="T37" s="310"/>
+      <c r="U37" s="310"/>
+      <c r="V37" s="310"/>
+      <c r="W37" s="336" t="s">
         <v>39</v>
       </c>
-      <c r="X37" s="341"/>
-      <c r="Y37" s="341"/>
-      <c r="Z37" s="341"/>
-      <c r="AA37" s="341"/>
-      <c r="AB37" s="341"/>
-      <c r="AC37" s="341"/>
-      <c r="AD37" s="341"/>
-      <c r="AE37" s="341"/>
-      <c r="AF37" s="342" t="s">
+      <c r="X37" s="337"/>
+      <c r="Y37" s="337"/>
+      <c r="Z37" s="337"/>
+      <c r="AA37" s="337"/>
+      <c r="AB37" s="337"/>
+      <c r="AC37" s="337"/>
+      <c r="AD37" s="337"/>
+      <c r="AE37" s="337"/>
+      <c r="AF37" s="338" t="s">
         <v>15</v>
       </c>
-      <c r="AG37" s="311"/>
-      <c r="AH37" s="311"/>
-      <c r="AI37" s="311"/>
-      <c r="AJ37" s="311"/>
-      <c r="AK37" s="311"/>
-      <c r="AL37" s="311"/>
-      <c r="AM37" s="311"/>
-      <c r="AN37" s="311"/>
-      <c r="AO37" s="311"/>
-      <c r="AP37" s="311"/>
-      <c r="AQ37" s="343"/>
+      <c r="AG37" s="310"/>
+      <c r="AH37" s="310"/>
+      <c r="AI37" s="310"/>
+      <c r="AJ37" s="310"/>
+      <c r="AK37" s="310"/>
+      <c r="AL37" s="310"/>
+      <c r="AM37" s="310"/>
+      <c r="AN37" s="310"/>
+      <c r="AO37" s="310"/>
+      <c r="AP37" s="310"/>
+      <c r="AQ37" s="339"/>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:43">
-      <c r="A38" s="340" t="s">
+      <c r="A38" s="336" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="341"/>
-      <c r="C38" s="341"/>
-      <c r="D38" s="341"/>
-      <c r="E38" s="341"/>
-      <c r="F38" s="341"/>
-      <c r="G38" s="341"/>
-      <c r="H38" s="341"/>
-      <c r="I38" s="341"/>
+      <c r="B38" s="337"/>
+      <c r="C38" s="337"/>
+      <c r="D38" s="337"/>
+      <c r="E38" s="337"/>
+      <c r="F38" s="337"/>
+      <c r="G38" s="337"/>
+      <c r="H38" s="337"/>
+      <c r="I38" s="337"/>
       <c r="J38" s="305" t="s">
         <v>15</v>
       </c>
-      <c r="K38" s="311"/>
-      <c r="L38" s="311"/>
-      <c r="M38" s="311"/>
-      <c r="N38" s="311"/>
-      <c r="O38" s="311"/>
-      <c r="P38" s="311"/>
-      <c r="Q38" s="311"/>
-      <c r="R38" s="311"/>
-      <c r="S38" s="311"/>
-      <c r="T38" s="311"/>
-      <c r="U38" s="311"/>
-      <c r="V38" s="311"/>
-      <c r="W38" s="340" t="s">
+      <c r="K38" s="310"/>
+      <c r="L38" s="310"/>
+      <c r="M38" s="310"/>
+      <c r="N38" s="310"/>
+      <c r="O38" s="310"/>
+      <c r="P38" s="310"/>
+      <c r="Q38" s="310"/>
+      <c r="R38" s="310"/>
+      <c r="S38" s="310"/>
+      <c r="T38" s="310"/>
+      <c r="U38" s="310"/>
+      <c r="V38" s="310"/>
+      <c r="W38" s="336" t="s">
         <v>41</v>
       </c>
-      <c r="X38" s="341"/>
-      <c r="Y38" s="341"/>
-      <c r="Z38" s="341"/>
-      <c r="AA38" s="341"/>
-      <c r="AB38" s="341"/>
-      <c r="AC38" s="341"/>
-      <c r="AD38" s="341"/>
-      <c r="AE38" s="341"/>
-      <c r="AF38" s="342" t="s">
+      <c r="X38" s="337"/>
+      <c r="Y38" s="337"/>
+      <c r="Z38" s="337"/>
+      <c r="AA38" s="337"/>
+      <c r="AB38" s="337"/>
+      <c r="AC38" s="337"/>
+      <c r="AD38" s="337"/>
+      <c r="AE38" s="337"/>
+      <c r="AF38" s="338" t="s">
         <v>15</v>
       </c>
-      <c r="AG38" s="311"/>
-      <c r="AH38" s="311"/>
-      <c r="AI38" s="341" t="s">
+      <c r="AG38" s="310"/>
+      <c r="AH38" s="310"/>
+      <c r="AI38" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="AJ38" s="341"/>
-      <c r="AK38" s="341"/>
-      <c r="AL38" s="341"/>
-      <c r="AM38" s="341"/>
-      <c r="AN38" s="341"/>
-      <c r="AO38" s="341"/>
-      <c r="AP38" s="341"/>
-      <c r="AQ38" s="344"/>
+      <c r="AJ38" s="337"/>
+      <c r="AK38" s="337"/>
+      <c r="AL38" s="337"/>
+      <c r="AM38" s="337"/>
+      <c r="AN38" s="337"/>
+      <c r="AO38" s="337"/>
+      <c r="AP38" s="337"/>
+      <c r="AQ38" s="340"/>
     </row>
     <row r="39" ht="12" customHeight="1" spans="1:43">
-      <c r="A39" s="332" t="s">
+      <c r="A39" s="329" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="333"/>
-      <c r="C39" s="333"/>
-      <c r="D39" s="333"/>
-      <c r="E39" s="333"/>
-      <c r="F39" s="333"/>
-      <c r="G39" s="333"/>
-      <c r="H39" s="333"/>
-      <c r="I39" s="333"/>
-      <c r="J39" s="345" t="s">
+      <c r="B39" s="330"/>
+      <c r="C39" s="330"/>
+      <c r="D39" s="330"/>
+      <c r="E39" s="330"/>
+      <c r="F39" s="330"/>
+      <c r="G39" s="330"/>
+      <c r="H39" s="330"/>
+      <c r="I39" s="330"/>
+      <c r="J39" s="341" t="s">
         <v>15</v>
       </c>
-      <c r="K39" s="346"/>
-      <c r="L39" s="345" t="s">
+      <c r="K39" s="342"/>
+      <c r="L39" s="341" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="346"/>
-      <c r="N39" s="346" t="s">
+      <c r="M39" s="342"/>
+      <c r="N39" s="342" t="s">
         <v>35</v>
       </c>
-      <c r="O39" s="346"/>
-      <c r="P39" s="346"/>
-      <c r="Q39" s="346"/>
-      <c r="R39" s="346"/>
-      <c r="S39" s="346"/>
-      <c r="T39" s="346"/>
-      <c r="U39" s="346"/>
-      <c r="V39" s="346"/>
-      <c r="W39" s="347" t="s">
+      <c r="O39" s="342"/>
+      <c r="P39" s="342"/>
+      <c r="Q39" s="342"/>
+      <c r="R39" s="342"/>
+      <c r="S39" s="342"/>
+      <c r="T39" s="342"/>
+      <c r="U39" s="342"/>
+      <c r="V39" s="342"/>
+      <c r="W39" s="343" t="s">
         <v>43</v>
       </c>
-      <c r="X39" s="288"/>
-      <c r="Y39" s="288"/>
-      <c r="Z39" s="288"/>
-      <c r="AA39" s="288"/>
-      <c r="AB39" s="288"/>
-      <c r="AC39" s="288"/>
-      <c r="AD39" s="288"/>
-      <c r="AE39" s="288"/>
-      <c r="AF39" s="348" t="s">
+      <c r="X39" s="344"/>
+      <c r="Y39" s="344"/>
+      <c r="Z39" s="344"/>
+      <c r="AA39" s="344"/>
+      <c r="AB39" s="344"/>
+      <c r="AC39" s="344"/>
+      <c r="AD39" s="344"/>
+      <c r="AE39" s="344"/>
+      <c r="AF39" s="345" t="s">
         <v>15</v>
       </c>
-      <c r="AG39" s="346"/>
-      <c r="AH39" s="346"/>
-      <c r="AI39" s="346"/>
-      <c r="AJ39" s="346"/>
-      <c r="AK39" s="346"/>
-      <c r="AL39" s="346"/>
-      <c r="AM39" s="346"/>
-      <c r="AN39" s="346"/>
-      <c r="AO39" s="346"/>
-      <c r="AP39" s="346"/>
-      <c r="AQ39" s="349"/>
+      <c r="AG39" s="342"/>
+      <c r="AH39" s="342"/>
+      <c r="AI39" s="342"/>
+      <c r="AJ39" s="342"/>
+      <c r="AK39" s="342"/>
+      <c r="AL39" s="342"/>
+      <c r="AM39" s="342"/>
+      <c r="AN39" s="342"/>
+      <c r="AO39" s="342"/>
+      <c r="AP39" s="342"/>
+      <c r="AQ39" s="346"/>
     </row>
     <row r="40" ht="12" customHeight="1" spans="1:43">
-      <c r="A40" s="332" t="s">
+      <c r="A40" s="329" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="333"/>
-      <c r="C40" s="333"/>
-      <c r="D40" s="333"/>
-      <c r="E40" s="333"/>
-      <c r="F40" s="333"/>
-      <c r="G40" s="333"/>
-      <c r="H40" s="333"/>
-      <c r="I40" s="333"/>
-      <c r="J40" s="345" t="s">
+      <c r="B40" s="330"/>
+      <c r="C40" s="330"/>
+      <c r="D40" s="330"/>
+      <c r="E40" s="330"/>
+      <c r="F40" s="330"/>
+      <c r="G40" s="330"/>
+      <c r="H40" s="330"/>
+      <c r="I40" s="330"/>
+      <c r="J40" s="341" t="s">
         <v>15</v>
       </c>
-      <c r="K40" s="346"/>
-      <c r="L40" s="345" t="s">
+      <c r="K40" s="342"/>
+      <c r="L40" s="341" t="s">
         <v>15</v>
       </c>
-      <c r="M40" s="346"/>
-      <c r="N40" s="346" t="s">
+      <c r="M40" s="342"/>
+      <c r="N40" s="342" t="s">
         <v>35</v>
       </c>
-      <c r="O40" s="346"/>
-      <c r="P40" s="346"/>
-      <c r="Q40" s="346"/>
-      <c r="R40" s="346"/>
-      <c r="S40" s="346"/>
-      <c r="T40" s="346"/>
-      <c r="U40" s="346"/>
-      <c r="V40" s="346"/>
-      <c r="W40" s="332" t="s">
+      <c r="O40" s="342"/>
+      <c r="P40" s="342"/>
+      <c r="Q40" s="342"/>
+      <c r="R40" s="342"/>
+      <c r="S40" s="342"/>
+      <c r="T40" s="342"/>
+      <c r="U40" s="342"/>
+      <c r="V40" s="342"/>
+      <c r="W40" s="329" t="s">
         <v>45</v>
       </c>
-      <c r="X40" s="333"/>
-      <c r="Y40" s="333"/>
-      <c r="Z40" s="333"/>
-      <c r="AA40" s="333"/>
-      <c r="AB40" s="333"/>
-      <c r="AC40" s="333"/>
-      <c r="AD40" s="333"/>
-      <c r="AE40" s="333"/>
-      <c r="AF40" s="348" t="s">
+      <c r="X40" s="330"/>
+      <c r="Y40" s="330"/>
+      <c r="Z40" s="330"/>
+      <c r="AA40" s="330"/>
+      <c r="AB40" s="330"/>
+      <c r="AC40" s="330"/>
+      <c r="AD40" s="330"/>
+      <c r="AE40" s="330"/>
+      <c r="AF40" s="345" t="s">
         <v>15</v>
       </c>
-      <c r="AG40" s="346"/>
-      <c r="AH40" s="346"/>
-      <c r="AI40" s="346"/>
-      <c r="AJ40" s="346"/>
-      <c r="AK40" s="346"/>
-      <c r="AL40" s="346"/>
-      <c r="AM40" s="346"/>
-      <c r="AN40" s="346"/>
-      <c r="AO40" s="346"/>
-      <c r="AP40" s="346"/>
-      <c r="AQ40" s="349"/>
+      <c r="AG40" s="342"/>
+      <c r="AH40" s="342"/>
+      <c r="AI40" s="342"/>
+      <c r="AJ40" s="342"/>
+      <c r="AK40" s="342"/>
+      <c r="AL40" s="342"/>
+      <c r="AM40" s="342"/>
+      <c r="AN40" s="342"/>
+      <c r="AO40" s="342"/>
+      <c r="AP40" s="342"/>
+      <c r="AQ40" s="346"/>
     </row>
     <row r="41" ht="12" customHeight="1" spans="1:43">
-      <c r="A41" s="350" t="s">
+      <c r="A41" s="347" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="350"/>
-      <c r="C41" s="350"/>
-      <c r="D41" s="350"/>
-      <c r="E41" s="350"/>
-      <c r="F41" s="350"/>
-      <c r="G41" s="350"/>
-      <c r="H41" s="350"/>
-      <c r="I41" s="350"/>
-      <c r="J41" s="350"/>
-      <c r="K41" s="350"/>
-      <c r="L41" s="350"/>
-      <c r="M41" s="350"/>
-      <c r="N41" s="350"/>
-      <c r="O41" s="350"/>
-      <c r="P41" s="350"/>
-      <c r="Q41" s="350"/>
-      <c r="R41" s="350"/>
-      <c r="S41" s="350"/>
-      <c r="T41" s="350"/>
-      <c r="U41" s="350"/>
-      <c r="V41" s="350"/>
-      <c r="W41" s="350"/>
-      <c r="X41" s="350"/>
-      <c r="Y41" s="350"/>
-      <c r="Z41" s="350"/>
-      <c r="AA41" s="350"/>
-      <c r="AB41" s="350"/>
-      <c r="AC41" s="350"/>
-      <c r="AD41" s="350"/>
-      <c r="AE41" s="350"/>
-      <c r="AF41" s="350"/>
-      <c r="AG41" s="350"/>
-      <c r="AH41" s="350"/>
-      <c r="AI41" s="350"/>
-      <c r="AJ41" s="350"/>
-      <c r="AK41" s="350"/>
-      <c r="AL41" s="350"/>
-      <c r="AM41" s="350"/>
-      <c r="AN41" s="350"/>
-      <c r="AO41" s="350"/>
-      <c r="AP41" s="350"/>
-      <c r="AQ41" s="350"/>
+      <c r="B41" s="347"/>
+      <c r="C41" s="347"/>
+      <c r="D41" s="347"/>
+      <c r="E41" s="347"/>
+      <c r="F41" s="347"/>
+      <c r="G41" s="347"/>
+      <c r="H41" s="347"/>
+      <c r="I41" s="347"/>
+      <c r="J41" s="347"/>
+      <c r="K41" s="347"/>
+      <c r="L41" s="347"/>
+      <c r="M41" s="347"/>
+      <c r="N41" s="347"/>
+      <c r="O41" s="347"/>
+      <c r="P41" s="347"/>
+      <c r="Q41" s="347"/>
+      <c r="R41" s="347"/>
+      <c r="S41" s="347"/>
+      <c r="T41" s="347"/>
+      <c r="U41" s="347"/>
+      <c r="V41" s="347"/>
+      <c r="W41" s="347"/>
+      <c r="X41" s="347"/>
+      <c r="Y41" s="347"/>
+      <c r="Z41" s="347"/>
+      <c r="AA41" s="347"/>
+      <c r="AB41" s="347"/>
+      <c r="AC41" s="347"/>
+      <c r="AD41" s="347"/>
+      <c r="AE41" s="347"/>
+      <c r="AF41" s="347"/>
+      <c r="AG41" s="347"/>
+      <c r="AH41" s="347"/>
+      <c r="AI41" s="347"/>
+      <c r="AJ41" s="347"/>
+      <c r="AK41" s="347"/>
+      <c r="AL41" s="347"/>
+      <c r="AM41" s="347"/>
+      <c r="AN41" s="347"/>
+      <c r="AO41" s="347"/>
+      <c r="AP41" s="347"/>
+      <c r="AQ41" s="347"/>
     </row>
     <row r="42" ht="12" customHeight="1" spans="1:43">
-      <c r="A42" s="350"/>
-      <c r="B42" s="350"/>
-      <c r="C42" s="350"/>
-      <c r="D42" s="350"/>
-      <c r="E42" s="350"/>
-      <c r="F42" s="350"/>
-      <c r="G42" s="350"/>
-      <c r="H42" s="350"/>
-      <c r="I42" s="350"/>
-      <c r="J42" s="350"/>
-      <c r="K42" s="350"/>
-      <c r="L42" s="350"/>
-      <c r="M42" s="350"/>
-      <c r="N42" s="350"/>
-      <c r="O42" s="350"/>
-      <c r="P42" s="350"/>
-      <c r="Q42" s="350"/>
-      <c r="R42" s="350"/>
-      <c r="S42" s="350"/>
-      <c r="T42" s="350"/>
-      <c r="U42" s="350"/>
-      <c r="V42" s="350"/>
-      <c r="W42" s="350"/>
-      <c r="X42" s="350"/>
-      <c r="Y42" s="350"/>
-      <c r="Z42" s="350"/>
-      <c r="AA42" s="350"/>
-      <c r="AB42" s="350"/>
-      <c r="AC42" s="350"/>
-      <c r="AD42" s="350"/>
-      <c r="AE42" s="350"/>
-      <c r="AF42" s="350"/>
-      <c r="AG42" s="350"/>
-      <c r="AH42" s="350"/>
-      <c r="AI42" s="350"/>
-      <c r="AJ42" s="350"/>
-      <c r="AK42" s="350"/>
-      <c r="AL42" s="350"/>
-      <c r="AM42" s="350"/>
-      <c r="AN42" s="350"/>
-      <c r="AO42" s="350"/>
-      <c r="AP42" s="350"/>
-      <c r="AQ42" s="350"/>
+      <c r="A42" s="347"/>
+      <c r="B42" s="347"/>
+      <c r="C42" s="347"/>
+      <c r="D42" s="347"/>
+      <c r="E42" s="347"/>
+      <c r="F42" s="347"/>
+      <c r="G42" s="347"/>
+      <c r="H42" s="347"/>
+      <c r="I42" s="347"/>
+      <c r="J42" s="347"/>
+      <c r="K42" s="347"/>
+      <c r="L42" s="347"/>
+      <c r="M42" s="347"/>
+      <c r="N42" s="347"/>
+      <c r="O42" s="347"/>
+      <c r="P42" s="347"/>
+      <c r="Q42" s="347"/>
+      <c r="R42" s="347"/>
+      <c r="S42" s="347"/>
+      <c r="T42" s="347"/>
+      <c r="U42" s="347"/>
+      <c r="V42" s="347"/>
+      <c r="W42" s="347"/>
+      <c r="X42" s="347"/>
+      <c r="Y42" s="347"/>
+      <c r="Z42" s="347"/>
+      <c r="AA42" s="347"/>
+      <c r="AB42" s="347"/>
+      <c r="AC42" s="347"/>
+      <c r="AD42" s="347"/>
+      <c r="AE42" s="347"/>
+      <c r="AF42" s="347"/>
+      <c r="AG42" s="347"/>
+      <c r="AH42" s="347"/>
+      <c r="AI42" s="347"/>
+      <c r="AJ42" s="347"/>
+      <c r="AK42" s="347"/>
+      <c r="AL42" s="347"/>
+      <c r="AM42" s="347"/>
+      <c r="AN42" s="347"/>
+      <c r="AO42" s="347"/>
+      <c r="AP42" s="347"/>
+      <c r="AQ42" s="347"/>
     </row>
     <row r="43" ht="12" customHeight="1" spans="1:43">
-      <c r="A43" s="325" t="s">
+      <c r="A43" s="324" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="326"/>
-      <c r="C43" s="326"/>
-      <c r="D43" s="351" t="s">
+      <c r="B43" s="325"/>
+      <c r="C43" s="325"/>
+      <c r="D43" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="326"/>
-      <c r="F43" s="326"/>
-      <c r="G43" s="326"/>
-      <c r="H43" s="326"/>
-      <c r="I43" s="326"/>
-      <c r="J43" s="326" t="s">
+      <c r="E43" s="325"/>
+      <c r="F43" s="325"/>
+      <c r="G43" s="325"/>
+      <c r="H43" s="325"/>
+      <c r="I43" s="325"/>
+      <c r="J43" s="325" t="s">
         <v>48</v>
       </c>
-      <c r="K43" s="326"/>
-      <c r="L43" s="326"/>
-      <c r="M43" s="351" t="s">
+      <c r="K43" s="325"/>
+      <c r="L43" s="325"/>
+      <c r="M43" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="N43" s="326"/>
-      <c r="O43" s="326"/>
-      <c r="P43" s="326"/>
-      <c r="Q43" s="326"/>
-      <c r="R43" s="326"/>
-      <c r="S43" s="326"/>
-      <c r="T43" s="326"/>
-      <c r="U43" s="352"/>
-      <c r="V43" s="325" t="s">
+      <c r="N43" s="325"/>
+      <c r="O43" s="325"/>
+      <c r="P43" s="325"/>
+      <c r="Q43" s="325"/>
+      <c r="R43" s="325"/>
+      <c r="S43" s="325"/>
+      <c r="T43" s="325"/>
+      <c r="U43" s="328"/>
+      <c r="V43" s="324" t="s">
         <v>47</v>
       </c>
-      <c r="W43" s="326"/>
-      <c r="X43" s="326"/>
-      <c r="Y43" s="326"/>
-      <c r="Z43" s="326" t="s">
+      <c r="W43" s="325"/>
+      <c r="X43" s="325"/>
+      <c r="Y43" s="325"/>
+      <c r="Z43" s="325" t="s">
         <v>15</v>
       </c>
-      <c r="AA43" s="326"/>
-      <c r="AB43" s="326"/>
-      <c r="AC43" s="326"/>
-      <c r="AD43" s="326"/>
-      <c r="AE43" s="326"/>
-      <c r="AF43" s="326" t="s">
+      <c r="AA43" s="325"/>
+      <c r="AB43" s="325"/>
+      <c r="AC43" s="325"/>
+      <c r="AD43" s="325"/>
+      <c r="AE43" s="325"/>
+      <c r="AF43" s="325" t="s">
         <v>48</v>
       </c>
-      <c r="AG43" s="326"/>
-      <c r="AH43" s="326"/>
-      <c r="AI43" s="351" t="s">
+      <c r="AG43" s="325"/>
+      <c r="AH43" s="325"/>
+      <c r="AI43" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="AJ43" s="326"/>
-      <c r="AK43" s="326"/>
-      <c r="AL43" s="326"/>
-      <c r="AM43" s="326"/>
-      <c r="AN43" s="326"/>
-      <c r="AO43" s="326"/>
-      <c r="AP43" s="326"/>
-      <c r="AQ43" s="352"/>
+      <c r="AJ43" s="325"/>
+      <c r="AK43" s="325"/>
+      <c r="AL43" s="325"/>
+      <c r="AM43" s="325"/>
+      <c r="AN43" s="325"/>
+      <c r="AO43" s="325"/>
+      <c r="AP43" s="325"/>
+      <c r="AQ43" s="328"/>
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:43">
-      <c r="A44" s="332" t="s">
+      <c r="A44" s="329" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="333"/>
-      <c r="C44" s="333"/>
-      <c r="D44" s="333"/>
-      <c r="E44" s="333"/>
-      <c r="F44" s="333"/>
-      <c r="G44" s="333"/>
-      <c r="H44" s="333"/>
-      <c r="I44" s="333"/>
-      <c r="J44" s="333"/>
-      <c r="K44" s="333"/>
-      <c r="L44" s="333"/>
-      <c r="M44" s="353" t="s">
+      <c r="B44" s="330"/>
+      <c r="C44" s="330"/>
+      <c r="D44" s="330"/>
+      <c r="E44" s="330"/>
+      <c r="F44" s="330"/>
+      <c r="G44" s="330"/>
+      <c r="H44" s="330"/>
+      <c r="I44" s="330"/>
+      <c r="J44" s="330"/>
+      <c r="K44" s="330"/>
+      <c r="L44" s="330"/>
+      <c r="M44" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="N44" s="333"/>
-      <c r="O44" s="333"/>
-      <c r="P44" s="333"/>
-      <c r="Q44" s="333"/>
-      <c r="R44" s="333"/>
-      <c r="S44" s="333"/>
-      <c r="T44" s="333"/>
-      <c r="U44" s="354"/>
-      <c r="V44" s="332" t="s">
+      <c r="N44" s="330"/>
+      <c r="O44" s="330"/>
+      <c r="P44" s="330"/>
+      <c r="Q44" s="330"/>
+      <c r="R44" s="330"/>
+      <c r="S44" s="330"/>
+      <c r="T44" s="330"/>
+      <c r="U44" s="350"/>
+      <c r="V44" s="329" t="s">
         <v>49</v>
       </c>
-      <c r="W44" s="333"/>
-      <c r="X44" s="333"/>
-      <c r="Y44" s="333"/>
-      <c r="Z44" s="333"/>
-      <c r="AA44" s="333"/>
-      <c r="AB44" s="333"/>
-      <c r="AC44" s="333"/>
-      <c r="AD44" s="333"/>
-      <c r="AE44" s="333"/>
-      <c r="AF44" s="333"/>
-      <c r="AG44" s="333"/>
-      <c r="AH44" s="333"/>
-      <c r="AI44" s="353" t="s">
+      <c r="W44" s="330"/>
+      <c r="X44" s="330"/>
+      <c r="Y44" s="330"/>
+      <c r="Z44" s="330"/>
+      <c r="AA44" s="330"/>
+      <c r="AB44" s="330"/>
+      <c r="AC44" s="330"/>
+      <c r="AD44" s="330"/>
+      <c r="AE44" s="330"/>
+      <c r="AF44" s="330"/>
+      <c r="AG44" s="330"/>
+      <c r="AH44" s="330"/>
+      <c r="AI44" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="AJ44" s="333"/>
-      <c r="AK44" s="333"/>
-      <c r="AL44" s="333"/>
-      <c r="AM44" s="333"/>
-      <c r="AN44" s="333"/>
-      <c r="AO44" s="333"/>
-      <c r="AP44" s="333"/>
-      <c r="AQ44" s="354"/>
+      <c r="AJ44" s="330"/>
+      <c r="AK44" s="330"/>
+      <c r="AL44" s="330"/>
+      <c r="AM44" s="330"/>
+      <c r="AN44" s="330"/>
+      <c r="AO44" s="330"/>
+      <c r="AP44" s="330"/>
+      <c r="AQ44" s="350"/>
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:43">
-      <c r="A45" s="332" t="s">
+      <c r="A45" s="329" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="333"/>
-      <c r="C45" s="333"/>
-      <c r="D45" s="333"/>
-      <c r="E45" s="333"/>
-      <c r="F45" s="333"/>
-      <c r="G45" s="333"/>
-      <c r="H45" s="333"/>
-      <c r="I45" s="333"/>
-      <c r="J45" s="333"/>
-      <c r="K45" s="333"/>
-      <c r="L45" s="333"/>
-      <c r="M45" s="353" t="s">
+      <c r="B45" s="330"/>
+      <c r="C45" s="330"/>
+      <c r="D45" s="330"/>
+      <c r="E45" s="330"/>
+      <c r="F45" s="330"/>
+      <c r="G45" s="330"/>
+      <c r="H45" s="330"/>
+      <c r="I45" s="330"/>
+      <c r="J45" s="330"/>
+      <c r="K45" s="330"/>
+      <c r="L45" s="330"/>
+      <c r="M45" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="N45" s="333"/>
-      <c r="O45" s="333"/>
-      <c r="P45" s="333"/>
-      <c r="Q45" s="333"/>
-      <c r="R45" s="333"/>
-      <c r="S45" s="333"/>
-      <c r="T45" s="333"/>
-      <c r="U45" s="354"/>
-      <c r="V45" s="332" t="s">
+      <c r="N45" s="330"/>
+      <c r="O45" s="330"/>
+      <c r="P45" s="330"/>
+      <c r="Q45" s="330"/>
+      <c r="R45" s="330"/>
+      <c r="S45" s="330"/>
+      <c r="T45" s="330"/>
+      <c r="U45" s="350"/>
+      <c r="V45" s="329" t="s">
         <v>51</v>
       </c>
-      <c r="W45" s="333"/>
-      <c r="X45" s="333"/>
-      <c r="Y45" s="333"/>
-      <c r="Z45" s="333"/>
-      <c r="AA45" s="333"/>
-      <c r="AB45" s="333"/>
-      <c r="AC45" s="333"/>
-      <c r="AD45" s="333"/>
-      <c r="AE45" s="333"/>
-      <c r="AF45" s="333"/>
-      <c r="AG45" s="333"/>
-      <c r="AH45" s="333"/>
-      <c r="AI45" s="353" t="s">
+      <c r="W45" s="330"/>
+      <c r="X45" s="330"/>
+      <c r="Y45" s="330"/>
+      <c r="Z45" s="330"/>
+      <c r="AA45" s="330"/>
+      <c r="AB45" s="330"/>
+      <c r="AC45" s="330"/>
+      <c r="AD45" s="330"/>
+      <c r="AE45" s="330"/>
+      <c r="AF45" s="330"/>
+      <c r="AG45" s="330"/>
+      <c r="AH45" s="330"/>
+      <c r="AI45" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="AJ45" s="333"/>
-      <c r="AK45" s="333"/>
-      <c r="AL45" s="333"/>
-      <c r="AM45" s="333"/>
-      <c r="AN45" s="333"/>
-      <c r="AO45" s="333"/>
-      <c r="AP45" s="333"/>
-      <c r="AQ45" s="354"/>
+      <c r="AJ45" s="330"/>
+      <c r="AK45" s="330"/>
+      <c r="AL45" s="330"/>
+      <c r="AM45" s="330"/>
+      <c r="AN45" s="330"/>
+      <c r="AO45" s="330"/>
+      <c r="AP45" s="330"/>
+      <c r="AQ45" s="350"/>
     </row>
     <row r="46" ht="12" customHeight="1" spans="1:43">
-      <c r="A46" s="332" t="s">
+      <c r="A46" s="329" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="333"/>
-      <c r="C46" s="333"/>
-      <c r="D46" s="333"/>
-      <c r="E46" s="333"/>
-      <c r="F46" s="333"/>
-      <c r="G46" s="333"/>
-      <c r="H46" s="333"/>
-      <c r="I46" s="333"/>
-      <c r="J46" s="333"/>
-      <c r="K46" s="333"/>
-      <c r="L46" s="333"/>
-      <c r="M46" s="353" t="s">
+      <c r="B46" s="330"/>
+      <c r="C46" s="330"/>
+      <c r="D46" s="330"/>
+      <c r="E46" s="330"/>
+      <c r="F46" s="330"/>
+      <c r="G46" s="330"/>
+      <c r="H46" s="330"/>
+      <c r="I46" s="330"/>
+      <c r="J46" s="330"/>
+      <c r="K46" s="330"/>
+      <c r="L46" s="330"/>
+      <c r="M46" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="N46" s="333"/>
-      <c r="O46" s="333"/>
-      <c r="P46" s="333"/>
-      <c r="Q46" s="333"/>
-      <c r="R46" s="333"/>
-      <c r="S46" s="333"/>
-      <c r="T46" s="333"/>
-      <c r="U46" s="354"/>
-      <c r="V46" s="332" t="s">
+      <c r="N46" s="330"/>
+      <c r="O46" s="330"/>
+      <c r="P46" s="330"/>
+      <c r="Q46" s="330"/>
+      <c r="R46" s="330"/>
+      <c r="S46" s="330"/>
+      <c r="T46" s="330"/>
+      <c r="U46" s="350"/>
+      <c r="V46" s="329" t="s">
         <v>53</v>
       </c>
-      <c r="W46" s="333"/>
-      <c r="X46" s="333"/>
-      <c r="Y46" s="333"/>
-      <c r="Z46" s="333"/>
-      <c r="AA46" s="333"/>
-      <c r="AB46" s="333"/>
-      <c r="AC46" s="333"/>
-      <c r="AD46" s="333"/>
-      <c r="AE46" s="333"/>
-      <c r="AF46" s="333"/>
-      <c r="AG46" s="333"/>
-      <c r="AH46" s="333"/>
-      <c r="AI46" s="353" t="s">
+      <c r="W46" s="330"/>
+      <c r="X46" s="330"/>
+      <c r="Y46" s="330"/>
+      <c r="Z46" s="330"/>
+      <c r="AA46" s="330"/>
+      <c r="AB46" s="330"/>
+      <c r="AC46" s="330"/>
+      <c r="AD46" s="330"/>
+      <c r="AE46" s="330"/>
+      <c r="AF46" s="330"/>
+      <c r="AG46" s="330"/>
+      <c r="AH46" s="330"/>
+      <c r="AI46" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="AJ46" s="333"/>
-      <c r="AK46" s="333"/>
-      <c r="AL46" s="333"/>
-      <c r="AM46" s="333"/>
-      <c r="AN46" s="333"/>
-      <c r="AO46" s="333"/>
-      <c r="AP46" s="333"/>
-      <c r="AQ46" s="354"/>
+      <c r="AJ46" s="330"/>
+      <c r="AK46" s="330"/>
+      <c r="AL46" s="330"/>
+      <c r="AM46" s="330"/>
+      <c r="AN46" s="330"/>
+      <c r="AO46" s="330"/>
+      <c r="AP46" s="330"/>
+      <c r="AQ46" s="350"/>
     </row>
     <row r="47" ht="12" customHeight="1" spans="1:43">
-      <c r="A47" s="332" t="s">
+      <c r="A47" s="329" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="333"/>
-      <c r="C47" s="333"/>
-      <c r="D47" s="353" t="s">
+      <c r="B47" s="330"/>
+      <c r="C47" s="330"/>
+      <c r="D47" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="355"/>
-      <c r="F47" s="355"/>
-      <c r="G47" s="333" t="s">
+      <c r="E47" s="351"/>
+      <c r="F47" s="351"/>
+      <c r="G47" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="333"/>
-      <c r="I47" s="333"/>
-      <c r="J47" s="333"/>
-      <c r="K47" s="333"/>
-      <c r="L47" s="333"/>
-      <c r="M47" s="353" t="s">
+      <c r="H47" s="330"/>
+      <c r="I47" s="330"/>
+      <c r="J47" s="330"/>
+      <c r="K47" s="330"/>
+      <c r="L47" s="330"/>
+      <c r="M47" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="N47" s="333"/>
-      <c r="O47" s="333"/>
-      <c r="P47" s="333"/>
-      <c r="Q47" s="333"/>
-      <c r="R47" s="333"/>
-      <c r="S47" s="333"/>
-      <c r="T47" s="333"/>
-      <c r="U47" s="354"/>
-      <c r="V47" s="332" t="s">
+      <c r="N47" s="330"/>
+      <c r="O47" s="330"/>
+      <c r="P47" s="330"/>
+      <c r="Q47" s="330"/>
+      <c r="R47" s="330"/>
+      <c r="S47" s="330"/>
+      <c r="T47" s="330"/>
+      <c r="U47" s="350"/>
+      <c r="V47" s="329" t="s">
         <v>54</v>
       </c>
-      <c r="W47" s="333"/>
-      <c r="X47" s="333"/>
-      <c r="Y47" s="333"/>
-      <c r="Z47" s="333" t="s">
+      <c r="W47" s="330"/>
+      <c r="X47" s="330"/>
+      <c r="Y47" s="330"/>
+      <c r="Z47" s="330" t="s">
         <v>15</v>
       </c>
-      <c r="AA47" s="356"/>
-      <c r="AB47" s="356"/>
-      <c r="AC47" s="333" t="s">
+      <c r="AA47" s="352"/>
+      <c r="AB47" s="352"/>
+      <c r="AC47" s="330" t="s">
         <v>55</v>
       </c>
-      <c r="AD47" s="333"/>
-      <c r="AE47" s="333"/>
-      <c r="AF47" s="333"/>
-      <c r="AG47" s="333"/>
-      <c r="AH47" s="333"/>
-      <c r="AI47" s="353" t="s">
+      <c r="AD47" s="330"/>
+      <c r="AE47" s="330"/>
+      <c r="AF47" s="330"/>
+      <c r="AG47" s="330"/>
+      <c r="AH47" s="330"/>
+      <c r="AI47" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="AJ47" s="333"/>
-      <c r="AK47" s="333"/>
-      <c r="AL47" s="333"/>
-      <c r="AM47" s="333"/>
-      <c r="AN47" s="333"/>
-      <c r="AO47" s="333"/>
-      <c r="AP47" s="333"/>
-      <c r="AQ47" s="354"/>
+      <c r="AJ47" s="330"/>
+      <c r="AK47" s="330"/>
+      <c r="AL47" s="330"/>
+      <c r="AM47" s="330"/>
+      <c r="AN47" s="330"/>
+      <c r="AO47" s="330"/>
+      <c r="AP47" s="330"/>
+      <c r="AQ47" s="350"/>
     </row>
     <row r="48" ht="12" customHeight="1" spans="1:43">
-      <c r="A48" s="357" t="s">
+      <c r="A48" s="353" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="358"/>
-      <c r="C48" s="358"/>
-      <c r="D48" s="358"/>
-      <c r="E48" s="358"/>
-      <c r="F48" s="358"/>
-      <c r="G48" s="358"/>
-      <c r="H48" s="358"/>
-      <c r="I48" s="358"/>
-      <c r="J48" s="358"/>
-      <c r="K48" s="358"/>
-      <c r="L48" s="358"/>
-      <c r="M48" s="359" t="s">
+      <c r="B48" s="354"/>
+      <c r="C48" s="354"/>
+      <c r="D48" s="354"/>
+      <c r="E48" s="354"/>
+      <c r="F48" s="354"/>
+      <c r="G48" s="354"/>
+      <c r="H48" s="354"/>
+      <c r="I48" s="354"/>
+      <c r="J48" s="354"/>
+      <c r="K48" s="354"/>
+      <c r="L48" s="354"/>
+      <c r="M48" s="355" t="s">
         <v>15</v>
       </c>
-      <c r="N48" s="359"/>
-      <c r="O48" s="359"/>
-      <c r="P48" s="359"/>
-      <c r="Q48" s="359"/>
-      <c r="R48" s="359"/>
-      <c r="S48" s="359"/>
-      <c r="T48" s="359"/>
-      <c r="U48" s="360"/>
-      <c r="V48" s="357" t="s">
+      <c r="N48" s="355"/>
+      <c r="O48" s="355"/>
+      <c r="P48" s="355"/>
+      <c r="Q48" s="355"/>
+      <c r="R48" s="355"/>
+      <c r="S48" s="355"/>
+      <c r="T48" s="355"/>
+      <c r="U48" s="356"/>
+      <c r="V48" s="353" t="s">
         <v>56</v>
       </c>
-      <c r="W48" s="333"/>
-      <c r="X48" s="333"/>
-      <c r="Y48" s="333"/>
-      <c r="Z48" s="333"/>
-      <c r="AA48" s="333"/>
-      <c r="AB48" s="333"/>
-      <c r="AC48" s="333"/>
-      <c r="AD48" s="333"/>
-      <c r="AE48" s="333"/>
-      <c r="AF48" s="333"/>
-      <c r="AG48" s="333"/>
-      <c r="AH48" s="333"/>
-      <c r="AI48" s="353" t="s">
+      <c r="W48" s="330"/>
+      <c r="X48" s="330"/>
+      <c r="Y48" s="330"/>
+      <c r="Z48" s="330"/>
+      <c r="AA48" s="330"/>
+      <c r="AB48" s="330"/>
+      <c r="AC48" s="330"/>
+      <c r="AD48" s="330"/>
+      <c r="AE48" s="330"/>
+      <c r="AF48" s="330"/>
+      <c r="AG48" s="330"/>
+      <c r="AH48" s="330"/>
+      <c r="AI48" s="349" t="s">
         <v>15</v>
       </c>
-      <c r="AJ48" s="358"/>
-      <c r="AK48" s="358"/>
-      <c r="AL48" s="358"/>
-      <c r="AM48" s="358"/>
-      <c r="AN48" s="358"/>
-      <c r="AO48" s="358"/>
-      <c r="AP48" s="358"/>
-      <c r="AQ48" s="361"/>
+      <c r="AJ48" s="354"/>
+      <c r="AK48" s="354"/>
+      <c r="AL48" s="354"/>
+      <c r="AM48" s="354"/>
+      <c r="AN48" s="354"/>
+      <c r="AO48" s="354"/>
+      <c r="AP48" s="354"/>
+      <c r="AQ48" s="357"/>
     </row>
     <row r="49" ht="12" customHeight="1" spans="1:43">
-      <c r="A49" s="362"/>
-      <c r="B49" s="332" t="s">
+      <c r="A49" s="358"/>
+      <c r="B49" s="329" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="333"/>
-      <c r="D49" s="333"/>
-      <c r="E49" s="333"/>
-      <c r="F49" s="333"/>
-      <c r="G49" s="333"/>
-      <c r="H49" s="333"/>
-      <c r="I49" s="333"/>
-      <c r="J49" s="333"/>
-      <c r="K49" s="333"/>
-      <c r="L49" s="333"/>
-      <c r="M49" s="333"/>
-      <c r="N49" s="333"/>
-      <c r="O49" s="333"/>
-      <c r="P49" s="333"/>
-      <c r="Q49" s="333"/>
-      <c r="R49" s="333"/>
-      <c r="S49" s="333"/>
-      <c r="T49" s="333"/>
-      <c r="U49" s="354"/>
-      <c r="V49" s="363"/>
-      <c r="W49" s="325" t="s">
+      <c r="C49" s="330"/>
+      <c r="D49" s="330"/>
+      <c r="E49" s="330"/>
+      <c r="F49" s="330"/>
+      <c r="G49" s="330"/>
+      <c r="H49" s="330"/>
+      <c r="I49" s="330"/>
+      <c r="J49" s="330"/>
+      <c r="K49" s="330"/>
+      <c r="L49" s="330"/>
+      <c r="M49" s="330"/>
+      <c r="N49" s="330"/>
+      <c r="O49" s="330"/>
+      <c r="P49" s="330"/>
+      <c r="Q49" s="330"/>
+      <c r="R49" s="330"/>
+      <c r="S49" s="330"/>
+      <c r="T49" s="330"/>
+      <c r="U49" s="350"/>
+      <c r="V49" s="359"/>
+      <c r="W49" s="324" t="s">
         <v>57</v>
       </c>
-      <c r="X49" s="326"/>
-      <c r="Y49" s="326"/>
-      <c r="Z49" s="326"/>
-      <c r="AA49" s="326"/>
-      <c r="AB49" s="326"/>
-      <c r="AC49" s="326"/>
-      <c r="AD49" s="326"/>
-      <c r="AE49" s="326"/>
-      <c r="AF49" s="326"/>
-      <c r="AG49" s="326"/>
-      <c r="AH49" s="326"/>
-      <c r="AI49" s="326"/>
-      <c r="AJ49" s="326"/>
-      <c r="AK49" s="326"/>
-      <c r="AL49" s="326"/>
-      <c r="AM49" s="326"/>
-      <c r="AN49" s="326"/>
-      <c r="AO49" s="326"/>
-      <c r="AP49" s="326"/>
-      <c r="AQ49" s="352"/>
+      <c r="X49" s="325"/>
+      <c r="Y49" s="325"/>
+      <c r="Z49" s="325"/>
+      <c r="AA49" s="325"/>
+      <c r="AB49" s="325"/>
+      <c r="AC49" s="325"/>
+      <c r="AD49" s="325"/>
+      <c r="AE49" s="325"/>
+      <c r="AF49" s="325"/>
+      <c r="AG49" s="325"/>
+      <c r="AH49" s="325"/>
+      <c r="AI49" s="325"/>
+      <c r="AJ49" s="325"/>
+      <c r="AK49" s="325"/>
+      <c r="AL49" s="325"/>
+      <c r="AM49" s="325"/>
+      <c r="AN49" s="325"/>
+      <c r="AO49" s="325"/>
+      <c r="AP49" s="325"/>
+      <c r="AQ49" s="328"/>
     </row>
     <row r="50" ht="12" customHeight="1" spans="1:43">
-      <c r="A50" s="364"/>
-      <c r="B50" s="340" t="s">
+      <c r="A50" s="360"/>
+      <c r="B50" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
-      <c r="G50" s="341"/>
-      <c r="H50" s="341"/>
-      <c r="I50" s="341"/>
-      <c r="J50" s="341"/>
-      <c r="K50" s="341"/>
-      <c r="L50" s="341"/>
-      <c r="M50" s="341"/>
-      <c r="N50" s="341"/>
-      <c r="O50" s="341"/>
-      <c r="P50" s="341"/>
-      <c r="Q50" s="341"/>
-      <c r="R50" s="341"/>
-      <c r="S50" s="341"/>
-      <c r="T50" s="341"/>
-      <c r="U50" s="344"/>
-      <c r="V50" s="365"/>
-      <c r="W50" s="340" t="s">
+      <c r="C50" s="337"/>
+      <c r="D50" s="337"/>
+      <c r="E50" s="337"/>
+      <c r="F50" s="337"/>
+      <c r="G50" s="337"/>
+      <c r="H50" s="337"/>
+      <c r="I50" s="337"/>
+      <c r="J50" s="337"/>
+      <c r="K50" s="337"/>
+      <c r="L50" s="337"/>
+      <c r="M50" s="337"/>
+      <c r="N50" s="337"/>
+      <c r="O50" s="337"/>
+      <c r="P50" s="337"/>
+      <c r="Q50" s="337"/>
+      <c r="R50" s="337"/>
+      <c r="S50" s="337"/>
+      <c r="T50" s="337"/>
+      <c r="U50" s="340"/>
+      <c r="V50" s="361"/>
+      <c r="W50" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="X50" s="341"/>
-      <c r="Y50" s="341"/>
-      <c r="Z50" s="341"/>
-      <c r="AA50" s="341"/>
-      <c r="AB50" s="341"/>
-      <c r="AC50" s="341"/>
-      <c r="AD50" s="341"/>
-      <c r="AE50" s="341"/>
-      <c r="AF50" s="341"/>
-      <c r="AG50" s="341"/>
-      <c r="AH50" s="341"/>
-      <c r="AI50" s="341"/>
-      <c r="AJ50" s="341"/>
-      <c r="AK50" s="341"/>
-      <c r="AL50" s="341"/>
-      <c r="AM50" s="341"/>
-      <c r="AN50" s="341"/>
-      <c r="AO50" s="341"/>
-      <c r="AP50" s="341"/>
-      <c r="AQ50" s="344"/>
+      <c r="X50" s="337"/>
+      <c r="Y50" s="337"/>
+      <c r="Z50" s="337"/>
+      <c r="AA50" s="337"/>
+      <c r="AB50" s="337"/>
+      <c r="AC50" s="337"/>
+      <c r="AD50" s="337"/>
+      <c r="AE50" s="337"/>
+      <c r="AF50" s="337"/>
+      <c r="AG50" s="337"/>
+      <c r="AH50" s="337"/>
+      <c r="AI50" s="337"/>
+      <c r="AJ50" s="337"/>
+      <c r="AK50" s="337"/>
+      <c r="AL50" s="337"/>
+      <c r="AM50" s="337"/>
+      <c r="AN50" s="337"/>
+      <c r="AO50" s="337"/>
+      <c r="AP50" s="337"/>
+      <c r="AQ50" s="340"/>
     </row>
     <row r="51" ht="12" customHeight="1" spans="1:43">
-      <c r="A51" s="364"/>
-      <c r="B51" s="340" t="s">
+      <c r="A51" s="360"/>
+      <c r="B51" s="336" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="341"/>
-      <c r="D51" s="341"/>
-      <c r="E51" s="341"/>
-      <c r="F51" s="341"/>
-      <c r="G51" s="341"/>
-      <c r="H51" s="341"/>
-      <c r="I51" s="341"/>
-      <c r="J51" s="341"/>
-      <c r="K51" s="341"/>
-      <c r="L51" s="341"/>
-      <c r="M51" s="341"/>
-      <c r="N51" s="341"/>
-      <c r="O51" s="341"/>
-      <c r="P51" s="341"/>
-      <c r="Q51" s="341"/>
-      <c r="R51" s="341"/>
-      <c r="S51" s="341"/>
-      <c r="T51" s="341"/>
-      <c r="U51" s="344"/>
-      <c r="V51" s="365"/>
-      <c r="W51" s="340" t="s">
+      <c r="C51" s="337"/>
+      <c r="D51" s="337"/>
+      <c r="E51" s="337"/>
+      <c r="F51" s="337"/>
+      <c r="G51" s="337"/>
+      <c r="H51" s="337"/>
+      <c r="I51" s="337"/>
+      <c r="J51" s="337"/>
+      <c r="K51" s="337"/>
+      <c r="L51" s="337"/>
+      <c r="M51" s="337"/>
+      <c r="N51" s="337"/>
+      <c r="O51" s="337"/>
+      <c r="P51" s="337"/>
+      <c r="Q51" s="337"/>
+      <c r="R51" s="337"/>
+      <c r="S51" s="337"/>
+      <c r="T51" s="337"/>
+      <c r="U51" s="340"/>
+      <c r="V51" s="361"/>
+      <c r="W51" s="336" t="s">
         <v>59</v>
       </c>
-      <c r="X51" s="341"/>
-      <c r="Y51" s="341"/>
-      <c r="Z51" s="341"/>
-      <c r="AA51" s="341"/>
-      <c r="AB51" s="341"/>
-      <c r="AC51" s="341"/>
-      <c r="AD51" s="341"/>
-      <c r="AE51" s="341"/>
-      <c r="AF51" s="341"/>
-      <c r="AG51" s="341"/>
-      <c r="AH51" s="341"/>
-      <c r="AI51" s="341"/>
-      <c r="AJ51" s="341"/>
-      <c r="AK51" s="341"/>
-      <c r="AL51" s="341"/>
-      <c r="AM51" s="341"/>
-      <c r="AN51" s="341"/>
-      <c r="AO51" s="341"/>
-      <c r="AP51" s="341"/>
-      <c r="AQ51" s="344"/>
+      <c r="X51" s="337"/>
+      <c r="Y51" s="337"/>
+      <c r="Z51" s="337"/>
+      <c r="AA51" s="337"/>
+      <c r="AB51" s="337"/>
+      <c r="AC51" s="337"/>
+      <c r="AD51" s="337"/>
+      <c r="AE51" s="337"/>
+      <c r="AF51" s="337"/>
+      <c r="AG51" s="337"/>
+      <c r="AH51" s="337"/>
+      <c r="AI51" s="337"/>
+      <c r="AJ51" s="337"/>
+      <c r="AK51" s="337"/>
+      <c r="AL51" s="337"/>
+      <c r="AM51" s="337"/>
+      <c r="AN51" s="337"/>
+      <c r="AO51" s="337"/>
+      <c r="AP51" s="337"/>
+      <c r="AQ51" s="340"/>
     </row>
     <row r="52" ht="12" customHeight="1" spans="1:43">
-      <c r="A52" s="364"/>
-      <c r="B52" s="340" t="s">
+      <c r="A52" s="360"/>
+      <c r="B52" s="336" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="341"/>
-      <c r="D52" s="341"/>
-      <c r="E52" s="341"/>
-      <c r="F52" s="341"/>
-      <c r="G52" s="341"/>
-      <c r="H52" s="341"/>
-      <c r="I52" s="341"/>
-      <c r="J52" s="341"/>
-      <c r="K52" s="341"/>
-      <c r="L52" s="341"/>
-      <c r="M52" s="341"/>
-      <c r="N52" s="341"/>
-      <c r="O52" s="341" t="s">
+      <c r="C52" s="337"/>
+      <c r="D52" s="337"/>
+      <c r="E52" s="337"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="337"/>
+      <c r="H52" s="337"/>
+      <c r="I52" s="337"/>
+      <c r="J52" s="337"/>
+      <c r="K52" s="337"/>
+      <c r="L52" s="337"/>
+      <c r="M52" s="337"/>
+      <c r="N52" s="337"/>
+      <c r="O52" s="337" t="s">
         <v>61</v>
       </c>
-      <c r="P52" s="341"/>
-      <c r="Q52" s="341"/>
-      <c r="R52" s="341"/>
-      <c r="S52" s="341"/>
-      <c r="T52" s="341"/>
-      <c r="U52" s="344"/>
-      <c r="V52" s="365"/>
-      <c r="W52" s="340" t="s">
+      <c r="P52" s="337"/>
+      <c r="Q52" s="337"/>
+      <c r="R52" s="337"/>
+      <c r="S52" s="337"/>
+      <c r="T52" s="337"/>
+      <c r="U52" s="340"/>
+      <c r="V52" s="361"/>
+      <c r="W52" s="336" t="s">
         <v>62</v>
       </c>
-      <c r="X52" s="341"/>
-      <c r="Y52" s="341"/>
-      <c r="Z52" s="341"/>
-      <c r="AA52" s="341"/>
-      <c r="AB52" s="341"/>
-      <c r="AC52" s="341"/>
-      <c r="AD52" s="341"/>
-      <c r="AE52" s="341"/>
-      <c r="AF52" s="341"/>
-      <c r="AG52" s="341"/>
-      <c r="AH52" s="341"/>
-      <c r="AI52" s="341"/>
-      <c r="AJ52" s="341"/>
-      <c r="AK52" s="341"/>
-      <c r="AL52" s="341"/>
-      <c r="AM52" s="341"/>
-      <c r="AN52" s="341"/>
-      <c r="AO52" s="341"/>
-      <c r="AP52" s="341"/>
-      <c r="AQ52" s="344"/>
+      <c r="X52" s="337"/>
+      <c r="Y52" s="337"/>
+      <c r="Z52" s="337"/>
+      <c r="AA52" s="337"/>
+      <c r="AB52" s="337"/>
+      <c r="AC52" s="337"/>
+      <c r="AD52" s="337"/>
+      <c r="AE52" s="337"/>
+      <c r="AF52" s="337"/>
+      <c r="AG52" s="337"/>
+      <c r="AH52" s="337"/>
+      <c r="AI52" s="337"/>
+      <c r="AJ52" s="337"/>
+      <c r="AK52" s="337"/>
+      <c r="AL52" s="337"/>
+      <c r="AM52" s="337"/>
+      <c r="AN52" s="337"/>
+      <c r="AO52" s="337"/>
+      <c r="AP52" s="337"/>
+      <c r="AQ52" s="340"/>
     </row>
     <row r="53" ht="12" customHeight="1" spans="1:43">
-      <c r="A53" s="364"/>
-      <c r="B53" s="340" t="s">
+      <c r="A53" s="360"/>
+      <c r="B53" s="336" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
-      <c r="G53" s="341"/>
-      <c r="H53" s="341"/>
-      <c r="I53" s="341"/>
-      <c r="J53" s="341"/>
-      <c r="K53" s="341"/>
-      <c r="L53" s="341"/>
-      <c r="M53" s="341"/>
-      <c r="N53" s="341"/>
-      <c r="O53" s="341"/>
-      <c r="P53" s="341"/>
-      <c r="Q53" s="341"/>
-      <c r="R53" s="341"/>
-      <c r="S53" s="341"/>
-      <c r="T53" s="341"/>
-      <c r="U53" s="344"/>
-      <c r="V53" s="365"/>
-      <c r="W53" s="340" t="s">
+      <c r="C53" s="337"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
+      <c r="G53" s="337"/>
+      <c r="H53" s="337"/>
+      <c r="I53" s="337"/>
+      <c r="J53" s="337"/>
+      <c r="K53" s="337"/>
+      <c r="L53" s="337"/>
+      <c r="M53" s="337"/>
+      <c r="N53" s="337"/>
+      <c r="O53" s="337"/>
+      <c r="P53" s="337"/>
+      <c r="Q53" s="337"/>
+      <c r="R53" s="337"/>
+      <c r="S53" s="337"/>
+      <c r="T53" s="337"/>
+      <c r="U53" s="340"/>
+      <c r="V53" s="361"/>
+      <c r="W53" s="336" t="s">
         <v>64</v>
       </c>
-      <c r="X53" s="341"/>
-      <c r="Y53" s="341"/>
-      <c r="Z53" s="341"/>
-      <c r="AA53" s="341"/>
-      <c r="AB53" s="341"/>
-      <c r="AC53" s="341"/>
-      <c r="AD53" s="341"/>
-      <c r="AE53" s="341"/>
-      <c r="AF53" s="341"/>
-      <c r="AG53" s="341"/>
-      <c r="AH53" s="341"/>
-      <c r="AI53" s="341"/>
-      <c r="AJ53" s="341"/>
-      <c r="AK53" s="341"/>
-      <c r="AL53" s="341"/>
-      <c r="AM53" s="341"/>
-      <c r="AN53" s="341"/>
-      <c r="AO53" s="341"/>
-      <c r="AP53" s="341"/>
-      <c r="AQ53" s="344"/>
+      <c r="X53" s="337"/>
+      <c r="Y53" s="337"/>
+      <c r="Z53" s="337"/>
+      <c r="AA53" s="337"/>
+      <c r="AB53" s="337"/>
+      <c r="AC53" s="337"/>
+      <c r="AD53" s="337"/>
+      <c r="AE53" s="337"/>
+      <c r="AF53" s="337"/>
+      <c r="AG53" s="337"/>
+      <c r="AH53" s="337"/>
+      <c r="AI53" s="337"/>
+      <c r="AJ53" s="337"/>
+      <c r="AK53" s="337"/>
+      <c r="AL53" s="337"/>
+      <c r="AM53" s="337"/>
+      <c r="AN53" s="337"/>
+      <c r="AO53" s="337"/>
+      <c r="AP53" s="337"/>
+      <c r="AQ53" s="340"/>
     </row>
     <row r="54" ht="12" customHeight="1" spans="1:43">
-      <c r="A54" s="364"/>
-      <c r="B54" s="340" t="s">
+      <c r="A54" s="360"/>
+      <c r="B54" s="336" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
-      <c r="G54" s="341"/>
-      <c r="H54" s="341"/>
-      <c r="I54" s="341"/>
-      <c r="J54" s="341"/>
-      <c r="K54" s="341"/>
-      <c r="L54" s="341"/>
-      <c r="M54" s="366" t="s">
+      <c r="C54" s="337"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
+      <c r="G54" s="337"/>
+      <c r="H54" s="337"/>
+      <c r="I54" s="337"/>
+      <c r="J54" s="337"/>
+      <c r="K54" s="337"/>
+      <c r="L54" s="337"/>
+      <c r="M54" s="362" t="s">
         <v>15</v>
       </c>
-      <c r="N54" s="341"/>
-      <c r="O54" s="341" t="s">
+      <c r="N54" s="337"/>
+      <c r="O54" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="341"/>
-      <c r="Q54" s="341"/>
-      <c r="R54" s="341"/>
-      <c r="S54" s="341"/>
-      <c r="T54" s="341"/>
-      <c r="U54" s="344"/>
-      <c r="V54" s="365"/>
-      <c r="W54" s="340" t="s">
+      <c r="P54" s="337"/>
+      <c r="Q54" s="337"/>
+      <c r="R54" s="337"/>
+      <c r="S54" s="337"/>
+      <c r="T54" s="337"/>
+      <c r="U54" s="340"/>
+      <c r="V54" s="361"/>
+      <c r="W54" s="336" t="s">
         <v>66</v>
       </c>
-      <c r="X54" s="341"/>
-      <c r="Y54" s="341"/>
-      <c r="Z54" s="341"/>
-      <c r="AA54" s="341"/>
-      <c r="AB54" s="341"/>
-      <c r="AC54" s="341"/>
-      <c r="AD54" s="341"/>
-      <c r="AE54" s="341"/>
-      <c r="AF54" s="341"/>
-      <c r="AG54" s="341"/>
-      <c r="AH54" s="341"/>
-      <c r="AI54" s="366" t="s">
+      <c r="X54" s="337"/>
+      <c r="Y54" s="337"/>
+      <c r="Z54" s="337"/>
+      <c r="AA54" s="337"/>
+      <c r="AB54" s="337"/>
+      <c r="AC54" s="337"/>
+      <c r="AD54" s="337"/>
+      <c r="AE54" s="337"/>
+      <c r="AF54" s="337"/>
+      <c r="AG54" s="337"/>
+      <c r="AH54" s="337"/>
+      <c r="AI54" s="362" t="s">
         <v>15</v>
       </c>
-      <c r="AJ54" s="341"/>
-      <c r="AK54" s="341" t="s">
+      <c r="AJ54" s="337"/>
+      <c r="AK54" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="AL54" s="341"/>
-      <c r="AM54" s="341"/>
-      <c r="AN54" s="341"/>
-      <c r="AO54" s="341"/>
-      <c r="AP54" s="341"/>
-      <c r="AQ54" s="344"/>
+      <c r="AL54" s="337"/>
+      <c r="AM54" s="337"/>
+      <c r="AN54" s="337"/>
+      <c r="AO54" s="337"/>
+      <c r="AP54" s="337"/>
+      <c r="AQ54" s="340"/>
     </row>
     <row r="55" ht="12" customHeight="1" spans="1:43">
-      <c r="A55" s="364"/>
-      <c r="B55" s="340" t="s">
+      <c r="A55" s="360"/>
+      <c r="B55" s="336" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="341"/>
-      <c r="D55" s="341"/>
-      <c r="E55" s="341"/>
-      <c r="F55" s="341"/>
-      <c r="G55" s="341"/>
-      <c r="H55" s="341"/>
-      <c r="I55" s="341"/>
-      <c r="J55" s="341"/>
-      <c r="K55" s="341"/>
-      <c r="L55" s="341"/>
-      <c r="M55" s="366" t="s">
+      <c r="C55" s="337"/>
+      <c r="D55" s="337"/>
+      <c r="E55" s="337"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="337"/>
+      <c r="H55" s="337"/>
+      <c r="I55" s="337"/>
+      <c r="J55" s="337"/>
+      <c r="K55" s="337"/>
+      <c r="L55" s="337"/>
+      <c r="M55" s="362" t="s">
         <v>15</v>
       </c>
-      <c r="N55" s="341"/>
-      <c r="O55" s="341" t="s">
+      <c r="N55" s="337"/>
+      <c r="O55" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="P55" s="341"/>
-      <c r="Q55" s="341"/>
-      <c r="R55" s="341"/>
-      <c r="S55" s="341"/>
-      <c r="T55" s="341"/>
-      <c r="U55" s="344"/>
-      <c r="V55" s="365"/>
-      <c r="W55" s="340" t="s">
+      <c r="P55" s="337"/>
+      <c r="Q55" s="337"/>
+      <c r="R55" s="337"/>
+      <c r="S55" s="337"/>
+      <c r="T55" s="337"/>
+      <c r="U55" s="340"/>
+      <c r="V55" s="361"/>
+      <c r="W55" s="336" t="s">
         <v>68</v>
       </c>
-      <c r="X55" s="341"/>
-      <c r="Y55" s="341"/>
-      <c r="Z55" s="341"/>
-      <c r="AA55" s="341"/>
-      <c r="AB55" s="341"/>
-      <c r="AC55" s="341"/>
-      <c r="AD55" s="341"/>
-      <c r="AE55" s="341"/>
-      <c r="AF55" s="341"/>
-      <c r="AG55" s="341"/>
-      <c r="AH55" s="341"/>
-      <c r="AI55" s="366" t="s">
+      <c r="X55" s="337"/>
+      <c r="Y55" s="337"/>
+      <c r="Z55" s="337"/>
+      <c r="AA55" s="337"/>
+      <c r="AB55" s="337"/>
+      <c r="AC55" s="337"/>
+      <c r="AD55" s="337"/>
+      <c r="AE55" s="337"/>
+      <c r="AF55" s="337"/>
+      <c r="AG55" s="337"/>
+      <c r="AH55" s="337"/>
+      <c r="AI55" s="362" t="s">
         <v>15</v>
       </c>
-      <c r="AJ55" s="341"/>
-      <c r="AK55" s="341" t="s">
+      <c r="AJ55" s="337"/>
+      <c r="AK55" s="337" t="s">
         <v>35</v>
       </c>
-      <c r="AL55" s="341"/>
-      <c r="AM55" s="341"/>
-      <c r="AN55" s="341"/>
-      <c r="AO55" s="341"/>
-      <c r="AP55" s="341"/>
-      <c r="AQ55" s="344"/>
+      <c r="AL55" s="337"/>
+      <c r="AM55" s="337"/>
+      <c r="AN55" s="337"/>
+      <c r="AO55" s="337"/>
+      <c r="AP55" s="337"/>
+      <c r="AQ55" s="340"/>
     </row>
     <row r="56" ht="12" customHeight="1" spans="1:43">
-      <c r="A56" s="364"/>
-      <c r="B56" s="367" t="s">
+      <c r="A56" s="360"/>
+      <c r="B56" s="363" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="368"/>
-      <c r="D56" s="368"/>
-      <c r="E56" s="368"/>
-      <c r="F56" s="368"/>
-      <c r="G56" s="368"/>
-      <c r="H56" s="368"/>
-      <c r="I56" s="368"/>
-      <c r="J56" s="368"/>
-      <c r="K56" s="368"/>
-      <c r="L56" s="368"/>
-      <c r="M56" s="368"/>
-      <c r="N56" s="368"/>
-      <c r="O56" s="368"/>
-      <c r="P56" s="368"/>
-      <c r="Q56" s="368"/>
-      <c r="R56" s="368"/>
-      <c r="S56" s="368"/>
-      <c r="T56" s="368"/>
-      <c r="U56" s="369"/>
-      <c r="V56" s="370"/>
-      <c r="W56" s="367" t="s">
+      <c r="C56" s="364"/>
+      <c r="D56" s="364"/>
+      <c r="E56" s="364"/>
+      <c r="F56" s="364"/>
+      <c r="G56" s="364"/>
+      <c r="H56" s="364"/>
+      <c r="I56" s="364"/>
+      <c r="J56" s="364"/>
+      <c r="K56" s="364"/>
+      <c r="L56" s="364"/>
+      <c r="M56" s="364"/>
+      <c r="N56" s="364"/>
+      <c r="O56" s="364"/>
+      <c r="P56" s="364"/>
+      <c r="Q56" s="364"/>
+      <c r="R56" s="364"/>
+      <c r="S56" s="364"/>
+      <c r="T56" s="364"/>
+      <c r="U56" s="365"/>
+      <c r="V56" s="366"/>
+      <c r="W56" s="363" t="s">
         <v>69</v>
       </c>
-      <c r="X56" s="368"/>
-      <c r="Y56" s="368"/>
-      <c r="Z56" s="368"/>
-      <c r="AA56" s="368"/>
-      <c r="AB56" s="368"/>
-      <c r="AC56" s="368"/>
-      <c r="AD56" s="368"/>
-      <c r="AE56" s="368"/>
-      <c r="AF56" s="368"/>
-      <c r="AG56" s="368"/>
-      <c r="AH56" s="368"/>
-      <c r="AI56" s="368"/>
-      <c r="AJ56" s="368"/>
-      <c r="AK56" s="368"/>
-      <c r="AL56" s="368"/>
-      <c r="AM56" s="368"/>
-      <c r="AN56" s="368"/>
-      <c r="AO56" s="368"/>
-      <c r="AP56" s="368"/>
-      <c r="AQ56" s="369"/>
+      <c r="X56" s="364"/>
+      <c r="Y56" s="364"/>
+      <c r="Z56" s="364"/>
+      <c r="AA56" s="364"/>
+      <c r="AB56" s="364"/>
+      <c r="AC56" s="364"/>
+      <c r="AD56" s="364"/>
+      <c r="AE56" s="364"/>
+      <c r="AF56" s="364"/>
+      <c r="AG56" s="364"/>
+      <c r="AH56" s="364"/>
+      <c r="AI56" s="364"/>
+      <c r="AJ56" s="364"/>
+      <c r="AK56" s="364"/>
+      <c r="AL56" s="364"/>
+      <c r="AM56" s="364"/>
+      <c r="AN56" s="364"/>
+      <c r="AO56" s="364"/>
+      <c r="AP56" s="364"/>
+      <c r="AQ56" s="365"/>
     </row>
     <row r="57" ht="12" customHeight="1" spans="1:43">
-      <c r="A57" s="364"/>
-      <c r="B57" s="367"/>
-      <c r="C57" s="368"/>
-      <c r="D57" s="368"/>
-      <c r="E57" s="368"/>
-      <c r="F57" s="368"/>
-      <c r="G57" s="368"/>
-      <c r="H57" s="368"/>
-      <c r="I57" s="368"/>
-      <c r="J57" s="368"/>
-      <c r="K57" s="368"/>
-      <c r="L57" s="368"/>
-      <c r="M57" s="368"/>
-      <c r="N57" s="368"/>
-      <c r="O57" s="368"/>
-      <c r="P57" s="368"/>
-      <c r="Q57" s="368"/>
-      <c r="R57" s="368"/>
-      <c r="S57" s="368"/>
-      <c r="T57" s="368"/>
-      <c r="U57" s="369"/>
-      <c r="V57" s="371"/>
-      <c r="W57" s="367"/>
-      <c r="X57" s="368"/>
-      <c r="Y57" s="368"/>
-      <c r="Z57" s="368"/>
-      <c r="AA57" s="368"/>
-      <c r="AB57" s="368"/>
-      <c r="AC57" s="368"/>
-      <c r="AD57" s="368"/>
-      <c r="AE57" s="368"/>
-      <c r="AF57" s="368"/>
-      <c r="AG57" s="368"/>
-      <c r="AH57" s="368"/>
-      <c r="AI57" s="368"/>
-      <c r="AJ57" s="368"/>
-      <c r="AK57" s="368"/>
-      <c r="AL57" s="368"/>
-      <c r="AM57" s="368"/>
-      <c r="AN57" s="368"/>
-      <c r="AO57" s="368"/>
-      <c r="AP57" s="368"/>
-      <c r="AQ57" s="369"/>
+      <c r="A57" s="360"/>
+      <c r="B57" s="363"/>
+      <c r="C57" s="364"/>
+      <c r="D57" s="364"/>
+      <c r="E57" s="364"/>
+      <c r="F57" s="364"/>
+      <c r="G57" s="364"/>
+      <c r="H57" s="364"/>
+      <c r="I57" s="364"/>
+      <c r="J57" s="364"/>
+      <c r="K57" s="364"/>
+      <c r="L57" s="364"/>
+      <c r="M57" s="364"/>
+      <c r="N57" s="364"/>
+      <c r="O57" s="364"/>
+      <c r="P57" s="364"/>
+      <c r="Q57" s="364"/>
+      <c r="R57" s="364"/>
+      <c r="S57" s="364"/>
+      <c r="T57" s="364"/>
+      <c r="U57" s="365"/>
+      <c r="V57" s="367"/>
+      <c r="W57" s="363"/>
+      <c r="X57" s="364"/>
+      <c r="Y57" s="364"/>
+      <c r="Z57" s="364"/>
+      <c r="AA57" s="364"/>
+      <c r="AB57" s="364"/>
+      <c r="AC57" s="364"/>
+      <c r="AD57" s="364"/>
+      <c r="AE57" s="364"/>
+      <c r="AF57" s="364"/>
+      <c r="AG57" s="364"/>
+      <c r="AH57" s="364"/>
+      <c r="AI57" s="364"/>
+      <c r="AJ57" s="364"/>
+      <c r="AK57" s="364"/>
+      <c r="AL57" s="364"/>
+      <c r="AM57" s="364"/>
+      <c r="AN57" s="364"/>
+      <c r="AO57" s="364"/>
+      <c r="AP57" s="364"/>
+      <c r="AQ57" s="365"/>
     </row>
     <row r="58" ht="12" customHeight="1" spans="1:43">
-      <c r="A58" s="364"/>
-      <c r="B58" s="340" t="s">
+      <c r="A58" s="360"/>
+      <c r="B58" s="336" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="341"/>
-      <c r="D58" s="341"/>
-      <c r="E58" s="341"/>
-      <c r="F58" s="341"/>
-      <c r="G58" s="341"/>
-      <c r="H58" s="341"/>
-      <c r="I58" s="341"/>
-      <c r="J58" s="341"/>
-      <c r="K58" s="341"/>
-      <c r="L58" s="341"/>
-      <c r="M58" s="341"/>
-      <c r="N58" s="341"/>
-      <c r="O58" s="341"/>
-      <c r="P58" s="341"/>
-      <c r="Q58" s="341"/>
-      <c r="R58" s="341"/>
-      <c r="S58" s="341"/>
-      <c r="T58" s="341"/>
-      <c r="U58" s="344"/>
-      <c r="V58" s="365"/>
-      <c r="W58" s="340" t="s">
+      <c r="C58" s="337"/>
+      <c r="D58" s="337"/>
+      <c r="E58" s="337"/>
+      <c r="F58" s="337"/>
+      <c r="G58" s="337"/>
+      <c r="H58" s="337"/>
+      <c r="I58" s="337"/>
+      <c r="J58" s="337"/>
+      <c r="K58" s="337"/>
+      <c r="L58" s="337"/>
+      <c r="M58" s="337"/>
+      <c r="N58" s="337"/>
+      <c r="O58" s="337"/>
+      <c r="P58" s="337"/>
+      <c r="Q58" s="337"/>
+      <c r="R58" s="337"/>
+      <c r="S58" s="337"/>
+      <c r="T58" s="337"/>
+      <c r="U58" s="340"/>
+      <c r="V58" s="361"/>
+      <c r="W58" s="336" t="s">
         <v>70</v>
       </c>
-      <c r="X58" s="341"/>
-      <c r="Y58" s="341"/>
-      <c r="Z58" s="341"/>
-      <c r="AA58" s="341"/>
-      <c r="AB58" s="341"/>
-      <c r="AC58" s="341"/>
-      <c r="AD58" s="341"/>
-      <c r="AE58" s="341"/>
-      <c r="AF58" s="341"/>
-      <c r="AG58" s="341"/>
-      <c r="AH58" s="341"/>
-      <c r="AI58" s="341"/>
-      <c r="AJ58" s="341"/>
-      <c r="AK58" s="341"/>
-      <c r="AL58" s="341"/>
-      <c r="AM58" s="341"/>
-      <c r="AN58" s="341"/>
-      <c r="AO58" s="341"/>
-      <c r="AP58" s="341"/>
-      <c r="AQ58" s="344"/>
+      <c r="X58" s="337"/>
+      <c r="Y58" s="337"/>
+      <c r="Z58" s="337"/>
+      <c r="AA58" s="337"/>
+      <c r="AB58" s="337"/>
+      <c r="AC58" s="337"/>
+      <c r="AD58" s="337"/>
+      <c r="AE58" s="337"/>
+      <c r="AF58" s="337"/>
+      <c r="AG58" s="337"/>
+      <c r="AH58" s="337"/>
+      <c r="AI58" s="337"/>
+      <c r="AJ58" s="337"/>
+      <c r="AK58" s="337"/>
+      <c r="AL58" s="337"/>
+      <c r="AM58" s="337"/>
+      <c r="AN58" s="337"/>
+      <c r="AO58" s="337"/>
+      <c r="AP58" s="337"/>
+      <c r="AQ58" s="340"/>
     </row>
     <row r="59" ht="12" customHeight="1" spans="1:43">
-      <c r="A59" s="364"/>
-      <c r="B59" s="340" t="s">
+      <c r="A59" s="360"/>
+      <c r="B59" s="336" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="341"/>
-      <c r="D59" s="341"/>
-      <c r="E59" s="341"/>
-      <c r="F59" s="341"/>
-      <c r="G59" s="341"/>
-      <c r="H59" s="341"/>
-      <c r="I59" s="341"/>
-      <c r="J59" s="341"/>
-      <c r="K59" s="341"/>
-      <c r="L59" s="341"/>
-      <c r="M59" s="341"/>
-      <c r="N59" s="341"/>
-      <c r="O59" s="341"/>
-      <c r="P59" s="341"/>
-      <c r="Q59" s="341"/>
-      <c r="R59" s="341"/>
-      <c r="S59" s="341"/>
-      <c r="T59" s="341"/>
-      <c r="U59" s="344"/>
-      <c r="V59" s="365"/>
-      <c r="W59" s="340" t="s">
+      <c r="C59" s="337"/>
+      <c r="D59" s="337"/>
+      <c r="E59" s="337"/>
+      <c r="F59" s="337"/>
+      <c r="G59" s="337"/>
+      <c r="H59" s="337"/>
+      <c r="I59" s="337"/>
+      <c r="J59" s="337"/>
+      <c r="K59" s="337"/>
+      <c r="L59" s="337"/>
+      <c r="M59" s="337"/>
+      <c r="N59" s="337"/>
+      <c r="O59" s="337"/>
+      <c r="P59" s="337"/>
+      <c r="Q59" s="337"/>
+      <c r="R59" s="337"/>
+      <c r="S59" s="337"/>
+      <c r="T59" s="337"/>
+      <c r="U59" s="340"/>
+      <c r="V59" s="361"/>
+      <c r="W59" s="336" t="s">
         <v>72</v>
       </c>
-      <c r="X59" s="341"/>
-      <c r="Y59" s="341"/>
-      <c r="Z59" s="341"/>
-      <c r="AA59" s="341"/>
-      <c r="AB59" s="341"/>
-      <c r="AC59" s="341"/>
-      <c r="AD59" s="341"/>
-      <c r="AE59" s="341"/>
-      <c r="AF59" s="341"/>
-      <c r="AG59" s="341"/>
-      <c r="AH59" s="341"/>
-      <c r="AI59" s="341"/>
-      <c r="AJ59" s="341"/>
-      <c r="AK59" s="341"/>
-      <c r="AL59" s="341"/>
-      <c r="AM59" s="341"/>
-      <c r="AN59" s="341"/>
-      <c r="AO59" s="341"/>
-      <c r="AP59" s="341"/>
-      <c r="AQ59" s="344"/>
+      <c r="X59" s="337"/>
+      <c r="Y59" s="337"/>
+      <c r="Z59" s="337"/>
+      <c r="AA59" s="337"/>
+      <c r="AB59" s="337"/>
+      <c r="AC59" s="337"/>
+      <c r="AD59" s="337"/>
+      <c r="AE59" s="337"/>
+      <c r="AF59" s="337"/>
+      <c r="AG59" s="337"/>
+      <c r="AH59" s="337"/>
+      <c r="AI59" s="337"/>
+      <c r="AJ59" s="337"/>
+      <c r="AK59" s="337"/>
+      <c r="AL59" s="337"/>
+      <c r="AM59" s="337"/>
+      <c r="AN59" s="337"/>
+      <c r="AO59" s="337"/>
+      <c r="AP59" s="337"/>
+      <c r="AQ59" s="340"/>
     </row>
     <row r="60" ht="12" customHeight="1" spans="1:43">
-      <c r="A60" s="364"/>
-      <c r="B60" s="340" t="s">
+      <c r="A60" s="360"/>
+      <c r="B60" s="336" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="341"/>
-      <c r="D60" s="341"/>
-      <c r="E60" s="341"/>
-      <c r="F60" s="341"/>
-      <c r="G60" s="341"/>
-      <c r="H60" s="341"/>
-      <c r="I60" s="341"/>
-      <c r="J60" s="341"/>
-      <c r="K60" s="341"/>
-      <c r="L60" s="341"/>
-      <c r="M60" s="341"/>
-      <c r="N60" s="341"/>
-      <c r="O60" s="341"/>
-      <c r="P60" s="341"/>
-      <c r="Q60" s="341"/>
-      <c r="R60" s="341"/>
-      <c r="S60" s="341"/>
-      <c r="T60" s="341"/>
-      <c r="U60" s="344"/>
-      <c r="V60" s="365"/>
-      <c r="W60" s="340" t="s">
+      <c r="C60" s="337"/>
+      <c r="D60" s="337"/>
+      <c r="E60" s="337"/>
+      <c r="F60" s="337"/>
+      <c r="G60" s="337"/>
+      <c r="H60" s="337"/>
+      <c r="I60" s="337"/>
+      <c r="J60" s="337"/>
+      <c r="K60" s="337"/>
+      <c r="L60" s="337"/>
+      <c r="M60" s="337"/>
+      <c r="N60" s="337"/>
+      <c r="O60" s="337"/>
+      <c r="P60" s="337"/>
+      <c r="Q60" s="337"/>
+      <c r="R60" s="337"/>
+      <c r="S60" s="337"/>
+      <c r="T60" s="337"/>
+      <c r="U60" s="340"/>
+      <c r="V60" s="361"/>
+      <c r="W60" s="336" t="s">
         <v>73</v>
       </c>
-      <c r="X60" s="341"/>
-      <c r="Y60" s="341"/>
-      <c r="Z60" s="341"/>
-      <c r="AA60" s="341"/>
-      <c r="AB60" s="341"/>
-      <c r="AC60" s="341"/>
-      <c r="AD60" s="341"/>
-      <c r="AE60" s="341"/>
-      <c r="AF60" s="341"/>
-      <c r="AG60" s="341"/>
-      <c r="AH60" s="341"/>
-      <c r="AI60" s="341"/>
-      <c r="AJ60" s="341"/>
-      <c r="AK60" s="341"/>
-      <c r="AL60" s="341"/>
-      <c r="AM60" s="341"/>
-      <c r="AN60" s="341"/>
-      <c r="AO60" s="341"/>
-      <c r="AP60" s="341"/>
-      <c r="AQ60" s="344"/>
+      <c r="X60" s="337"/>
+      <c r="Y60" s="337"/>
+      <c r="Z60" s="337"/>
+      <c r="AA60" s="337"/>
+      <c r="AB60" s="337"/>
+      <c r="AC60" s="337"/>
+      <c r="AD60" s="337"/>
+      <c r="AE60" s="337"/>
+      <c r="AF60" s="337"/>
+      <c r="AG60" s="337"/>
+      <c r="AH60" s="337"/>
+      <c r="AI60" s="337"/>
+      <c r="AJ60" s="337"/>
+      <c r="AK60" s="337"/>
+      <c r="AL60" s="337"/>
+      <c r="AM60" s="337"/>
+      <c r="AN60" s="337"/>
+      <c r="AO60" s="337"/>
+      <c r="AP60" s="337"/>
+      <c r="AQ60" s="340"/>
     </row>
     <row r="61" ht="12" customHeight="1" spans="1:43">
-      <c r="A61" s="363"/>
-      <c r="B61" s="357" t="s">
+      <c r="A61" s="359"/>
+      <c r="B61" s="353" t="s">
         <v>74</v>
       </c>
-      <c r="C61" s="358"/>
-      <c r="D61" s="358"/>
-      <c r="E61" s="358"/>
-      <c r="F61" s="358"/>
-      <c r="G61" s="358"/>
-      <c r="H61" s="358"/>
-      <c r="I61" s="358"/>
-      <c r="J61" s="358"/>
-      <c r="K61" s="358"/>
-      <c r="L61" s="358"/>
-      <c r="M61" s="358"/>
-      <c r="N61" s="358"/>
-      <c r="O61" s="358"/>
-      <c r="P61" s="358"/>
-      <c r="Q61" s="358"/>
-      <c r="R61" s="358"/>
-      <c r="S61" s="358"/>
-      <c r="T61" s="358"/>
-      <c r="U61" s="361"/>
-      <c r="V61" s="372"/>
-      <c r="W61" s="357" t="s">
-        <v>74</v>
-      </c>
-      <c r="X61" s="358"/>
-      <c r="Y61" s="358"/>
-      <c r="Z61" s="358"/>
-      <c r="AA61" s="358"/>
-      <c r="AB61" s="358"/>
-      <c r="AC61" s="358"/>
-      <c r="AD61" s="358"/>
-      <c r="AE61" s="358"/>
-      <c r="AF61" s="358"/>
-      <c r="AG61" s="358"/>
-      <c r="AH61" s="358"/>
-      <c r="AI61" s="358"/>
-      <c r="AJ61" s="358"/>
-      <c r="AK61" s="358"/>
-      <c r="AL61" s="358"/>
-      <c r="AM61" s="358"/>
-      <c r="AN61" s="358"/>
-      <c r="AO61" s="358"/>
-      <c r="AP61" s="358"/>
-      <c r="AQ61" s="361"/>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
+      <c r="G61" s="354"/>
+      <c r="H61" s="354"/>
+      <c r="I61" s="354"/>
+      <c r="J61" s="354"/>
+      <c r="K61" s="354"/>
+      <c r="L61" s="354"/>
+      <c r="M61" s="354"/>
+      <c r="N61" s="354"/>
+      <c r="O61" s="354"/>
+      <c r="P61" s="354"/>
+      <c r="Q61" s="354"/>
+      <c r="R61" s="354"/>
+      <c r="S61" s="354"/>
+      <c r="T61" s="354"/>
+      <c r="U61" s="357"/>
+      <c r="V61" s="368"/>
+      <c r="W61" s="353" t="s">
+        <v>75</v>
+      </c>
+      <c r="X61" s="354"/>
+      <c r="Y61" s="354"/>
+      <c r="Z61" s="354"/>
+      <c r="AA61" s="354"/>
+      <c r="AB61" s="354"/>
+      <c r="AC61" s="354"/>
+      <c r="AD61" s="354"/>
+      <c r="AE61" s="354"/>
+      <c r="AF61" s="354"/>
+      <c r="AG61" s="354"/>
+      <c r="AH61" s="354"/>
+      <c r="AI61" s="354"/>
+      <c r="AJ61" s="354"/>
+      <c r="AK61" s="354"/>
+      <c r="AL61" s="354"/>
+      <c r="AM61" s="354"/>
+      <c r="AN61" s="354"/>
+      <c r="AO61" s="354"/>
+      <c r="AP61" s="354"/>
+      <c r="AQ61" s="357"/>
     </row>
     <row r="62" ht="12" customHeight="1" spans="1:43">
-      <c r="A62" s="325" t="s">
-        <v>75</v>
-      </c>
-      <c r="B62" s="326"/>
-      <c r="C62" s="326"/>
-      <c r="D62" s="326"/>
-      <c r="E62" s="326"/>
-      <c r="F62" s="326"/>
-      <c r="G62" s="326"/>
-      <c r="H62" s="326"/>
-      <c r="I62" s="326"/>
-      <c r="J62" s="326"/>
-      <c r="K62" s="326"/>
-      <c r="L62" s="326"/>
-      <c r="M62" s="351" t="s">
+      <c r="A62" s="324" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="325"/>
+      <c r="C62" s="325"/>
+      <c r="D62" s="325"/>
+      <c r="E62" s="325"/>
+      <c r="F62" s="325"/>
+      <c r="G62" s="325"/>
+      <c r="H62" s="325"/>
+      <c r="I62" s="325"/>
+      <c r="J62" s="325"/>
+      <c r="K62" s="325"/>
+      <c r="L62" s="325"/>
+      <c r="M62" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="N62" s="351"/>
-      <c r="O62" s="351"/>
-      <c r="P62" s="351"/>
-      <c r="Q62" s="351"/>
-      <c r="R62" s="351"/>
-      <c r="S62" s="351"/>
-      <c r="T62" s="351"/>
-      <c r="U62" s="373"/>
-      <c r="V62" s="325" t="s">
-        <v>75</v>
-      </c>
-      <c r="W62" s="326"/>
-      <c r="X62" s="326"/>
-      <c r="Y62" s="326"/>
-      <c r="Z62" s="326"/>
-      <c r="AA62" s="326"/>
-      <c r="AB62" s="326"/>
-      <c r="AC62" s="326"/>
-      <c r="AD62" s="326"/>
-      <c r="AE62" s="326"/>
-      <c r="AF62" s="326"/>
-      <c r="AG62" s="326"/>
-      <c r="AH62" s="326"/>
-      <c r="AI62" s="351" t="s">
+      <c r="N62" s="348"/>
+      <c r="O62" s="348"/>
+      <c r="P62" s="348"/>
+      <c r="Q62" s="348"/>
+      <c r="R62" s="348"/>
+      <c r="S62" s="348"/>
+      <c r="T62" s="348"/>
+      <c r="U62" s="369"/>
+      <c r="V62" s="324" t="s">
+        <v>76</v>
+      </c>
+      <c r="W62" s="325"/>
+      <c r="X62" s="325"/>
+      <c r="Y62" s="325"/>
+      <c r="Z62" s="325"/>
+      <c r="AA62" s="325"/>
+      <c r="AB62" s="325"/>
+      <c r="AC62" s="325"/>
+      <c r="AD62" s="325"/>
+      <c r="AE62" s="325"/>
+      <c r="AF62" s="325"/>
+      <c r="AG62" s="325"/>
+      <c r="AH62" s="325"/>
+      <c r="AI62" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="AJ62" s="374"/>
-      <c r="AK62" s="374"/>
-      <c r="AL62" s="374"/>
-      <c r="AM62" s="374"/>
-      <c r="AN62" s="374"/>
-      <c r="AO62" s="374"/>
-      <c r="AP62" s="374"/>
-      <c r="AQ62" s="375"/>
+      <c r="AJ62" s="370"/>
+      <c r="AK62" s="370"/>
+      <c r="AL62" s="370"/>
+      <c r="AM62" s="370"/>
+      <c r="AN62" s="370"/>
+      <c r="AO62" s="370"/>
+      <c r="AP62" s="370"/>
+      <c r="AQ62" s="371"/>
     </row>
     <row r="63" ht="12" customHeight="1" spans="1:43">
-      <c r="A63" s="376"/>
-      <c r="B63" s="359"/>
-      <c r="C63" s="359"/>
-      <c r="D63" s="359"/>
-      <c r="E63" s="359"/>
-      <c r="F63" s="359"/>
-      <c r="G63" s="359"/>
-      <c r="H63" s="359"/>
-      <c r="I63" s="359"/>
-      <c r="J63" s="359"/>
-      <c r="K63" s="359"/>
-      <c r="L63" s="359"/>
-      <c r="M63" s="359"/>
-      <c r="N63" s="359"/>
-      <c r="O63" s="359"/>
-      <c r="P63" s="359"/>
-      <c r="Q63" s="359"/>
-      <c r="R63" s="359"/>
-      <c r="S63" s="359"/>
-      <c r="T63" s="359"/>
-      <c r="U63" s="360"/>
-      <c r="V63" s="376"/>
-      <c r="W63" s="359"/>
-      <c r="X63" s="359"/>
-      <c r="Y63" s="359"/>
-      <c r="Z63" s="359"/>
-      <c r="AA63" s="359"/>
-      <c r="AB63" s="359"/>
-      <c r="AC63" s="359"/>
-      <c r="AD63" s="359"/>
-      <c r="AE63" s="359"/>
-      <c r="AF63" s="359"/>
-      <c r="AG63" s="359"/>
-      <c r="AH63" s="359"/>
-      <c r="AI63" s="359"/>
-      <c r="AJ63" s="359"/>
-      <c r="AK63" s="359"/>
-      <c r="AL63" s="359"/>
-      <c r="AM63" s="359"/>
-      <c r="AN63" s="359"/>
-      <c r="AO63" s="359"/>
-      <c r="AP63" s="359"/>
-      <c r="AQ63" s="360"/>
+      <c r="A63" s="372"/>
+      <c r="B63" s="355"/>
+      <c r="C63" s="355"/>
+      <c r="D63" s="355"/>
+      <c r="E63" s="355"/>
+      <c r="F63" s="355"/>
+      <c r="G63" s="355"/>
+      <c r="H63" s="355"/>
+      <c r="I63" s="355"/>
+      <c r="J63" s="355"/>
+      <c r="K63" s="355"/>
+      <c r="L63" s="355"/>
+      <c r="M63" s="355"/>
+      <c r="N63" s="355"/>
+      <c r="O63" s="355"/>
+      <c r="P63" s="355"/>
+      <c r="Q63" s="355"/>
+      <c r="R63" s="355"/>
+      <c r="S63" s="355"/>
+      <c r="T63" s="355"/>
+      <c r="U63" s="356"/>
+      <c r="V63" s="372"/>
+      <c r="W63" s="355"/>
+      <c r="X63" s="355"/>
+      <c r="Y63" s="355"/>
+      <c r="Z63" s="355"/>
+      <c r="AA63" s="355"/>
+      <c r="AB63" s="355"/>
+      <c r="AC63" s="355"/>
+      <c r="AD63" s="355"/>
+      <c r="AE63" s="355"/>
+      <c r="AF63" s="355"/>
+      <c r="AG63" s="355"/>
+      <c r="AH63" s="355"/>
+      <c r="AI63" s="355"/>
+      <c r="AJ63" s="355"/>
+      <c r="AK63" s="355"/>
+      <c r="AL63" s="355"/>
+      <c r="AM63" s="355"/>
+      <c r="AN63" s="355"/>
+      <c r="AO63" s="355"/>
+      <c r="AP63" s="355"/>
+      <c r="AQ63" s="356"/>
     </row>
     <row r="64" ht="12" customHeight="1" spans="1:43">
-      <c r="A64" s="377" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" s="378"/>
-      <c r="C64" s="378"/>
-      <c r="D64" s="378"/>
-      <c r="E64" s="378"/>
-      <c r="F64" s="378"/>
-      <c r="G64" s="378"/>
-      <c r="H64" s="378"/>
-      <c r="I64" s="378"/>
-      <c r="J64" s="378"/>
-      <c r="K64" s="378"/>
-      <c r="L64" s="378"/>
-      <c r="M64" s="379" t="s">
+      <c r="A64" s="373" t="s">
         <v>77</v>
       </c>
-      <c r="N64" s="378"/>
-      <c r="O64" s="380"/>
-      <c r="P64" s="380"/>
-      <c r="Q64" s="380"/>
-      <c r="R64" s="380"/>
-      <c r="S64" s="380"/>
-      <c r="T64" s="380"/>
-      <c r="U64" s="380"/>
-      <c r="V64" s="377" t="s">
-        <v>76</v>
-      </c>
-      <c r="W64" s="378"/>
-      <c r="X64" s="378"/>
-      <c r="Y64" s="378"/>
-      <c r="Z64" s="378"/>
-      <c r="AA64" s="378"/>
-      <c r="AB64" s="378"/>
-      <c r="AC64" s="378"/>
-      <c r="AD64" s="378"/>
-      <c r="AE64" s="378"/>
-      <c r="AF64" s="378"/>
-      <c r="AG64" s="378"/>
-      <c r="AH64" s="378"/>
-      <c r="AI64" s="379" t="s">
+      <c r="B64" s="374"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
+      <c r="G64" s="374"/>
+      <c r="H64" s="374"/>
+      <c r="I64" s="374"/>
+      <c r="J64" s="374"/>
+      <c r="K64" s="374"/>
+      <c r="L64" s="374"/>
+      <c r="M64" s="375" t="s">
+        <v>78</v>
+      </c>
+      <c r="N64" s="374"/>
+      <c r="O64" s="376"/>
+      <c r="P64" s="376"/>
+      <c r="Q64" s="376"/>
+      <c r="R64" s="376"/>
+      <c r="S64" s="376"/>
+      <c r="T64" s="376"/>
+      <c r="U64" s="376"/>
+      <c r="V64" s="373" t="s">
+        <v>77</v>
+      </c>
+      <c r="W64" s="374"/>
+      <c r="X64" s="374"/>
+      <c r="Y64" s="374"/>
+      <c r="Z64" s="374"/>
+      <c r="AA64" s="374"/>
+      <c r="AB64" s="374"/>
+      <c r="AC64" s="374"/>
+      <c r="AD64" s="374"/>
+      <c r="AE64" s="374"/>
+      <c r="AF64" s="374"/>
+      <c r="AG64" s="374"/>
+      <c r="AH64" s="374"/>
+      <c r="AI64" s="375" t="s">
         <v>15</v>
       </c>
-      <c r="AJ64" s="378"/>
-      <c r="AK64" s="378"/>
-      <c r="AL64" s="378"/>
-      <c r="AM64" s="378"/>
-      <c r="AN64" s="378"/>
-      <c r="AO64" s="378"/>
-      <c r="AP64" s="378"/>
-      <c r="AQ64" s="381"/>
+      <c r="AJ64" s="374"/>
+      <c r="AK64" s="374"/>
+      <c r="AL64" s="374"/>
+      <c r="AM64" s="374"/>
+      <c r="AN64" s="374"/>
+      <c r="AO64" s="374"/>
+      <c r="AP64" s="374"/>
+      <c r="AQ64" s="377"/>
     </row>
     <row r="65" ht="12" customHeight="1" spans="1:47">
-      <c r="A65" s="382"/>
-      <c r="B65" s="383"/>
-      <c r="C65" s="383"/>
-      <c r="D65" s="383"/>
-      <c r="E65" s="383"/>
-      <c r="F65" s="383"/>
-      <c r="G65" s="383"/>
-      <c r="H65" s="383"/>
-      <c r="I65" s="383"/>
-      <c r="J65" s="383"/>
-      <c r="K65" s="383"/>
-      <c r="L65" s="383"/>
-      <c r="M65" s="383"/>
-      <c r="N65" s="383"/>
-      <c r="O65" s="383"/>
-      <c r="P65" s="383"/>
-      <c r="Q65" s="383"/>
-      <c r="R65" s="383"/>
-      <c r="S65" s="383"/>
-      <c r="T65" s="383"/>
-      <c r="U65" s="384"/>
-      <c r="V65" s="371"/>
-      <c r="W65" s="385"/>
-      <c r="X65" s="385"/>
-      <c r="Y65" s="385"/>
-      <c r="Z65" s="385"/>
-      <c r="AA65" s="385"/>
-      <c r="AB65" s="385"/>
-      <c r="AC65" s="385"/>
-      <c r="AD65" s="385"/>
-      <c r="AE65" s="385"/>
-      <c r="AF65" s="385"/>
-      <c r="AG65" s="385"/>
-      <c r="AH65" s="385"/>
-      <c r="AI65" s="385"/>
-      <c r="AJ65" s="385"/>
-      <c r="AK65" s="385"/>
-      <c r="AL65" s="385"/>
-      <c r="AM65" s="385"/>
-      <c r="AN65" s="385"/>
-      <c r="AO65" s="385"/>
-      <c r="AP65" s="385"/>
-      <c r="AQ65" s="386"/>
+      <c r="A65" s="378"/>
+      <c r="B65" s="379"/>
+      <c r="C65" s="379"/>
+      <c r="D65" s="379"/>
+      <c r="E65" s="379"/>
+      <c r="F65" s="379"/>
+      <c r="G65" s="379"/>
+      <c r="H65" s="379"/>
+      <c r="I65" s="379"/>
+      <c r="J65" s="379"/>
+      <c r="K65" s="379"/>
+      <c r="L65" s="379"/>
+      <c r="M65" s="379"/>
+      <c r="N65" s="379"/>
+      <c r="O65" s="379"/>
+      <c r="P65" s="379"/>
+      <c r="Q65" s="379"/>
+      <c r="R65" s="379"/>
+      <c r="S65" s="379"/>
+      <c r="T65" s="379"/>
+      <c r="U65" s="380"/>
+      <c r="V65" s="367"/>
+      <c r="W65" s="381"/>
+      <c r="X65" s="381"/>
+      <c r="Y65" s="381"/>
+      <c r="Z65" s="381"/>
+      <c r="AA65" s="381"/>
+      <c r="AB65" s="381"/>
+      <c r="AC65" s="381"/>
+      <c r="AD65" s="381"/>
+      <c r="AE65" s="381"/>
+      <c r="AF65" s="381"/>
+      <c r="AG65" s="381"/>
+      <c r="AH65" s="381"/>
+      <c r="AI65" s="381"/>
+      <c r="AJ65" s="381"/>
+      <c r="AK65" s="381"/>
+      <c r="AL65" s="381"/>
+      <c r="AM65" s="381"/>
+      <c r="AN65" s="381"/>
+      <c r="AO65" s="381"/>
+      <c r="AP65" s="381"/>
+      <c r="AQ65" s="382"/>
     </row>
     <row r="66" ht="12" customHeight="1" spans="1:47">
-      <c r="A66" s="387"/>
-      <c r="B66" s="380"/>
-      <c r="C66" s="380"/>
-      <c r="D66" s="380"/>
-      <c r="E66" s="380"/>
-      <c r="F66" s="380"/>
-      <c r="G66" s="380"/>
-      <c r="H66" s="380"/>
-      <c r="I66" s="380"/>
-      <c r="J66" s="380"/>
-      <c r="K66" s="380"/>
-      <c r="L66" s="380"/>
-      <c r="M66" s="380"/>
-      <c r="N66" s="380"/>
-      <c r="O66" s="380"/>
-      <c r="P66" s="380"/>
-      <c r="Q66" s="380"/>
-      <c r="R66" s="380"/>
-      <c r="S66" s="380"/>
-      <c r="T66" s="380"/>
-      <c r="U66" s="388"/>
-      <c r="V66" s="365"/>
-      <c r="W66" s="389"/>
-      <c r="X66" s="389"/>
-      <c r="Y66" s="389"/>
-      <c r="Z66" s="389"/>
-      <c r="AA66" s="389"/>
-      <c r="AB66" s="389"/>
-      <c r="AC66" s="389"/>
-      <c r="AD66" s="389"/>
-      <c r="AE66" s="389"/>
-      <c r="AF66" s="389"/>
-      <c r="AG66" s="389"/>
-      <c r="AH66" s="389"/>
-      <c r="AI66" s="389"/>
-      <c r="AJ66" s="389"/>
-      <c r="AK66" s="389"/>
-      <c r="AL66" s="389"/>
-      <c r="AM66" s="389"/>
-      <c r="AN66" s="389"/>
-      <c r="AO66" s="389"/>
-      <c r="AP66" s="389"/>
-      <c r="AQ66" s="390"/>
+      <c r="A66" s="383"/>
+      <c r="B66" s="376"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="376"/>
+      <c r="E66" s="376"/>
+      <c r="F66" s="376"/>
+      <c r="G66" s="376"/>
+      <c r="H66" s="376"/>
+      <c r="I66" s="376"/>
+      <c r="J66" s="376"/>
+      <c r="K66" s="376"/>
+      <c r="L66" s="376"/>
+      <c r="M66" s="376"/>
+      <c r="N66" s="376"/>
+      <c r="O66" s="376"/>
+      <c r="P66" s="376"/>
+      <c r="Q66" s="376"/>
+      <c r="R66" s="376"/>
+      <c r="S66" s="376"/>
+      <c r="T66" s="376"/>
+      <c r="U66" s="384"/>
+      <c r="V66" s="361"/>
+      <c r="W66" s="385"/>
+      <c r="X66" s="385"/>
+      <c r="Y66" s="385"/>
+      <c r="Z66" s="385"/>
+      <c r="AA66" s="385"/>
+      <c r="AB66" s="385"/>
+      <c r="AC66" s="385"/>
+      <c r="AD66" s="385"/>
+      <c r="AE66" s="385"/>
+      <c r="AF66" s="385"/>
+      <c r="AG66" s="385"/>
+      <c r="AH66" s="385"/>
+      <c r="AI66" s="385"/>
+      <c r="AJ66" s="385"/>
+      <c r="AK66" s="385"/>
+      <c r="AL66" s="385"/>
+      <c r="AM66" s="385"/>
+      <c r="AN66" s="385"/>
+      <c r="AO66" s="385"/>
+      <c r="AP66" s="385"/>
+      <c r="AQ66" s="386"/>
     </row>
     <row r="67" ht="12" customHeight="1" spans="1:47">
-      <c r="A67" s="387"/>
-      <c r="B67" s="380"/>
-      <c r="C67" s="380"/>
-      <c r="D67" s="380"/>
-      <c r="E67" s="380"/>
-      <c r="F67" s="380"/>
-      <c r="G67" s="380"/>
-      <c r="H67" s="380"/>
-      <c r="I67" s="380"/>
-      <c r="J67" s="380"/>
-      <c r="K67" s="380"/>
-      <c r="L67" s="380"/>
-      <c r="M67" s="380"/>
-      <c r="N67" s="380"/>
-      <c r="O67" s="380"/>
-      <c r="P67" s="380"/>
-      <c r="Q67" s="380"/>
-      <c r="R67" s="380"/>
-      <c r="S67" s="380"/>
-      <c r="T67" s="380"/>
-      <c r="U67" s="388"/>
-      <c r="V67" s="365"/>
-      <c r="W67" s="389"/>
-      <c r="X67" s="389"/>
-      <c r="Y67" s="389"/>
-      <c r="Z67" s="389"/>
-      <c r="AA67" s="389"/>
-      <c r="AB67" s="389"/>
-      <c r="AC67" s="389"/>
-      <c r="AD67" s="389"/>
-      <c r="AE67" s="389"/>
-      <c r="AF67" s="389"/>
-      <c r="AG67" s="389"/>
-      <c r="AH67" s="389"/>
-      <c r="AI67" s="389"/>
-      <c r="AJ67" s="389"/>
-      <c r="AK67" s="389"/>
-      <c r="AL67" s="389"/>
-      <c r="AM67" s="389"/>
-      <c r="AN67" s="389"/>
-      <c r="AO67" s="389"/>
-      <c r="AP67" s="389"/>
-      <c r="AQ67" s="390"/>
+      <c r="A67" s="383"/>
+      <c r="B67" s="376"/>
+      <c r="C67" s="376"/>
+      <c r="D67" s="376"/>
+      <c r="E67" s="376"/>
+      <c r="F67" s="376"/>
+      <c r="G67" s="376"/>
+      <c r="H67" s="376"/>
+      <c r="I67" s="376"/>
+      <c r="J67" s="376"/>
+      <c r="K67" s="376"/>
+      <c r="L67" s="376"/>
+      <c r="M67" s="376"/>
+      <c r="N67" s="376"/>
+      <c r="O67" s="376"/>
+      <c r="P67" s="376"/>
+      <c r="Q67" s="376"/>
+      <c r="R67" s="376"/>
+      <c r="S67" s="376"/>
+      <c r="T67" s="376"/>
+      <c r="U67" s="384"/>
+      <c r="V67" s="361"/>
+      <c r="W67" s="385"/>
+      <c r="X67" s="385"/>
+      <c r="Y67" s="385"/>
+      <c r="Z67" s="385"/>
+      <c r="AA67" s="385"/>
+      <c r="AB67" s="385"/>
+      <c r="AC67" s="385"/>
+      <c r="AD67" s="385"/>
+      <c r="AE67" s="385"/>
+      <c r="AF67" s="385"/>
+      <c r="AG67" s="385"/>
+      <c r="AH67" s="385"/>
+      <c r="AI67" s="385"/>
+      <c r="AJ67" s="385"/>
+      <c r="AK67" s="385"/>
+      <c r="AL67" s="385"/>
+      <c r="AM67" s="385"/>
+      <c r="AN67" s="385"/>
+      <c r="AO67" s="385"/>
+      <c r="AP67" s="385"/>
+      <c r="AQ67" s="386"/>
     </row>
     <row r="68" ht="12" customHeight="1" spans="1:47">
       <c r="E68"/>
@@ -12836,7 +12880,7 @@
     <row r="201" ht="12" customHeight="1"/>
     <row r="202" ht="12" customHeight="1"/>
   </sheetData>
-  <mergeCells count="160">
+  <mergeCells count="161">
     <mergeCell ref="AH1:AQ1"/>
     <mergeCell ref="AH2:AQ2"/>
     <mergeCell ref="AH3:AQ3"/>
@@ -12908,6 +12952,7 @@
     <mergeCell ref="AI38:AQ38"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="N39:V39"/>
+    <mergeCell ref="W39:AE39"/>
     <mergeCell ref="AG39:AQ39"/>
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="N40:V40"/>
@@ -13021,7 +13066,7 @@
       <c r="C1" s="241"/>
       <c r="D1" s="241"/>
       <c r="E1" s="242" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1" s="242"/>
       <c r="G1" s="242"/>
@@ -13232,7 +13277,7 @@
       <c r="AF5" s="243"/>
       <c r="AG5" s="243"/>
       <c r="AH5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
@@ -13241,7 +13286,7 @@
       <c r="AM5" s="4"/>
       <c r="AN5" s="4"/>
       <c r="AO5" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP5" s="21"/>
       <c r="AQ5" s="243"/>
@@ -13293,14 +13338,14 @@
     </row>
     <row r="7" ht="12" customHeight="1" spans="1:43">
       <c r="A7" s="217" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
       <c r="D7" s="58"/>
       <c r="E7" s="59"/>
       <c r="F7" s="245" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="245"/>
       <c r="H7" s="245"/>
@@ -13330,7 +13375,7 @@
       <c r="AF7" s="245"/>
       <c r="AG7" s="246"/>
       <c r="AH7" s="247" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI7" s="99"/>
       <c r="AJ7" s="99"/>
@@ -13434,14 +13479,14 @@
     </row>
     <row r="10" ht="12" customHeight="1" spans="1:43">
       <c r="A10" s="157" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" s="158"/>
       <c r="C10" s="158"/>
       <c r="D10" s="158"/>
       <c r="E10" s="159"/>
       <c r="F10" s="248" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="248"/>
       <c r="H10" s="248"/>
@@ -13663,7 +13708,7 @@
     </row>
     <row r="15" ht="12" customHeight="1" spans="1:43">
       <c r="A15" s="172" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="173"/>
       <c r="C15" s="173"/>
@@ -13676,7 +13721,7 @@
       <c r="H15" s="133"/>
       <c r="I15" s="133"/>
       <c r="J15" s="252" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" s="173"/>
       <c r="L15" s="133">
@@ -13685,7 +13730,7 @@
       <c r="M15" s="133"/>
       <c r="N15" s="133"/>
       <c r="O15" s="252" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P15" s="173"/>
       <c r="Q15" s="133">
@@ -13694,17 +13739,17 @@
       <c r="R15" s="133"/>
       <c r="S15" s="133"/>
       <c r="T15" s="109" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U15" s="68"/>
       <c r="V15" s="55" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W15" s="58"/>
       <c r="X15" s="58"/>
       <c r="Y15" s="59"/>
       <c r="Z15" s="104" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA15" s="18"/>
       <c r="AB15" s="18"/>
@@ -13816,14 +13861,14 @@
     </row>
     <row r="18" ht="12" customHeight="1" spans="1:43">
       <c r="A18" s="172" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" s="173"/>
       <c r="C18" s="173"/>
       <c r="D18" s="173"/>
       <c r="E18" s="173"/>
       <c r="F18" s="133" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G18" s="133"/>
       <c r="H18" s="133"/>
@@ -13833,13 +13878,13 @@
       <c r="L18" s="133"/>
       <c r="M18" s="133"/>
       <c r="N18" s="252" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O18" s="173"/>
       <c r="P18" s="173"/>
       <c r="Q18" s="173"/>
       <c r="R18" s="255" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S18" s="255"/>
       <c r="T18" s="255"/>
@@ -13847,13 +13892,13 @@
       <c r="V18" s="255"/>
       <c r="W18" s="255"/>
       <c r="X18" s="252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y18" s="173"/>
       <c r="Z18" s="173"/>
       <c r="AA18" s="173"/>
       <c r="AB18" s="255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC18" s="255"/>
       <c r="AD18" s="255"/>
@@ -13963,14 +14008,14 @@
     </row>
     <row r="21" ht="12" customHeight="1" spans="1:43">
       <c r="A21" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G21" s="99"/>
       <c r="H21" s="99"/>
@@ -13982,7 +14027,7 @@
       <c r="N21" s="99"/>
       <c r="O21" s="99"/>
       <c r="P21" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -13990,7 +14035,7 @@
       <c r="T21" s="10"/>
       <c r="U21" s="10"/>
       <c r="V21" s="174" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="W21" s="174"/>
       <c r="X21" s="174"/>
@@ -14094,13 +14139,13 @@
       <c r="AF23" s="176"/>
       <c r="AG23" s="177"/>
       <c r="AH23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AI23" s="10"/>
       <c r="AJ23" s="10"/>
       <c r="AK23" s="10"/>
       <c r="AL23" s="245" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM23" s="245"/>
       <c r="AN23" s="245"/>
@@ -14200,7 +14245,7 @@
     </row>
     <row r="26" ht="12" customHeight="1" spans="1:43">
       <c r="A26" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -14213,7 +14258,7 @@
       <c r="H26" s="99"/>
       <c r="I26" s="99"/>
       <c r="J26" s="42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
@@ -14225,7 +14270,7 @@
       <c r="P26" s="99"/>
       <c r="Q26" s="99"/>
       <c r="R26" s="42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
@@ -14237,19 +14282,19 @@
       <c r="X26" s="99"/>
       <c r="Y26" s="99"/>
       <c r="Z26" s="42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA26" s="10"/>
       <c r="AB26" s="10"/>
       <c r="AC26" s="10"/>
       <c r="AD26" s="99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE26" s="99"/>
       <c r="AF26" s="99"/>
       <c r="AG26" s="100"/>
       <c r="AH26" s="172" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI26" s="173"/>
       <c r="AJ26" s="173"/>
@@ -14260,7 +14305,7 @@
       <c r="AM26" s="133"/>
       <c r="AN26" s="133"/>
       <c r="AO26" s="133" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP26" s="133">
         <v>5</v>
@@ -14404,7 +14449,7 @@
     </row>
     <row r="30" ht="12" customHeight="1" spans="1:43">
       <c r="A30" s="264" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="264"/>
       <c r="C30" s="264"/>
@@ -14496,7 +14541,7 @@
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:43">
       <c r="A32" s="41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -14513,7 +14558,7 @@
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
       <c r="P32" s="218" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q32" s="58"/>
       <c r="R32" s="58"/>
@@ -14525,7 +14570,7 @@
       <c r="X32" s="58"/>
       <c r="Y32" s="59"/>
       <c r="Z32" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA32" s="10"/>
       <c r="AB32" s="10"/>
@@ -14535,7 +14580,7 @@
       <c r="AF32" s="10"/>
       <c r="AG32" s="10"/>
       <c r="AH32" s="42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AI32" s="10"/>
       <c r="AJ32" s="10"/>
@@ -14543,7 +14588,7 @@
       <c r="AL32" s="10"/>
       <c r="AM32" s="10"/>
       <c r="AN32" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO32" s="10"/>
       <c r="AP32" s="10"/>
@@ -14641,7 +14686,7 @@
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:43">
       <c r="A35" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" s="46"/>
       <c r="C35" s="46"/>
@@ -14658,7 +14703,7 @@
       <c r="N35" s="46"/>
       <c r="O35" s="46"/>
       <c r="P35" s="46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="46"/>
       <c r="R35" s="46"/>
@@ -14670,7 +14715,7 @@
       <c r="X35" s="46"/>
       <c r="Y35" s="46"/>
       <c r="Z35" s="46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA35" s="46"/>
       <c r="AB35" s="46"/>
@@ -14685,14 +14730,14 @@
       <c r="AI35" s="46"/>
       <c r="AJ35" s="46"/>
       <c r="AK35" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL35" s="46">
         <v>5</v>
       </c>
       <c r="AM35" s="46"/>
       <c r="AN35" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AO35" s="46"/>
       <c r="AP35" s="46"/>
@@ -14790,7 +14835,7 @@
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:43">
       <c r="A38" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B38" s="46"/>
       <c r="C38" s="46"/>
@@ -14807,7 +14852,7 @@
       <c r="N38" s="46"/>
       <c r="O38" s="46"/>
       <c r="P38" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q38" s="46"/>
       <c r="R38" s="46"/>
@@ -14819,7 +14864,7 @@
       <c r="X38" s="46"/>
       <c r="Y38" s="46"/>
       <c r="Z38" s="46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA38" s="46"/>
       <c r="AB38" s="46"/>
@@ -14834,14 +14879,14 @@
       <c r="AI38" s="46"/>
       <c r="AJ38" s="46"/>
       <c r="AK38" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL38" s="46">
         <v>5</v>
       </c>
       <c r="AM38" s="46"/>
       <c r="AN38" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AO38" s="46"/>
       <c r="AP38" s="46"/>
@@ -14939,7 +14984,7 @@
     </row>
     <row r="41" ht="12" customHeight="1" spans="1:43">
       <c r="A41" s="45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B41" s="46"/>
       <c r="C41" s="46"/>
@@ -14956,7 +15001,7 @@
       <c r="N41" s="46"/>
       <c r="O41" s="46"/>
       <c r="P41" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q41" s="46"/>
       <c r="R41" s="46"/>
@@ -14968,7 +15013,7 @@
       <c r="X41" s="46"/>
       <c r="Y41" s="46"/>
       <c r="Z41" s="46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA41" s="46"/>
       <c r="AB41" s="46"/>
@@ -14983,14 +15028,14 @@
       <c r="AI41" s="46"/>
       <c r="AJ41" s="46"/>
       <c r="AK41" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL41" s="46">
         <v>12</v>
       </c>
       <c r="AM41" s="46"/>
       <c r="AN41" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AO41" s="46"/>
       <c r="AP41" s="46"/>
@@ -15133,7 +15178,7 @@
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:43">
       <c r="A45" s="264" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B45" s="264"/>
       <c r="C45" s="264"/>
@@ -15225,7 +15270,7 @@
     </row>
     <row r="47" ht="12" customHeight="1" spans="1:43">
       <c r="A47" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -15242,7 +15287,7 @@
       <c r="N47" s="10"/>
       <c r="O47" s="10"/>
       <c r="P47" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -15250,7 +15295,7 @@
       <c r="T47" s="10"/>
       <c r="U47" s="43"/>
       <c r="V47" s="265" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W47" s="10"/>
       <c r="X47" s="10"/>
@@ -15258,7 +15303,7 @@
       <c r="Z47" s="10"/>
       <c r="AA47" s="10"/>
       <c r="AB47" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AC47" s="10"/>
       <c r="AD47" s="10"/>
@@ -15266,13 +15311,13 @@
       <c r="AF47" s="10"/>
       <c r="AG47" s="10"/>
       <c r="AH47" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AI47" s="10"/>
       <c r="AJ47" s="10"/>
       <c r="AK47" s="10"/>
       <c r="AL47" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM47" s="10"/>
       <c r="AN47" s="10"/>
@@ -15372,7 +15417,7 @@
     </row>
     <row r="50" ht="12" customHeight="1" spans="1:43">
       <c r="A50" s="267" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="24"/>
@@ -15394,14 +15439,14 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="24"/>
       <c r="S50" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T50" s="24">
         <v>1</v>
       </c>
       <c r="U50" s="26"/>
       <c r="V50" s="266" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
@@ -15409,7 +15454,7 @@
       <c r="Z50" s="14"/>
       <c r="AA50" s="14"/>
       <c r="AB50" s="46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC50" s="46"/>
       <c r="AD50" s="46"/>
@@ -15428,7 +15473,7 @@
       <c r="AM50" s="46"/>
       <c r="AN50" s="46"/>
       <c r="AO50" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP50" s="46">
         <v>3</v>
@@ -15572,7 +15617,7 @@
     </row>
     <row r="54" ht="12" customHeight="1" spans="1:43">
       <c r="A54" s="267" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="24"/>
@@ -15594,14 +15639,14 @@
       <c r="Q54" s="24"/>
       <c r="R54" s="24"/>
       <c r="S54" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T54" s="24">
         <v>2</v>
       </c>
       <c r="U54" s="26"/>
       <c r="V54" s="266" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
@@ -15609,7 +15654,7 @@
       <c r="Z54" s="14"/>
       <c r="AA54" s="14"/>
       <c r="AB54" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC54" s="46"/>
       <c r="AD54" s="46"/>
@@ -15628,7 +15673,7 @@
       <c r="AM54" s="46"/>
       <c r="AN54" s="46"/>
       <c r="AO54" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP54" s="46">
         <v>4</v>
@@ -15817,7 +15862,7 @@
     </row>
     <row r="59" ht="12" customHeight="1" spans="1:43">
       <c r="A59" s="264" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B59" s="264"/>
       <c r="C59" s="264"/>
@@ -15909,7 +15954,7 @@
     </row>
     <row r="61" ht="12" customHeight="1" spans="1:43">
       <c r="A61" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -15920,7 +15965,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
       <c r="J61" s="42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
@@ -15938,21 +15983,21 @@
       <c r="X61" s="10"/>
       <c r="Y61" s="10"/>
       <c r="Z61" s="42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AA61" s="10"/>
       <c r="AB61" s="10"/>
       <c r="AC61" s="10"/>
       <c r="AD61" s="10"/>
       <c r="AE61" s="42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF61" s="10"/>
       <c r="AG61" s="10"/>
       <c r="AH61" s="10"/>
       <c r="AI61" s="10"/>
       <c r="AJ61" s="42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK61" s="10"/>
       <c r="AL61" s="10"/>
@@ -16054,7 +16099,7 @@
     </row>
     <row r="64" ht="12" customHeight="1" spans="1:43">
       <c r="A64" s="45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
@@ -16065,7 +16110,7 @@
       <c r="H64" s="46"/>
       <c r="I64" s="46"/>
       <c r="J64" s="46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K64" s="46"/>
       <c r="L64" s="46"/>
@@ -16083,21 +16128,21 @@
       <c r="X64" s="46"/>
       <c r="Y64" s="46"/>
       <c r="Z64" s="46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA64" s="46"/>
       <c r="AB64" s="46"/>
       <c r="AC64" s="46"/>
       <c r="AD64" s="46"/>
       <c r="AE64" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF64" s="46"/>
       <c r="AG64" s="46"/>
       <c r="AH64" s="46"/>
       <c r="AI64" s="46"/>
       <c r="AJ64" s="46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK64" s="46"/>
       <c r="AL64" s="46"/>
@@ -16154,7 +16199,7 @@
     </row>
     <row r="66" ht="12" customHeight="1" spans="1:43">
       <c r="A66" s="45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="46"/>
       <c r="C66" s="46"/>
@@ -16165,7 +16210,7 @@
       <c r="H66" s="46"/>
       <c r="I66" s="46"/>
       <c r="J66" s="46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K66" s="46"/>
       <c r="L66" s="46"/>
@@ -16183,21 +16228,21 @@
       <c r="X66" s="46"/>
       <c r="Y66" s="46"/>
       <c r="Z66" s="46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA66" s="46"/>
       <c r="AB66" s="46"/>
       <c r="AC66" s="46"/>
       <c r="AD66" s="46"/>
       <c r="AE66" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF66" s="46"/>
       <c r="AG66" s="46"/>
       <c r="AH66" s="46"/>
       <c r="AI66" s="46"/>
       <c r="AJ66" s="46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK66" s="46"/>
       <c r="AL66" s="46"/>
@@ -16254,7 +16299,7 @@
     </row>
     <row r="68" ht="12" customHeight="1" spans="1:43">
       <c r="A68" s="45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="46"/>
       <c r="C68" s="46"/>
@@ -16265,7 +16310,7 @@
       <c r="H68" s="46"/>
       <c r="I68" s="46"/>
       <c r="J68" s="46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K68" s="46"/>
       <c r="L68" s="46"/>
@@ -16283,21 +16328,21 @@
       <c r="X68" s="46"/>
       <c r="Y68" s="46"/>
       <c r="Z68" s="46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA68" s="46"/>
       <c r="AB68" s="46"/>
       <c r="AC68" s="46"/>
       <c r="AD68" s="46"/>
       <c r="AE68" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AF68" s="46"/>
       <c r="AG68" s="46"/>
       <c r="AH68" s="46"/>
       <c r="AI68" s="46"/>
       <c r="AJ68" s="46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AK68" s="46"/>
       <c r="AL68" s="46"/>
@@ -16354,7 +16399,7 @@
     </row>
     <row r="70" ht="12" customHeight="1" spans="1:43">
       <c r="A70" s="45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="46"/>
       <c r="C70" s="46"/>
@@ -16365,7 +16410,7 @@
       <c r="H70" s="46"/>
       <c r="I70" s="46"/>
       <c r="J70" s="46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K70" s="46"/>
       <c r="L70" s="46"/>
@@ -16383,21 +16428,21 @@
       <c r="X70" s="46"/>
       <c r="Y70" s="46"/>
       <c r="Z70" s="46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA70" s="46"/>
       <c r="AB70" s="46"/>
       <c r="AC70" s="46"/>
       <c r="AD70" s="46"/>
       <c r="AE70" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AF70" s="46"/>
       <c r="AG70" s="46"/>
       <c r="AH70" s="46"/>
       <c r="AI70" s="46"/>
       <c r="AJ70" s="46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AK70" s="46"/>
       <c r="AL70" s="46"/>
@@ -16454,7 +16499,7 @@
     </row>
     <row r="72" ht="12" customHeight="1" spans="1:43">
       <c r="A72" s="45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B72" s="46"/>
       <c r="C72" s="46"/>
@@ -16465,7 +16510,7 @@
       <c r="H72" s="46"/>
       <c r="I72" s="46"/>
       <c r="J72" s="46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K72" s="46"/>
       <c r="L72" s="46"/>
@@ -16483,21 +16528,21 @@
       <c r="X72" s="46"/>
       <c r="Y72" s="46"/>
       <c r="Z72" s="46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA72" s="46"/>
       <c r="AB72" s="46"/>
       <c r="AC72" s="46"/>
       <c r="AD72" s="46"/>
       <c r="AE72" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF72" s="46"/>
       <c r="AG72" s="46"/>
       <c r="AH72" s="46"/>
       <c r="AI72" s="46"/>
       <c r="AJ72" s="46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AK72" s="46"/>
       <c r="AL72" s="46"/>
@@ -16554,7 +16599,7 @@
     </row>
     <row r="74" ht="12" customHeight="1" spans="1:43">
       <c r="A74" s="45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B74" s="46"/>
       <c r="C74" s="46"/>
@@ -16565,7 +16610,7 @@
       <c r="H74" s="46"/>
       <c r="I74" s="46"/>
       <c r="J74" s="46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K74" s="46"/>
       <c r="L74" s="46"/>
@@ -16583,21 +16628,21 @@
       <c r="X74" s="46"/>
       <c r="Y74" s="46"/>
       <c r="Z74" s="46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA74" s="46"/>
       <c r="AB74" s="46"/>
       <c r="AC74" s="46"/>
       <c r="AD74" s="46"/>
       <c r="AE74" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF74" s="46"/>
       <c r="AG74" s="46"/>
       <c r="AH74" s="46"/>
       <c r="AI74" s="46"/>
       <c r="AJ74" s="46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AK74" s="46"/>
       <c r="AL74" s="46"/>
@@ -16655,7 +16700,7 @@
     <row r="76" ht="12" customHeight="1"/>
     <row r="77" ht="12" customHeight="1" spans="1:43">
       <c r="A77" s="270" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="270"/>
       <c r="C77" s="270"/>
@@ -16747,13 +16792,13 @@
     </row>
     <row r="79" ht="12" customHeight="1" spans="1:43">
       <c r="A79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
       <c r="E79" s="99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F79" s="99"/>
       <c r="G79" s="99"/>
@@ -16769,13 +16814,13 @@
       <c r="Q79" s="99"/>
       <c r="R79" s="100"/>
       <c r="S79" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T79" s="10"/>
       <c r="U79" s="10"/>
       <c r="V79" s="10"/>
       <c r="W79" s="271" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X79" s="271"/>
       <c r="Y79" s="271"/>
@@ -16786,13 +16831,13 @@
       <c r="AD79" s="271"/>
       <c r="AE79" s="271"/>
       <c r="AF79" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG79" s="10"/>
       <c r="AH79" s="10"/>
       <c r="AI79" s="10"/>
       <c r="AJ79" s="99" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AK79" s="99"/>
       <c r="AL79" s="99"/>
@@ -16984,7 +17029,7 @@
     </row>
     <row r="84" ht="12" customHeight="1" spans="1:43">
       <c r="A84" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -16995,14 +17040,14 @@
       <c r="F84" s="77"/>
       <c r="G84" s="77"/>
       <c r="H84" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I84" s="77">
         <v>6</v>
       </c>
       <c r="J84" s="77"/>
       <c r="K84" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L84" s="46"/>
       <c r="M84" s="77">
@@ -17011,20 +17056,20 @@
       <c r="N84" s="77"/>
       <c r="O84" s="77"/>
       <c r="P84" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q84" s="77">
         <v>5</v>
       </c>
       <c r="R84" s="83"/>
       <c r="S84" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T84" s="14"/>
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
       <c r="W84" s="176" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X84" s="176"/>
       <c r="Y84" s="176"/>
@@ -17229,13 +17274,13 @@
     </row>
     <row r="89" ht="12" customHeight="1" spans="1:43">
       <c r="A89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="99" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F89" s="99"/>
       <c r="G89" s="99"/>
@@ -17251,13 +17296,13 @@
       <c r="Q89" s="99"/>
       <c r="R89" s="100"/>
       <c r="S89" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T89" s="10"/>
       <c r="U89" s="10"/>
       <c r="V89" s="10"/>
       <c r="W89" s="99" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="X89" s="99"/>
       <c r="Y89" s="99"/>
@@ -17268,13 +17313,13 @@
       <c r="AD89" s="99"/>
       <c r="AE89" s="99"/>
       <c r="AF89" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG89" s="10"/>
       <c r="AH89" s="10"/>
       <c r="AI89" s="10"/>
       <c r="AJ89" s="99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK89" s="99"/>
       <c r="AL89" s="99"/>
@@ -17466,7 +17511,7 @@
     </row>
     <row r="94" ht="12" customHeight="1" spans="1:43">
       <c r="A94" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -17477,14 +17522,14 @@
       <c r="F94" s="77"/>
       <c r="G94" s="77"/>
       <c r="H94" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I94" s="77">
         <v>2</v>
       </c>
       <c r="J94" s="77"/>
       <c r="K94" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L94" s="46"/>
       <c r="M94" s="77">
@@ -17493,20 +17538,20 @@
       <c r="N94" s="77"/>
       <c r="O94" s="77"/>
       <c r="P94" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q94" s="77">
         <v>6</v>
       </c>
       <c r="R94" s="83"/>
       <c r="S94" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T94" s="14"/>
       <c r="U94" s="14"/>
       <c r="V94" s="14"/>
       <c r="W94" s="176" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X94" s="176"/>
       <c r="Y94" s="176"/>
@@ -17711,7 +17756,7 @@
     </row>
     <row r="99" ht="12" customHeight="1" spans="1:43">
       <c r="A99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -17731,7 +17776,7 @@
       <c r="Q99" s="99"/>
       <c r="R99" s="100"/>
       <c r="S99" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T99" s="10"/>
       <c r="U99" s="10"/>
@@ -17746,7 +17791,7 @@
       <c r="AD99" s="99"/>
       <c r="AE99" s="99"/>
       <c r="AF99" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG99" s="10"/>
       <c r="AH99" s="10"/>
@@ -17942,7 +17987,7 @@
     </row>
     <row r="104" ht="12" customHeight="1" spans="1:43">
       <c r="A104" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -17951,24 +17996,24 @@
       <c r="F104" s="77"/>
       <c r="G104" s="77"/>
       <c r="H104" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I104" s="77"/>
       <c r="J104" s="77"/>
       <c r="K104" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L104" s="46"/>
       <c r="M104" s="77"/>
       <c r="N104" s="77"/>
       <c r="O104" s="77"/>
       <c r="P104" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q104" s="77"/>
       <c r="R104" s="83"/>
       <c r="S104" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T104" s="14"/>
       <c r="U104" s="14"/>
@@ -18222,7 +18267,7 @@
     </row>
     <row r="110" ht="12" customHeight="1" spans="1:43">
       <c r="A110" s="264" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B110" s="264"/>
       <c r="C110" s="264"/>
@@ -18314,7 +18359,7 @@
     </row>
     <row r="112" ht="12" customHeight="1" spans="1:43">
       <c r="A112" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
@@ -18328,7 +18373,7 @@
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
       <c r="M112" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N112" s="99"/>
       <c r="O112" s="99"/>
@@ -18340,7 +18385,7 @@
       <c r="U112" s="99"/>
       <c r="V112" s="100"/>
       <c r="W112" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="X112" s="10"/>
       <c r="Y112" s="10"/>
@@ -18354,7 +18399,7 @@
       <c r="AG112" s="10"/>
       <c r="AH112" s="10"/>
       <c r="AI112" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AJ112" s="99"/>
       <c r="AK112" s="99"/>
@@ -18502,25 +18547,25 @@
     </row>
     <row r="116" ht="12" customHeight="1" spans="1:43">
       <c r="A116" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
       <c r="D116" s="10"/>
       <c r="E116" s="51"/>
       <c r="F116" s="104" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G116" s="18"/>
       <c r="H116" s="18"/>
       <c r="I116" s="18"/>
       <c r="J116" s="18"/>
       <c r="K116" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L116" s="19"/>
       <c r="M116" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
@@ -18532,7 +18577,7 @@
       <c r="U116" s="10"/>
       <c r="V116" s="10"/>
       <c r="W116" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="X116" s="99"/>
       <c r="Y116" s="99"/>
@@ -18540,7 +18585,7 @@
       <c r="AA116" s="99"/>
       <c r="AB116" s="100"/>
       <c r="AC116" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD116" s="10"/>
       <c r="AE116" s="10"/>
@@ -18552,7 +18597,7 @@
       <c r="AK116" s="10"/>
       <c r="AL116" s="10"/>
       <c r="AM116" s="99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AN116" s="99"/>
       <c r="AO116" s="99"/>
@@ -18611,14 +18656,14 @@
       <c r="D118" s="14"/>
       <c r="E118" s="52"/>
       <c r="F118" s="79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G118" s="77"/>
       <c r="H118" s="77"/>
       <c r="I118" s="77"/>
       <c r="J118" s="77"/>
       <c r="K118" s="77" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L118" s="83"/>
       <c r="M118" s="13"/>
@@ -18701,7 +18746,7 @@
     <row r="120" ht="12" customHeight="1"/>
     <row r="121" ht="12" customHeight="1" spans="1:43">
       <c r="A121" s="270" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B121" s="270"/>
       <c r="C121" s="270"/>
@@ -18793,14 +18838,14 @@
     </row>
     <row r="123" ht="12" customHeight="1" spans="1:43">
       <c r="A123" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B123" s="10"/>
       <c r="C123" s="10"/>
       <c r="D123" s="10"/>
       <c r="E123" s="10"/>
       <c r="F123" s="271" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G123" s="271"/>
       <c r="H123" s="271"/>
@@ -18819,14 +18864,14 @@
       <c r="U123" s="271"/>
       <c r="V123" s="273"/>
       <c r="W123" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="X123" s="10"/>
       <c r="Y123" s="10"/>
       <c r="Z123" s="10"/>
       <c r="AA123" s="10"/>
       <c r="AB123" s="99" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC123" s="99"/>
       <c r="AD123" s="99"/>
@@ -18936,14 +18981,14 @@
     </row>
     <row r="126" ht="12" customHeight="1" spans="1:43">
       <c r="A126" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
       <c r="E126" s="14"/>
       <c r="F126" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G126" s="24"/>
       <c r="H126" s="24"/>
@@ -18962,14 +19007,14 @@
       <c r="U126" s="24"/>
       <c r="V126" s="256"/>
       <c r="W126" s="23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X126" s="14"/>
       <c r="Y126" s="14"/>
       <c r="Z126" s="14"/>
       <c r="AA126" s="14"/>
       <c r="AB126" s="46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AC126" s="46"/>
       <c r="AD126" s="46"/>
@@ -19079,7 +19124,7 @@
     </row>
     <row r="129" ht="12" customHeight="1" spans="1:43">
       <c r="A129" s="172" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B129" s="173"/>
       <c r="C129" s="173"/>
@@ -19090,7 +19135,7 @@
       </c>
       <c r="G129" s="133"/>
       <c r="H129" s="133" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I129" s="133"/>
       <c r="J129" s="133"/>
@@ -19231,7 +19276,7 @@
       </c>
       <c r="G132" s="46"/>
       <c r="H132" s="46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I132" s="46"/>
       <c r="J132" s="46"/>
@@ -19363,14 +19408,14 @@
     </row>
     <row r="135" ht="12" customHeight="1" spans="1:43">
       <c r="A135" s="172" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B135" s="173"/>
       <c r="C135" s="173"/>
       <c r="D135" s="173"/>
       <c r="E135" s="173"/>
       <c r="F135" s="133" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G135" s="133"/>
       <c r="H135" s="133"/>
@@ -19637,14 +19682,14 @@
     </row>
     <row r="141" ht="12" customHeight="1" spans="1:43">
       <c r="A141" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B141" s="10"/>
       <c r="C141" s="10"/>
       <c r="D141" s="10"/>
       <c r="E141" s="10"/>
       <c r="F141" s="99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G141" s="99"/>
       <c r="H141" s="99"/>
@@ -19956,7 +20001,7 @@
     </row>
     <row r="148" ht="12" customHeight="1" spans="1:43">
       <c r="A148" s="264" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B148" s="264"/>
       <c r="C148" s="264"/>
@@ -20051,7 +20096,7 @@
         <v>1</v>
       </c>
       <c r="B150" s="180" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C150" s="181"/>
       <c r="D150" s="181"/>
@@ -20070,7 +20115,7 @@
       <c r="Q150" s="181"/>
       <c r="R150" s="181"/>
       <c r="S150" s="104" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T150" s="18"/>
       <c r="U150" s="18"/>
@@ -20192,7 +20237,7 @@
         <v>2</v>
       </c>
       <c r="B153" s="183" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C153" s="182"/>
       <c r="D153" s="182"/>
@@ -20211,7 +20256,7 @@
       <c r="Q153" s="182"/>
       <c r="R153" s="182"/>
       <c r="S153" s="79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T153" s="77"/>
       <c r="U153" s="77"/>
@@ -20348,7 +20393,7 @@
       <c r="Q156" s="182"/>
       <c r="R156" s="182"/>
       <c r="S156" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="T156" s="14"/>
       <c r="U156" s="14"/>
@@ -20372,7 +20417,7 @@
       <c r="AM156" s="77"/>
       <c r="AN156" s="77"/>
       <c r="AO156" s="77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP156" s="77"/>
       <c r="AQ156" s="83"/>
@@ -20487,7 +20532,7 @@
       <c r="Q159" s="182"/>
       <c r="R159" s="182"/>
       <c r="S159" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T159" s="14"/>
       <c r="U159" s="14"/>
@@ -20498,28 +20543,28 @@
       <c r="Z159" s="133"/>
       <c r="AA159" s="87"/>
       <c r="AB159" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC159" s="86"/>
       <c r="AD159" s="87"/>
       <c r="AE159" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF159" s="86"/>
       <c r="AG159" s="133"/>
       <c r="AH159" s="133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AI159" s="133"/>
       <c r="AJ159" s="133"/>
       <c r="AK159" s="87"/>
       <c r="AL159" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM159" s="86"/>
       <c r="AN159" s="87"/>
       <c r="AO159" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP159" s="115"/>
       <c r="AQ159" s="47"/>
@@ -20619,7 +20664,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="183" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C162" s="182"/>
       <c r="D162" s="182"/>
@@ -20638,7 +20683,7 @@
       <c r="Q162" s="182"/>
       <c r="R162" s="182"/>
       <c r="S162" s="79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T162" s="77"/>
       <c r="U162" s="77"/>
@@ -20775,7 +20820,7 @@
       <c r="Q165" s="182"/>
       <c r="R165" s="182"/>
       <c r="S165" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="T165" s="14"/>
       <c r="U165" s="14"/>
@@ -20784,7 +20829,7 @@
       <c r="X165" s="46"/>
       <c r="Y165" s="46"/>
       <c r="Z165" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA165" s="14"/>
       <c r="AB165" s="14"/>
@@ -20801,7 +20846,7 @@
       <c r="AM165" s="77"/>
       <c r="AN165" s="77"/>
       <c r="AO165" s="77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP165" s="77"/>
       <c r="AQ165" s="83"/>
@@ -21245,207 +21290,207 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="240" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B1" s="240" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C1" s="240" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1" s="240" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E1" s="240" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F1" s="240" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="240" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H1" s="240" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I1" s="240" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J1" s="240" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K1" s="240" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L1" s="240" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="240" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" s="240" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C2" s="240" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D2" s="240" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E2" s="240" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F2" s="240" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G2" s="240" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H2" s="240" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I2" s="240" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J2" s="240" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K2" s="240" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L2" s="240" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="C3" s="240" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D3" s="240" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F3" s="240" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H3" s="240" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I3" s="240" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J3" s="240" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="C4" s="240" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D4" s="240" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F4" s="240" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H4" s="240" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I4" s="240" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J4" s="240" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="C5" s="240" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5" s="240" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F5" s="240" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I5" s="240" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J5" s="240" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="C6" s="240" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D6" s="240" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I6" s="240" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J6" s="240" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="240" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" s="240" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I7" s="240" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="C8" s="240" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I8" s="240" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="C9" s="240" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I9" s="240" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="C10" s="240" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="240" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="C11" s="240" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I11" s="240" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="I12" s="240" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="I13" s="240" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="I14" s="240" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -21475,7 +21520,7 @@
       <c r="C1" s="185"/>
       <c r="D1" s="185"/>
       <c r="E1" s="186" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1" s="186"/>
       <c r="G1" s="186"/>
@@ -21692,7 +21737,7 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
@@ -21701,7 +21746,7 @@
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ5" s="21"/>
       <c r="AK5" s="3"/>
@@ -21765,7 +21810,7 @@
     </row>
     <row r="7" ht="12" customHeight="1" spans="1:46">
       <c r="A7" s="55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -21996,7 +22041,7 @@
       <c r="AJ11" s="195"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM11" s="18"/>
       <c r="AN11" s="18"/>
@@ -22153,7 +22198,7 @@
     </row>
     <row r="15" ht="12" customHeight="1" spans="1:46">
       <c r="A15" s="157" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="202"/>
       <c r="C15" s="202"/>
@@ -22164,31 +22209,31 @@
       <c r="H15" s="205"/>
       <c r="I15" s="206"/>
       <c r="J15" s="207" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" s="203"/>
       <c r="L15" s="204"/>
       <c r="M15" s="205"/>
       <c r="N15" s="206"/>
       <c r="O15" s="207" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P15" s="203"/>
       <c r="Q15" s="204"/>
       <c r="R15" s="205"/>
       <c r="S15" s="206"/>
       <c r="T15" s="207" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U15" s="203"/>
       <c r="V15" s="207" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W15" s="202"/>
       <c r="X15" s="202"/>
       <c r="Y15" s="203"/>
       <c r="Z15" s="204" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA15" s="205"/>
       <c r="AB15" s="205"/>
@@ -22309,7 +22354,7 @@
     </row>
     <row r="18" ht="12" customHeight="1" spans="1:46">
       <c r="A18" s="157" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" s="202"/>
       <c r="C18" s="202"/>
@@ -22329,7 +22374,7 @@
       <c r="Q18" s="205"/>
       <c r="R18" s="206"/>
       <c r="S18" s="207" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T18" s="202"/>
       <c r="U18" s="202"/>
@@ -22340,7 +22385,7 @@
       <c r="Z18" s="205"/>
       <c r="AA18" s="206"/>
       <c r="AB18" s="207" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AC18" s="202"/>
       <c r="AD18" s="202"/>
@@ -22459,7 +22504,7 @@
     </row>
     <row r="21" ht="12" customHeight="1" spans="1:46">
       <c r="A21" s="157" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="202"/>
       <c r="C21" s="202"/>
@@ -22475,7 +22520,7 @@
       <c r="M21" s="205"/>
       <c r="N21" s="206"/>
       <c r="O21" s="207" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P21" s="202"/>
       <c r="Q21" s="202"/>
@@ -22655,7 +22700,7 @@
     </row>
     <row r="25" ht="12" customHeight="1" spans="1:46">
       <c r="A25" s="157" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="202"/>
       <c r="C25" s="202"/>
@@ -22666,7 +22711,7 @@
       <c r="H25" s="205"/>
       <c r="I25" s="206"/>
       <c r="J25" s="207" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K25" s="202"/>
       <c r="L25" s="202"/>
@@ -22677,7 +22722,7 @@
       <c r="Q25" s="205"/>
       <c r="R25" s="206"/>
       <c r="S25" s="207" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T25" s="202"/>
       <c r="U25" s="202"/>
@@ -22688,7 +22733,7 @@
       <c r="Z25" s="205"/>
       <c r="AA25" s="206"/>
       <c r="AB25" s="207" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC25" s="202"/>
       <c r="AD25" s="202"/>
@@ -22855,7 +22900,7 @@
     </row>
     <row r="29" ht="12" customHeight="1" spans="1:46">
       <c r="A29" s="39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="39"/>
       <c r="C29" s="39"/>
@@ -22953,7 +22998,7 @@
     </row>
     <row r="31" ht="12" customHeight="1" spans="1:46">
       <c r="A31" s="217" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="58"/>
       <c r="C31" s="58"/>
@@ -22971,7 +23016,7 @@
       <c r="O31" s="58"/>
       <c r="P31" s="59"/>
       <c r="Q31" s="218" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R31" s="58"/>
       <c r="S31" s="58"/>
@@ -22983,7 +23028,7 @@
       <c r="Y31" s="58"/>
       <c r="Z31" s="59"/>
       <c r="AA31" s="218" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AB31" s="58"/>
       <c r="AC31" s="58"/>
@@ -22994,7 +23039,7 @@
       <c r="AH31" s="58"/>
       <c r="AI31" s="59"/>
       <c r="AJ31" s="42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK31" s="10"/>
       <c r="AL31" s="10"/>
@@ -23002,7 +23047,7 @@
       <c r="AN31" s="10"/>
       <c r="AO31" s="10"/>
       <c r="AP31" s="218" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AQ31" s="58"/>
       <c r="AR31" s="58"/>
@@ -23145,12 +23190,12 @@
       <c r="AK34" s="46"/>
       <c r="AL34" s="46"/>
       <c r="AM34" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN34" s="46"/>
       <c r="AO34" s="46"/>
       <c r="AP34" s="79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ34" s="77"/>
       <c r="AR34" s="77"/>
@@ -23293,12 +23338,12 @@
       <c r="AK37" s="46"/>
       <c r="AL37" s="46"/>
       <c r="AM37" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN37" s="46"/>
       <c r="AO37" s="46"/>
       <c r="AP37" s="79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ37" s="77"/>
       <c r="AR37" s="77"/>
@@ -23441,12 +23486,12 @@
       <c r="AK40" s="46"/>
       <c r="AL40" s="46"/>
       <c r="AM40" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN40" s="46"/>
       <c r="AO40" s="46"/>
       <c r="AP40" s="79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ40" s="77"/>
       <c r="AR40" s="77"/>
@@ -23599,7 +23644,7 @@
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:46">
       <c r="A44" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -23697,7 +23742,7 @@
     </row>
     <row r="46" ht="12" customHeight="1" spans="1:46">
       <c r="A46" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -23715,7 +23760,7 @@
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
       <c r="Q46" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R46" s="10"/>
       <c r="S46" s="10"/>
@@ -23723,7 +23768,7 @@
       <c r="U46" s="10"/>
       <c r="V46" s="51"/>
       <c r="W46" s="41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X46" s="10"/>
       <c r="Y46" s="10"/>
@@ -23731,7 +23776,7 @@
       <c r="AA46" s="10"/>
       <c r="AB46" s="10"/>
       <c r="AC46" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AE46" s="10"/>
@@ -23740,13 +23785,13 @@
       <c r="AH46" s="10"/>
       <c r="AI46" s="10"/>
       <c r="AJ46" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK46" s="10"/>
       <c r="AL46" s="10"/>
       <c r="AM46" s="10"/>
       <c r="AN46" s="60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AO46" s="56"/>
       <c r="AP46" s="56"/>
@@ -23872,12 +23917,12 @@
       <c r="R49" s="46"/>
       <c r="S49" s="46"/>
       <c r="T49" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U49" s="46"/>
       <c r="V49" s="53"/>
       <c r="W49" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X49" s="14"/>
       <c r="Y49" s="14"/>
@@ -23885,7 +23930,7 @@
       <c r="AA49" s="14"/>
       <c r="AB49" s="14"/>
       <c r="AC49" s="46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AD49" s="46"/>
       <c r="AE49" s="46"/>
@@ -23901,7 +23946,7 @@
       <c r="AO49" s="46"/>
       <c r="AP49" s="46"/>
       <c r="AQ49" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR49" s="46"/>
       <c r="AS49" s="47"/>
@@ -24072,12 +24117,12 @@
       <c r="R53" s="46"/>
       <c r="S53" s="46"/>
       <c r="T53" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U53" s="46"/>
       <c r="V53" s="53"/>
       <c r="W53" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X53" s="14"/>
       <c r="Y53" s="14"/>
@@ -24099,7 +24144,7 @@
       <c r="AO53" s="46"/>
       <c r="AP53" s="46"/>
       <c r="AQ53" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR53" s="46"/>
       <c r="AS53" s="47"/>
@@ -24299,7 +24344,7 @@
     </row>
     <row r="58" ht="12" customHeight="1" spans="1:46">
       <c r="A58" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B58" s="39"/>
       <c r="C58" s="39"/>
@@ -24397,7 +24442,7 @@
     </row>
     <row r="60" ht="12" customHeight="1" spans="1:46">
       <c r="A60" s="55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B60" s="56"/>
       <c r="C60" s="56"/>
@@ -24406,7 +24451,7 @@
       <c r="F60" s="56"/>
       <c r="G60" s="57"/>
       <c r="H60" s="56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I60" s="58"/>
       <c r="J60" s="58"/>
@@ -24422,7 +24467,7 @@
       <c r="T60" s="58"/>
       <c r="U60" s="59"/>
       <c r="V60" s="60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W60" s="58"/>
       <c r="X60" s="58"/>
@@ -24435,14 +24480,14 @@
       <c r="AE60" s="58"/>
       <c r="AF60" s="59"/>
       <c r="AG60" s="60" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH60" s="58"/>
       <c r="AI60" s="58"/>
       <c r="AJ60" s="58"/>
       <c r="AK60" s="59"/>
       <c r="AL60" s="60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM60" s="56"/>
       <c r="AN60" s="56"/>
@@ -25175,7 +25220,7 @@
     </row>
     <row r="76" ht="12" customHeight="1" spans="1:46">
       <c r="A76" s="39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B76" s="39"/>
       <c r="C76" s="39"/>
@@ -25273,7 +25318,7 @@
     </row>
     <row r="78" ht="12" customHeight="1" spans="1:46">
       <c r="A78" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
@@ -25292,7 +25337,7 @@
       <c r="P78" s="99"/>
       <c r="Q78" s="100"/>
       <c r="R78" s="101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S78" s="102"/>
       <c r="T78" s="102"/>
@@ -25308,7 +25353,7 @@
       <c r="AD78" s="18"/>
       <c r="AE78" s="105"/>
       <c r="AF78" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG78" s="56"/>
       <c r="AH78" s="56"/>
@@ -25519,7 +25564,7 @@
     </row>
     <row r="83" ht="12" customHeight="1" spans="1:46">
       <c r="A83" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B83" s="14"/>
       <c r="C83" s="52"/>
@@ -25527,24 +25572,24 @@
       <c r="E83" s="77"/>
       <c r="F83" s="77"/>
       <c r="G83" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H83" s="115"/>
       <c r="I83" s="46"/>
       <c r="J83" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K83" s="46"/>
       <c r="L83" s="46"/>
       <c r="M83" s="46"/>
       <c r="N83" s="53"/>
       <c r="O83" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P83" s="115"/>
       <c r="Q83" s="47"/>
       <c r="R83" s="116" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S83" s="117"/>
       <c r="T83" s="117"/>
@@ -25769,7 +25814,7 @@
     </row>
     <row r="88" ht="12" customHeight="1" spans="1:46">
       <c r="A88" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
@@ -25788,7 +25833,7 @@
       <c r="P88" s="99"/>
       <c r="Q88" s="100"/>
       <c r="R88" s="55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S88" s="56"/>
       <c r="T88" s="56"/>
@@ -25804,7 +25849,7 @@
       <c r="AD88" s="18"/>
       <c r="AE88" s="105"/>
       <c r="AF88" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG88" s="56"/>
       <c r="AH88" s="56"/>
@@ -26015,7 +26060,7 @@
     </row>
     <row r="93" ht="12" customHeight="1" spans="1:46">
       <c r="A93" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -26023,24 +26068,24 @@
       <c r="E93" s="46"/>
       <c r="F93" s="53"/>
       <c r="G93" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H93" s="115"/>
       <c r="I93" s="46"/>
       <c r="J93" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K93" s="46"/>
       <c r="L93" s="46"/>
       <c r="M93" s="46"/>
       <c r="N93" s="53"/>
       <c r="O93" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P93" s="115"/>
       <c r="Q93" s="47"/>
       <c r="R93" s="134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="S93" s="135"/>
       <c r="T93" s="135"/>
@@ -26265,7 +26310,7 @@
     </row>
     <row r="98" ht="12" customHeight="1" spans="1:46">
       <c r="A98" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
@@ -26284,7 +26329,7 @@
       <c r="P98" s="99"/>
       <c r="Q98" s="100"/>
       <c r="R98" s="55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S98" s="58"/>
       <c r="T98" s="58"/>
@@ -26300,7 +26345,7 @@
       <c r="AD98" s="144"/>
       <c r="AE98" s="145"/>
       <c r="AF98" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG98" s="58"/>
       <c r="AH98" s="58"/>
@@ -26511,7 +26556,7 @@
     </row>
     <row r="103" ht="12" customHeight="1" spans="1:46">
       <c r="A103" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -26519,24 +26564,24 @@
       <c r="E103" s="46"/>
       <c r="F103" s="53"/>
       <c r="G103" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H103" s="115"/>
       <c r="I103" s="46"/>
       <c r="J103" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K103" s="46"/>
       <c r="L103" s="46"/>
       <c r="M103" s="46"/>
       <c r="N103" s="53"/>
       <c r="O103" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P103" s="115"/>
       <c r="Q103" s="47"/>
       <c r="R103" s="157" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S103" s="158"/>
       <c r="T103" s="158"/>
@@ -26809,7 +26854,7 @@
     </row>
     <row r="109" ht="12" customHeight="1" spans="1:46">
       <c r="A109" s="39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B109" s="39"/>
       <c r="C109" s="39"/>
@@ -26907,7 +26952,7 @@
     </row>
     <row r="111" ht="12" customHeight="1" spans="1:46">
       <c r="A111" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B111" s="10"/>
       <c r="C111" s="10"/>
@@ -26921,7 +26966,7 @@
       <c r="K111" s="10"/>
       <c r="L111" s="10"/>
       <c r="M111" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N111" s="99"/>
       <c r="O111" s="99"/>
@@ -26934,7 +26979,7 @@
       <c r="V111" s="99"/>
       <c r="W111" s="100"/>
       <c r="X111" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y111" s="10"/>
       <c r="Z111" s="10"/>
@@ -26947,7 +26992,7 @@
       <c r="AG111" s="10"/>
       <c r="AH111" s="10"/>
       <c r="AI111" s="104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AJ111" s="18"/>
       <c r="AK111" s="18"/>
@@ -27107,7 +27152,7 @@
     </row>
     <row r="115" ht="12" customHeight="1" spans="1:46">
       <c r="A115" s="172" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B115" s="173"/>
       <c r="C115" s="173"/>
@@ -27119,11 +27164,11 @@
       <c r="I115" s="21"/>
       <c r="J115" s="21"/>
       <c r="K115" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L115" s="22"/>
       <c r="M115" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N115" s="10"/>
       <c r="O115" s="10"/>
@@ -27141,7 +27186,7 @@
       <c r="AA115" s="99"/>
       <c r="AB115" s="100"/>
       <c r="AC115" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD115" s="10"/>
       <c r="AE115" s="10"/>
@@ -27221,7 +27266,7 @@
       <c r="I117" s="77"/>
       <c r="J117" s="77"/>
       <c r="K117" s="77" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L117" s="83"/>
       <c r="M117" s="13"/>
@@ -27357,7 +27402,7 @@
     </row>
     <row r="120" ht="12" customHeight="1" spans="1:46">
       <c r="A120" s="39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B120" s="39"/>
       <c r="C120" s="39"/>
@@ -27455,7 +27500,7 @@
     </row>
     <row r="122" ht="12" customHeight="1" spans="1:46">
       <c r="A122" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B122" s="42"/>
       <c r="C122" s="42"/>
@@ -27479,7 +27524,7 @@
       <c r="U122" s="231"/>
       <c r="V122" s="231"/>
       <c r="W122" s="42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="X122" s="42"/>
       <c r="Y122" s="42"/>
@@ -27603,7 +27648,7 @@
     </row>
     <row r="125" ht="12" customHeight="1" spans="1:46">
       <c r="A125" s="23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B125" s="25"/>
       <c r="C125" s="25"/>
@@ -27627,7 +27672,7 @@
       <c r="U125" s="239"/>
       <c r="V125" s="239"/>
       <c r="W125" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="X125" s="25"/>
       <c r="Y125" s="25"/>
@@ -27751,7 +27796,7 @@
     </row>
     <row r="128" ht="12" customHeight="1" spans="1:46">
       <c r="A128" s="23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B128" s="25"/>
       <c r="C128" s="25"/>
@@ -27945,7 +27990,7 @@
     </row>
     <row r="132" ht="12" customHeight="1" spans="1:46">
       <c r="A132" s="157" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B132" s="202"/>
       <c r="C132" s="202"/>
@@ -28235,7 +28280,7 @@
     </row>
     <row r="138" ht="12" customHeight="1" spans="1:46">
       <c r="A138" s="157" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B138" s="202"/>
       <c r="C138" s="202"/>
@@ -28573,7 +28618,7 @@
     </row>
     <row r="145" ht="12" customHeight="1" spans="1:46">
       <c r="A145" s="39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B145" s="39"/>
       <c r="C145" s="39"/>
@@ -28674,7 +28719,7 @@
         <v>1</v>
       </c>
       <c r="B147" s="180" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C147" s="181"/>
       <c r="D147" s="181"/>
@@ -28822,7 +28867,7 @@
         <v>2</v>
       </c>
       <c r="B150" s="183" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C150" s="182"/>
       <c r="D150" s="182"/>
@@ -28987,7 +29032,7 @@
       <c r="S153" s="182"/>
       <c r="T153" s="182"/>
       <c r="U153" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V153" s="14"/>
       <c r="W153" s="14"/>
@@ -29011,7 +29056,7 @@
       <c r="AO153" s="77"/>
       <c r="AP153" s="77"/>
       <c r="AQ153" s="77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AR153" s="77"/>
       <c r="AS153" s="83"/>
@@ -29135,7 +29180,7 @@
       <c r="S156" s="182"/>
       <c r="T156" s="182"/>
       <c r="U156" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V156" s="14"/>
       <c r="W156" s="14"/>
@@ -29146,28 +29191,28 @@
       <c r="AB156" s="133"/>
       <c r="AC156" s="87"/>
       <c r="AD156" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE156" s="86"/>
       <c r="AF156" s="87"/>
       <c r="AG156" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH156" s="86"/>
       <c r="AI156" s="133"/>
       <c r="AJ156" s="133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AK156" s="133"/>
       <c r="AL156" s="133"/>
       <c r="AM156" s="87"/>
       <c r="AN156" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO156" s="86"/>
       <c r="AP156" s="87"/>
       <c r="AQ156" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR156" s="115"/>
       <c r="AS156" s="47"/>
@@ -29272,7 +29317,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="183" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C159" s="182"/>
       <c r="D159" s="182"/>
@@ -29434,7 +29479,7 @@
       <c r="S162" s="182"/>
       <c r="T162" s="182"/>
       <c r="U162" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V162" s="14"/>
       <c r="W162" s="14"/>
@@ -29443,7 +29488,7 @@
       <c r="Z162" s="46"/>
       <c r="AA162" s="46"/>
       <c r="AB162" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC162" s="14"/>
       <c r="AD162" s="14"/>
@@ -29460,7 +29505,7 @@
       <c r="AO162" s="77"/>
       <c r="AP162" s="77"/>
       <c r="AQ162" s="77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AR162" s="77"/>
       <c r="AS162" s="83"/>
@@ -29924,7 +29969,7 @@
   <sheetData>
     <row r="1" ht="12" customHeight="1" spans="1:46">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30046,7 +30091,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -30056,7 +30101,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
@@ -30122,14 +30167,14 @@
     </row>
     <row r="5" ht="12" customHeight="1" spans="1:46">
       <c r="A5" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -30275,7 +30320,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
@@ -30357,7 +30402,7 @@
       <c r="AJ9" s="16"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AM9" s="18"/>
       <c r="AN9" s="18"/>
@@ -30514,7 +30559,7 @@
     </row>
     <row r="13" ht="12" customHeight="1" spans="1:46">
       <c r="A13" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -30527,7 +30572,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="24">
@@ -30536,7 +30581,7 @@
       <c r="M13" s="24"/>
       <c r="N13" s="24"/>
       <c r="O13" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P13" s="14"/>
       <c r="Q13" s="24">
@@ -30545,17 +30590,17 @@
       <c r="R13" s="24"/>
       <c r="S13" s="24"/>
       <c r="T13" s="25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U13" s="14"/>
       <c r="V13" s="25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
       <c r="Y13" s="14"/>
       <c r="Z13" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA13" s="24"/>
       <c r="AB13" s="24"/>
@@ -30676,14 +30721,14 @@
     </row>
     <row r="16" ht="12" customHeight="1" spans="1:46">
       <c r="A16" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
@@ -30698,26 +30743,26 @@
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T16" s="14"/>
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
       <c r="W16" s="24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X16" s="24"/>
       <c r="Y16" s="24"/>
       <c r="Z16" s="24"/>
       <c r="AA16" s="24"/>
       <c r="AB16" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AC16" s="14"/>
       <c r="AD16" s="14"/>
       <c r="AE16" s="14"/>
       <c r="AF16" s="24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG16" s="24"/>
       <c r="AH16" s="24"/>
@@ -30832,14 +30877,14 @@
     </row>
     <row r="19" ht="12" customHeight="1" spans="1:46">
       <c r="A19" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
@@ -30854,7 +30899,7 @@
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T19" s="14"/>
       <c r="U19" s="14"/>
@@ -30862,7 +30907,7 @@
       <c r="W19" s="14"/>
       <c r="X19" s="14"/>
       <c r="Y19" s="27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z19" s="28"/>
       <c r="AA19" s="28"/>
@@ -30984,14 +31029,14 @@
     </row>
     <row r="22" ht="12" customHeight="1" spans="1:46">
       <c r="A22" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
@@ -31002,7 +31047,7 @@
       <c r="M22" s="24"/>
       <c r="N22" s="24"/>
       <c r="O22" s="25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
@@ -31011,7 +31056,7 @@
       <c r="T22" s="14"/>
       <c r="U22" s="14"/>
       <c r="V22" s="30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="W22" s="30"/>
       <c r="X22" s="30"/>
@@ -31184,7 +31229,7 @@
     </row>
     <row r="26" ht="12" customHeight="1" spans="1:46">
       <c r="A26" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -31197,7 +31242,7 @@
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
       <c r="J26" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
@@ -31210,7 +31255,7 @@
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T26" s="14"/>
       <c r="U26" s="14"/>
@@ -31223,13 +31268,13 @@
       <c r="Z26" s="24"/>
       <c r="AA26" s="24"/>
       <c r="AB26" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC26" s="14"/>
       <c r="AD26" s="14"/>
       <c r="AE26" s="14"/>
       <c r="AF26" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG26" s="24"/>
       <c r="AH26" s="24"/>
@@ -31392,7 +31437,7 @@
     </row>
     <row r="30" ht="12" customHeight="1" spans="1:46">
       <c r="A30" s="39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="39"/>
       <c r="C30" s="39"/>
@@ -31490,7 +31535,7 @@
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:46">
       <c r="A32" s="41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -31506,7 +31551,7 @@
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
@@ -31517,7 +31562,7 @@
       <c r="V32" s="10"/>
       <c r="W32" s="10"/>
       <c r="X32" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Y32" s="10"/>
       <c r="Z32" s="10"/>
@@ -31525,7 +31570,7 @@
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
       <c r="AD32" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AE32" s="10"/>
       <c r="AF32" s="10"/>
@@ -31533,7 +31578,7 @@
       <c r="AH32" s="10"/>
       <c r="AI32" s="10"/>
       <c r="AJ32" s="42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK32" s="10"/>
       <c r="AL32" s="10"/>
@@ -31541,7 +31586,7 @@
       <c r="AN32" s="10"/>
       <c r="AO32" s="10"/>
       <c r="AP32" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AQ32" s="10"/>
       <c r="AR32" s="10"/>
@@ -31646,7 +31691,7 @@
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:46">
       <c r="A35" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" s="46"/>
       <c r="C35" s="46"/>
@@ -31662,7 +31707,7 @@
       <c r="M35" s="46"/>
       <c r="N35" s="46"/>
       <c r="O35" s="46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P35" s="46"/>
       <c r="Q35" s="46"/>
@@ -31673,7 +31718,7 @@
       <c r="V35" s="46"/>
       <c r="W35" s="46"/>
       <c r="X35" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y35" s="46"/>
       <c r="Z35" s="46"/>
@@ -31681,7 +31726,7 @@
       <c r="AB35" s="46"/>
       <c r="AC35" s="46"/>
       <c r="AD35" s="46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AE35" s="46"/>
       <c r="AF35" s="46"/>
@@ -31694,14 +31739,14 @@
       <c r="AK35" s="46"/>
       <c r="AL35" s="46"/>
       <c r="AM35" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN35" s="46">
         <v>5</v>
       </c>
       <c r="AO35" s="46"/>
       <c r="AP35" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ35" s="46"/>
       <c r="AR35" s="46"/>
@@ -31806,7 +31851,7 @@
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:46">
       <c r="A38" s="45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B38" s="46"/>
       <c r="C38" s="46"/>
@@ -31822,7 +31867,7 @@
       <c r="M38" s="46"/>
       <c r="N38" s="46"/>
       <c r="O38" s="46" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P38" s="46"/>
       <c r="Q38" s="46"/>
@@ -31833,7 +31878,7 @@
       <c r="V38" s="46"/>
       <c r="W38" s="46"/>
       <c r="X38" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y38" s="46"/>
       <c r="Z38" s="46"/>
@@ -31841,7 +31886,7 @@
       <c r="AB38" s="46"/>
       <c r="AC38" s="46"/>
       <c r="AD38" s="46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AE38" s="46"/>
       <c r="AF38" s="46"/>
@@ -31854,14 +31899,14 @@
       <c r="AK38" s="46"/>
       <c r="AL38" s="46"/>
       <c r="AM38" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN38" s="46">
         <v>5</v>
       </c>
       <c r="AO38" s="46"/>
       <c r="AP38" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ38" s="46"/>
       <c r="AR38" s="46"/>
@@ -31966,7 +32011,7 @@
     </row>
     <row r="41" ht="12" customHeight="1" spans="1:46">
       <c r="A41" s="45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B41" s="46"/>
       <c r="C41" s="46"/>
@@ -31982,7 +32027,7 @@
       <c r="M41" s="46"/>
       <c r="N41" s="46"/>
       <c r="O41" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P41" s="46"/>
       <c r="Q41" s="46"/>
@@ -31993,7 +32038,7 @@
       <c r="V41" s="46"/>
       <c r="W41" s="46"/>
       <c r="X41" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y41" s="46"/>
       <c r="Z41" s="46"/>
@@ -32001,7 +32046,7 @@
       <c r="AB41" s="46"/>
       <c r="AC41" s="46"/>
       <c r="AD41" s="46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE41" s="46"/>
       <c r="AF41" s="46"/>
@@ -32014,14 +32059,14 @@
       <c r="AK41" s="46"/>
       <c r="AL41" s="46"/>
       <c r="AM41" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN41" s="46">
         <v>12</v>
       </c>
       <c r="AO41" s="46"/>
       <c r="AP41" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AQ41" s="46"/>
       <c r="AR41" s="46"/>
@@ -32174,7 +32219,7 @@
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:46">
       <c r="A45" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -32272,7 +32317,7 @@
     </row>
     <row r="47" ht="12" customHeight="1" spans="1:46">
       <c r="A47" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -32290,7 +32335,7 @@
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
       <c r="Q47" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R47" s="10"/>
       <c r="S47" s="10"/>
@@ -32298,7 +32343,7 @@
       <c r="U47" s="10"/>
       <c r="V47" s="51"/>
       <c r="W47" s="41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X47" s="10"/>
       <c r="Y47" s="10"/>
@@ -32306,7 +32351,7 @@
       <c r="AA47" s="10"/>
       <c r="AB47" s="10"/>
       <c r="AC47" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AE47" s="10"/>
@@ -32315,13 +32360,13 @@
       <c r="AH47" s="10"/>
       <c r="AI47" s="10"/>
       <c r="AJ47" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK47" s="10"/>
       <c r="AL47" s="10"/>
       <c r="AM47" s="10"/>
       <c r="AN47" s="42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AO47" s="10"/>
       <c r="AP47" s="10"/>
@@ -32428,7 +32473,7 @@
     </row>
     <row r="50" ht="12" customHeight="1" spans="1:46">
       <c r="A50" s="45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B50" s="46"/>
       <c r="C50" s="46"/>
@@ -32451,14 +32496,14 @@
       <c r="R50" s="46"/>
       <c r="S50" s="46"/>
       <c r="T50" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U50" s="46">
         <v>1</v>
       </c>
       <c r="V50" s="53"/>
       <c r="W50" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="X50" s="14"/>
       <c r="Y50" s="14"/>
@@ -32466,7 +32511,7 @@
       <c r="AA50" s="14"/>
       <c r="AB50" s="14"/>
       <c r="AC50" s="46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AD50" s="46"/>
       <c r="AE50" s="46"/>
@@ -32486,7 +32531,7 @@
       <c r="AO50" s="46"/>
       <c r="AP50" s="46"/>
       <c r="AQ50" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR50" s="46">
         <v>3</v>
@@ -32640,7 +32685,7 @@
     </row>
     <row r="54" ht="12" customHeight="1" spans="1:46">
       <c r="A54" s="45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B54" s="46"/>
       <c r="C54" s="46"/>
@@ -32663,14 +32708,14 @@
       <c r="R54" s="46"/>
       <c r="S54" s="46"/>
       <c r="T54" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U54" s="46">
         <v>2</v>
       </c>
       <c r="V54" s="53"/>
       <c r="W54" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X54" s="14"/>
       <c r="Y54" s="14"/>
@@ -32678,7 +32723,7 @@
       <c r="AA54" s="14"/>
       <c r="AB54" s="14"/>
       <c r="AC54" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AD54" s="46"/>
       <c r="AE54" s="46"/>
@@ -32698,7 +32743,7 @@
       <c r="AO54" s="46"/>
       <c r="AP54" s="46"/>
       <c r="AQ54" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR54" s="46">
         <v>4</v>
@@ -32900,7 +32945,7 @@
     </row>
     <row r="59" ht="12" customHeight="1" spans="1:46">
       <c r="A59" s="39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B59" s="39"/>
       <c r="C59" s="39"/>
@@ -32998,7 +33043,7 @@
     </row>
     <row r="61" ht="12" customHeight="1" spans="1:46">
       <c r="A61" s="55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B61" s="56"/>
       <c r="C61" s="56"/>
@@ -33007,7 +33052,7 @@
       <c r="F61" s="56"/>
       <c r="G61" s="57"/>
       <c r="H61" s="56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I61" s="58"/>
       <c r="J61" s="58"/>
@@ -33023,14 +33068,14 @@
       <c r="T61" s="58"/>
       <c r="U61" s="59"/>
       <c r="V61" s="60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="W61" s="58"/>
       <c r="X61" s="58"/>
       <c r="Y61" s="58"/>
       <c r="Z61" s="59"/>
       <c r="AA61" s="60" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB61" s="58"/>
       <c r="AC61" s="58"/>
@@ -33038,14 +33083,14 @@
       <c r="AE61" s="58"/>
       <c r="AF61" s="59"/>
       <c r="AG61" s="60" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH61" s="58"/>
       <c r="AI61" s="58"/>
       <c r="AJ61" s="58"/>
       <c r="AK61" s="59"/>
       <c r="AL61" s="60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM61" s="58"/>
       <c r="AN61" s="58"/>
@@ -33154,7 +33199,7 @@
     </row>
     <row r="64" ht="12" customHeight="1" spans="1:46">
       <c r="A64" s="76" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="77"/>
       <c r="C64" s="77"/>
@@ -33163,7 +33208,7 @@
       <c r="F64" s="77"/>
       <c r="G64" s="78"/>
       <c r="H64" s="79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I64" s="77"/>
       <c r="J64" s="77"/>
@@ -33186,7 +33231,7 @@
       <c r="Y64" s="81"/>
       <c r="Z64" s="82"/>
       <c r="AA64" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB64" s="46"/>
       <c r="AC64" s="46"/>
@@ -33194,14 +33239,14 @@
       <c r="AE64" s="46"/>
       <c r="AF64" s="46"/>
       <c r="AG64" s="79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH64" s="77"/>
       <c r="AI64" s="77"/>
       <c r="AJ64" s="77"/>
       <c r="AK64" s="78"/>
       <c r="AL64" s="79" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM64" s="77"/>
       <c r="AN64" s="77"/>
@@ -33262,7 +33307,7 @@
     </row>
     <row r="66" ht="12" customHeight="1" spans="1:46">
       <c r="A66" s="76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="77"/>
       <c r="C66" s="77"/>
@@ -33271,7 +33316,7 @@
       <c r="F66" s="77"/>
       <c r="G66" s="78"/>
       <c r="H66" s="79" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I66" s="77"/>
       <c r="J66" s="77"/>
@@ -33294,7 +33339,7 @@
       <c r="Y66" s="81"/>
       <c r="Z66" s="82"/>
       <c r="AA66" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB66" s="46"/>
       <c r="AC66" s="46"/>
@@ -33302,14 +33347,14 @@
       <c r="AE66" s="46"/>
       <c r="AF66" s="46"/>
       <c r="AG66" s="79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH66" s="77"/>
       <c r="AI66" s="77"/>
       <c r="AJ66" s="77"/>
       <c r="AK66" s="78"/>
       <c r="AL66" s="79" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM66" s="77"/>
       <c r="AN66" s="77"/>
@@ -33370,7 +33415,7 @@
     </row>
     <row r="68" ht="12" customHeight="1" spans="1:46">
       <c r="A68" s="76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="77"/>
       <c r="C68" s="77"/>
@@ -33379,7 +33424,7 @@
       <c r="F68" s="77"/>
       <c r="G68" s="78"/>
       <c r="H68" s="79" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I68" s="77"/>
       <c r="J68" s="77"/>
@@ -33402,7 +33447,7 @@
       <c r="Y68" s="81"/>
       <c r="Z68" s="82"/>
       <c r="AA68" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB68" s="46"/>
       <c r="AC68" s="46"/>
@@ -33410,14 +33455,14 @@
       <c r="AE68" s="46"/>
       <c r="AF68" s="46"/>
       <c r="AG68" s="79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH68" s="77"/>
       <c r="AI68" s="77"/>
       <c r="AJ68" s="77"/>
       <c r="AK68" s="78"/>
       <c r="AL68" s="79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM68" s="77"/>
       <c r="AN68" s="77"/>
@@ -33478,7 +33523,7 @@
     </row>
     <row r="70" ht="12" customHeight="1" spans="1:46">
       <c r="A70" s="76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="77"/>
       <c r="C70" s="77"/>
@@ -33487,7 +33532,7 @@
       <c r="F70" s="77"/>
       <c r="G70" s="78"/>
       <c r="H70" s="79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I70" s="77"/>
       <c r="J70" s="77"/>
@@ -33510,7 +33555,7 @@
       <c r="Y70" s="81"/>
       <c r="Z70" s="82"/>
       <c r="AA70" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB70" s="46"/>
       <c r="AC70" s="46"/>
@@ -33518,14 +33563,14 @@
       <c r="AE70" s="46"/>
       <c r="AF70" s="46"/>
       <c r="AG70" s="79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH70" s="77"/>
       <c r="AI70" s="77"/>
       <c r="AJ70" s="77"/>
       <c r="AK70" s="78"/>
       <c r="AL70" s="79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AM70" s="77"/>
       <c r="AN70" s="77"/>
@@ -33586,7 +33631,7 @@
     </row>
     <row r="72" ht="12" customHeight="1" spans="1:46">
       <c r="A72" s="76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B72" s="77"/>
       <c r="C72" s="77"/>
@@ -33595,7 +33640,7 @@
       <c r="F72" s="77"/>
       <c r="G72" s="78"/>
       <c r="H72" s="79" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I72" s="77"/>
       <c r="J72" s="77"/>
@@ -33618,7 +33663,7 @@
       <c r="Y72" s="81"/>
       <c r="Z72" s="82"/>
       <c r="AA72" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB72" s="46"/>
       <c r="AC72" s="46"/>
@@ -33626,14 +33671,14 @@
       <c r="AE72" s="46"/>
       <c r="AF72" s="46"/>
       <c r="AG72" s="79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH72" s="77"/>
       <c r="AI72" s="77"/>
       <c r="AJ72" s="77"/>
       <c r="AK72" s="78"/>
       <c r="AL72" s="79" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM72" s="77"/>
       <c r="AN72" s="77"/>
@@ -33694,7 +33739,7 @@
     </row>
     <row r="74" ht="12" customHeight="1" spans="1:46">
       <c r="A74" s="76" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B74" s="77"/>
       <c r="C74" s="77"/>
@@ -33703,7 +33748,7 @@
       <c r="F74" s="77"/>
       <c r="G74" s="78"/>
       <c r="H74" s="79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I74" s="77"/>
       <c r="J74" s="77"/>
@@ -33726,7 +33771,7 @@
       <c r="Y74" s="81"/>
       <c r="Z74" s="82"/>
       <c r="AA74" s="92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB74" s="21"/>
       <c r="AC74" s="21"/>
@@ -33734,14 +33779,14 @@
       <c r="AE74" s="21"/>
       <c r="AF74" s="93"/>
       <c r="AG74" s="79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH74" s="77"/>
       <c r="AI74" s="77"/>
       <c r="AJ74" s="77"/>
       <c r="AK74" s="78"/>
       <c r="AL74" s="79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AM74" s="77"/>
       <c r="AN74" s="77"/>
@@ -33850,7 +33895,7 @@
     </row>
     <row r="77" ht="12" customHeight="1" spans="1:46">
       <c r="A77" s="39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -33948,12 +33993,12 @@
     </row>
     <row r="79" ht="12" customHeight="1" spans="1:46">
       <c r="A79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="99" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E79" s="99"/>
       <c r="F79" s="99"/>
@@ -33969,13 +34014,13 @@
       <c r="P79" s="99"/>
       <c r="Q79" s="100"/>
       <c r="R79" s="101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S79" s="102"/>
       <c r="T79" s="102"/>
       <c r="U79" s="103"/>
       <c r="V79" s="104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="W79" s="18"/>
       <c r="X79" s="18"/>
@@ -33987,13 +34032,13 @@
       <c r="AD79" s="18"/>
       <c r="AE79" s="105"/>
       <c r="AF79" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG79" s="56"/>
       <c r="AH79" s="56"/>
       <c r="AI79" s="57"/>
       <c r="AJ79" s="104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" s="18"/>
       <c r="AL79" s="18"/>
@@ -34200,7 +34245,7 @@
     </row>
     <row r="84" ht="12" customHeight="1" spans="1:46">
       <c r="A84" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="52"/>
@@ -34210,32 +34255,32 @@
       <c r="E84" s="77"/>
       <c r="F84" s="77"/>
       <c r="G84" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H84" s="115">
         <v>6</v>
       </c>
       <c r="I84" s="46"/>
       <c r="J84" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K84" s="46"/>
       <c r="L84" s="46"/>
       <c r="M84" s="46"/>
       <c r="N84" s="53"/>
       <c r="O84" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P84" s="115"/>
       <c r="Q84" s="47"/>
       <c r="R84" s="116" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S84" s="117"/>
       <c r="T84" s="117"/>
       <c r="U84" s="118"/>
       <c r="V84" s="119" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="W84" s="120"/>
       <c r="X84" s="120"/>
@@ -34456,12 +34501,12 @@
     </row>
     <row r="89" ht="12" customHeight="1" spans="1:46">
       <c r="A89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="133" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E89" s="133"/>
       <c r="F89" s="133"/>
@@ -34477,13 +34522,13 @@
       <c r="P89" s="99"/>
       <c r="Q89" s="100"/>
       <c r="R89" s="55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S89" s="56"/>
       <c r="T89" s="56"/>
       <c r="U89" s="57"/>
       <c r="V89" s="104" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W89" s="18"/>
       <c r="X89" s="18"/>
@@ -34495,13 +34540,13 @@
       <c r="AD89" s="18"/>
       <c r="AE89" s="105"/>
       <c r="AF89" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG89" s="56"/>
       <c r="AH89" s="56"/>
       <c r="AI89" s="57"/>
       <c r="AJ89" s="104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK89" s="18"/>
       <c r="AL89" s="18"/>
@@ -34708,7 +34753,7 @@
     </row>
     <row r="94" ht="12" customHeight="1" spans="1:46">
       <c r="A94" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -34718,32 +34763,32 @@
       <c r="E94" s="46"/>
       <c r="F94" s="53"/>
       <c r="G94" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H94" s="115">
         <v>2</v>
       </c>
       <c r="I94" s="46"/>
       <c r="J94" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K94" s="46"/>
       <c r="L94" s="46"/>
       <c r="M94" s="46"/>
       <c r="N94" s="53"/>
       <c r="O94" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P94" s="115"/>
       <c r="Q94" s="47"/>
       <c r="R94" s="134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="S94" s="135"/>
       <c r="T94" s="135"/>
       <c r="U94" s="136"/>
       <c r="V94" s="119" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W94" s="120"/>
       <c r="X94" s="120"/>
@@ -34964,7 +35009,7 @@
     </row>
     <row r="99" ht="12" customHeight="1" spans="1:46">
       <c r="A99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
@@ -34983,7 +35028,7 @@
       <c r="P99" s="99"/>
       <c r="Q99" s="100"/>
       <c r="R99" s="55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S99" s="58"/>
       <c r="T99" s="58"/>
@@ -34999,7 +35044,7 @@
       <c r="AD99" s="144"/>
       <c r="AE99" s="145"/>
       <c r="AF99" s="60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG99" s="58"/>
       <c r="AH99" s="58"/>
@@ -35210,7 +35255,7 @@
     </row>
     <row r="104" ht="12" customHeight="1" spans="1:46">
       <c r="A104" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -35218,24 +35263,24 @@
       <c r="E104" s="46"/>
       <c r="F104" s="53"/>
       <c r="G104" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H104" s="115"/>
       <c r="I104" s="46"/>
       <c r="J104" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K104" s="46"/>
       <c r="L104" s="46"/>
       <c r="M104" s="46"/>
       <c r="N104" s="53"/>
       <c r="O104" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P104" s="115"/>
       <c r="Q104" s="47"/>
       <c r="R104" s="157" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S104" s="158"/>
       <c r="T104" s="158"/>
@@ -35508,7 +35553,7 @@
     </row>
     <row r="110" ht="12" customHeight="1" spans="1:46">
       <c r="A110" s="39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -35606,7 +35651,7 @@
     </row>
     <row r="112" ht="12" customHeight="1" spans="1:46">
       <c r="A112" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
@@ -35620,7 +35665,7 @@
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
       <c r="M112" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N112" s="99"/>
       <c r="O112" s="99"/>
@@ -35633,7 +35678,7 @@
       <c r="V112" s="99"/>
       <c r="W112" s="100"/>
       <c r="X112" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y112" s="10"/>
       <c r="Z112" s="10"/>
@@ -35646,7 +35691,7 @@
       <c r="AG112" s="10"/>
       <c r="AH112" s="10"/>
       <c r="AI112" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AJ112" s="99"/>
       <c r="AK112" s="99"/>
@@ -35806,25 +35851,25 @@
     </row>
     <row r="116" ht="12" customHeight="1" spans="1:46">
       <c r="A116" s="172" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B116" s="173"/>
       <c r="C116" s="173"/>
       <c r="D116" s="173"/>
       <c r="E116" s="173"/>
       <c r="F116" s="92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G116" s="21"/>
       <c r="H116" s="21"/>
       <c r="I116" s="21"/>
       <c r="J116" s="21"/>
       <c r="K116" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L116" s="22"/>
       <c r="M116" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
@@ -35834,7 +35879,7 @@
       <c r="S116" s="10"/>
       <c r="T116" s="10"/>
       <c r="U116" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V116" s="99"/>
       <c r="W116" s="99"/>
@@ -35844,7 +35889,7 @@
       <c r="AA116" s="99"/>
       <c r="AB116" s="100"/>
       <c r="AC116" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD116" s="10"/>
       <c r="AE116" s="10"/>
@@ -35854,7 +35899,7 @@
       <c r="AI116" s="10"/>
       <c r="AJ116" s="10"/>
       <c r="AK116" s="99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL116" s="99"/>
       <c r="AM116" s="99"/>
@@ -35921,14 +35966,14 @@
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
       <c r="F118" s="79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G118" s="77"/>
       <c r="H118" s="77"/>
       <c r="I118" s="77"/>
       <c r="J118" s="77"/>
       <c r="K118" s="77" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L118" s="83"/>
       <c r="M118" s="13"/>
@@ -36112,7 +36157,7 @@
     </row>
     <row r="122" ht="12" customHeight="1" spans="1:46">
       <c r="A122" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B122" s="10"/>
       <c r="C122" s="10"/>
@@ -36134,7 +36179,7 @@
       <c r="S122" s="10"/>
       <c r="T122" s="10"/>
       <c r="U122" s="174" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="V122" s="174"/>
       <c r="W122" s="174"/>
@@ -36260,7 +36305,7 @@
     </row>
     <row r="125" ht="12" customHeight="1" spans="1:46">
       <c r="A125" s="23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -36282,7 +36327,7 @@
       <c r="S125" s="14"/>
       <c r="T125" s="14"/>
       <c r="U125" s="176" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="V125" s="176"/>
       <c r="W125" s="176"/>
@@ -36408,7 +36453,7 @@
     </row>
     <row r="128" ht="12" customHeight="1" spans="1:46">
       <c r="A128" s="23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -36430,7 +36475,7 @@
       <c r="S128" s="14"/>
       <c r="T128" s="14"/>
       <c r="U128" s="176" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V128" s="176"/>
       <c r="W128" s="176"/>
@@ -36556,7 +36601,7 @@
     </row>
     <row r="131" ht="12" customHeight="1" spans="1:46">
       <c r="A131" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -36578,7 +36623,7 @@
       <c r="S131" s="14"/>
       <c r="T131" s="14"/>
       <c r="U131" s="176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="V131" s="176"/>
       <c r="W131" s="176"/>
@@ -36704,7 +36749,7 @@
     </row>
     <row r="134" ht="12" customHeight="1" spans="1:46">
       <c r="A134" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -36726,7 +36771,7 @@
       <c r="S134" s="14"/>
       <c r="T134" s="14"/>
       <c r="U134" s="176" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V134" s="176"/>
       <c r="W134" s="176"/>
@@ -36900,7 +36945,7 @@
     </row>
     <row r="138" ht="12" customHeight="1" spans="1:46">
       <c r="A138" s="39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -37001,7 +37046,7 @@
         <v>1</v>
       </c>
       <c r="B140" s="180" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C140" s="181"/>
       <c r="D140" s="181"/>
@@ -37022,7 +37067,7 @@
       <c r="S140" s="181"/>
       <c r="T140" s="181"/>
       <c r="U140" s="99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V140" s="99"/>
       <c r="W140" s="99"/>
@@ -37151,7 +37196,7 @@
         <v>2</v>
       </c>
       <c r="B143" s="183" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C143" s="182"/>
       <c r="D143" s="182"/>
@@ -37172,7 +37217,7 @@
       <c r="S143" s="182"/>
       <c r="T143" s="182"/>
       <c r="U143" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V143" s="46"/>
       <c r="W143" s="46"/>
@@ -37318,7 +37363,7 @@
       <c r="S146" s="182"/>
       <c r="T146" s="182"/>
       <c r="U146" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V146" s="14"/>
       <c r="W146" s="14"/>
@@ -37342,7 +37387,7 @@
       <c r="AO146" s="77"/>
       <c r="AP146" s="77"/>
       <c r="AQ146" s="115" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AR146" s="46"/>
       <c r="AS146" s="47"/>
@@ -37466,7 +37511,7 @@
       <c r="S149" s="182"/>
       <c r="T149" s="182"/>
       <c r="U149" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="V149" s="14"/>
       <c r="W149" s="14"/>
@@ -37477,28 +37522,28 @@
       <c r="AB149" s="133"/>
       <c r="AC149" s="87"/>
       <c r="AD149" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE149" s="86"/>
       <c r="AF149" s="87"/>
       <c r="AG149" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH149" s="86"/>
       <c r="AI149" s="133"/>
       <c r="AJ149" s="133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AK149" s="133"/>
       <c r="AL149" s="133"/>
       <c r="AM149" s="87"/>
       <c r="AN149" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO149" s="86"/>
       <c r="AP149" s="87"/>
       <c r="AQ149" s="77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR149" s="115"/>
       <c r="AS149" s="47"/>
@@ -37605,7 +37650,7 @@
         <v>3</v>
       </c>
       <c r="B152" s="183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C152" s="182"/>
       <c r="D152" s="182"/>
@@ -37626,7 +37671,7 @@
       <c r="S152" s="182"/>
       <c r="T152" s="182"/>
       <c r="U152" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V152" s="46"/>
       <c r="W152" s="46"/>
@@ -37755,7 +37800,7 @@
         <v>4</v>
       </c>
       <c r="B155" s="183" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C155" s="182"/>
       <c r="D155" s="182"/>
@@ -37776,7 +37821,7 @@
       <c r="S155" s="182"/>
       <c r="T155" s="182"/>
       <c r="U155" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V155" s="46"/>
       <c r="W155" s="46"/>
@@ -37922,7 +37967,7 @@
       <c r="S158" s="182"/>
       <c r="T158" s="182"/>
       <c r="U158" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V158" s="14"/>
       <c r="W158" s="14"/>
@@ -37931,7 +37976,7 @@
       <c r="Z158" s="46"/>
       <c r="AA158" s="46"/>
       <c r="AB158" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC158" s="14"/>
       <c r="AD158" s="14"/>
@@ -37948,7 +37993,7 @@
       <c r="AO158" s="77"/>
       <c r="AP158" s="77"/>
       <c r="AQ158" s="115" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AR158" s="46"/>
       <c r="AS158" s="47"/>
@@ -38055,7 +38100,7 @@
         <v>5</v>
       </c>
       <c r="B161" s="183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C161" s="182"/>
       <c r="D161" s="182"/>
@@ -38076,7 +38121,7 @@
       <c r="S161" s="182"/>
       <c r="T161" s="182"/>
       <c r="U161" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V161" s="46"/>
       <c r="W161" s="46"/>
@@ -38599,7 +38644,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC50:AI53">
       <formula1>DB!$K$1:$K$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U140:AS145 U152:AS157 U116:AB119 U161:AS163 AK116:AS119">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U116:AB119 U140:AS145 U152:AS157 U161:AS163 AK116:AS119">
       <formula1>DB!$E$1:$E$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A50:P57">
